--- a/model/CX_VIA_Model.xlsx
+++ b/model/CX_VIA_Model.xlsx
@@ -48,7 +48,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="25">
+  <numFmts count="24">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(#,##0.0%_);_(\(#,##0.0%\)_);_(#,##0.0%_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-??_);_(@_)"/>
@@ -71,9 +71,8 @@
     <numFmt numFmtId="183" formatCode="mmm\-dd\-yyyy"/>
     <numFmt numFmtId="184" formatCode="_(* #,##0_);_(* \(#,##0\)_)\ ;_(* 0_)"/>
     <numFmt numFmtId="185" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="186" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="187" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="188" formatCode="0.0x"/>
+    <numFmt numFmtId="186" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="187" formatCode="0.0x"/>
   </numFmts>
   <fonts count="50">
     <font>
@@ -664,7 +663,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1065,7 +1064,7 @@
     <xf numFmtId="170" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="188" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="187" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="16" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="16" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1112,12 +1111,6 @@
     <xf numFmtId="164" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="19" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="19" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1129,36 +1122,23 @@
     <xf numFmtId="164" fontId="19" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="186" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="186" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="186" fontId="19" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="186" fontId="19" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="186" fontId="19" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="186" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="186" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="186" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="187" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="187" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="187" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="187" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="187" fontId="19" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="187" fontId="19" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="187" fontId="19" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="19" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="48" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1325,7 +1305,7 @@
   <commentList>
     <comment ref="M6" authorId="0" shapeId="0">
       <text>
-        <t>Steady-state UFCF margin after SBC: ~10% adj. EBITDA (operator-like) less ~5% SBC, ~1.4% capex and working capital. 2030 UFCF is still negative, so it cannot be capitalized directly.</t>
+        <t>Steady-state UFCF margin after SBC: ~16% adj. EBITDA (below mgmt's 20-25% target) less ~4% SBC and ~1.4% capex, plus some working capital; taxes shielded by NOLs. 2030 UFCF is still negative, so it cannot be capitalized directly.</t>
       </text>
     </comment>
     <comment ref="C17" authorId="0" shapeId="0">
@@ -1350,7 +1330,7 @@
     </comment>
     <comment ref="M27" authorId="0" shapeId="0">
       <text>
-        <t>Blend: ~20% software revenue at ~5x + ~80% services at ~0.6x (transit operators) = ~1.5x. VIA trades at 2.9x FY27E revenue (Key Stats). 2030 EBIT is negative, so an EBIT multiple cannot be used.</t>
+        <t>De-rating from 2.9x FY27E EV/revenue today (Key Stats) toward a services mix: ~20% software at ~6x + ~80% services at ~1.5x = ~2.5x. 2030 EBIT is negative, so an EBIT multiple cannot be used.</t>
       </text>
     </comment>
     <comment ref="E29" authorId="0" shapeId="0">
@@ -1370,7 +1350,7 @@
     </comment>
     <comment ref="F35" authorId="0" shapeId="0">
       <text>
-        <t>1H26 SBC = 12% of revenue (Cash Flow tab).</t>
+        <t>1H26 SBC = 12% of revenue (Cash Flow tab), inflated by IPO grants; falls to 6% by FY30 as they vest.</t>
       </text>
     </comment>
     <comment ref="F36" authorId="0" shapeId="0">
@@ -1408,14 +1388,14 @@
     <author>Model</author>
   </authors>
   <commentList>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>ESTIMATE. Via reports all recurring revenue as one 'subscription' line. Software ~24% of recurring revenue, services ~76% (margin back-out in VIA_software_services_mix.xlsx; Bleecker 72% as published).</t>
+      </text>
+    </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
         <t>Historical: residual = total - one-time - software - network.</t>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>Vehicle-hours x price per hour.</t>
       </text>
     </comment>
     <comment ref="E7" authorId="0" shapeId="0">
@@ -1425,100 +1405,65 @@
     </comment>
     <comment ref="F7" authorId="0" shapeId="0">
       <text>
-        <t>Opening run-rate + launch-year factor x new contract value launched.</t>
+        <t>Opening run-rate + half of the contract value launched in the year.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Historical total revenue links to Annual IS (CapIQ). Stream split is an estimate: Via reports all recurring revenue as one 'subscription' line.</t>
+        <t>Historical total revenue links to Annual IS (CapIQ).</t>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
+    <comment ref="F17" authorId="0" shapeId="0">
       <text>
-        <t>Customer count at year-end. Source: Via S-1 (FY23, FY24) and FY25 10-K (821). Includes 94 Downtowner customers acquired Dec 2025.</t>
+        <t>Organic customer growth ~9% ex-Downtowner (thesis 3), ~+2%/yr price. FY26 +3%: 94 small Downtowner customers add little. Software fees face near-zero bids (Spare bid $0.01 at LA Metro).</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Expansion at existing customers less budget-driven downsell (~4%/yr: Jersey City cut ~half, federal stopgap / ARPA cliff), with price +2%/yr as rebids reset rates. FY26 +28% ties to 1H26 actuals ($263M revenue) plus the H2 ramp.</t>
       </text>
     </comment>
     <comment ref="F19" authorId="0" shapeId="0">
       <text>
-        <t>Organic customer growth ~9% ex-Downtowner (thesis 3). FY26 +8%: 847 at Q2'26.</t>
+        <t>FY26: Twin Cities MI (Apr), Rochester $14.6M (Sep) and part of the 2026 wins; FY27: rest of the signed ~$70M book. Then ~2 mid-sized cities a year (thesis 1.1). Earned at half rate in the launch year.</t>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0" shapeId="0">
+      <text>
+        <t>Sioux Falls: 2024 NTD purchased transportation paid $11.07M (Via's first network deal).</t>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0">
+      <text>
+        <t>Sioux Falls ~$11.4M + Mobile $12.1M/yr (from Oct 2025).</t>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0">
+      <text>
+        <t>10-K: one-time revenue 3% of total in FY24 and FY25 (97% recurring). FY23 assumed the same.</t>
       </text>
     </comment>
     <comment ref="F21" authorId="0" shapeId="0">
       <text>
-        <t>FY26 -5%: 94 small Downtowner customers dilute the average. Then +2%/yr: software fees face $0.01 bids (Spare at LA Metro).</t>
+        <t>3% (10-K FY24-25; 1H26 also 3%).</t>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
+    <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>ESTIMATE. Software ~24% of recurring revenue, services ~76% (margin back-out in VIA_software_services_mix.xlsx; Bleecker 72% services as published).</t>
+        <t>Bleecker assumption; reported cost split implies ~73%.</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
+      <text>
+        <t>Bleecker TaaS gross margin, arithmetic corrected and updated to 2026 contract pricing.</t>
       </text>
     </comment>
     <comment ref="F26" authorId="0" shapeId="0">
       <text>
-        <t>Expansion with existing customers drives most growth (10-K). FY26 +28% (net +25%) calibrated so FY26 revenue matches 1H26 actuals ($263M) plus the H2 ramp (~consensus).</t>
+        <t>ASSUMPTION (undisclosed): operator economics, below the ~29% on microtransit. Labor is 72% of mid-sized bus system cost (NTD 2024); CFO: 'some accretive, some less.'</t>
       </text>
     </comment>
     <comment ref="F27" authorId="0" shapeId="0">
-      <text>
-        <t>Budget-bound downsell (thesis 3.2): Jersey City cut ~half of Via spend (Jul 2026); ARPA / federal stopgap cliff from FY27.</t>
-      </text>
-    </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
-      <text>
-        <t>ESTIMATE. Blended $/vehicle-hour across legacy (~$42-50, e.g. DCTA $42.95) and 2025-26 contracts (micro $64.5-70, para $67.75, LA Metro $82.35). FY23-24 deflated 3%/yr (Via's example contract escalator).</t>
-      </text>
-    </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
-      <text>
-        <t>3% escalator on existing contracts, but rebids reset price (thesis 3.1: LA Metro set the target cost per trip).</t>
-      </text>
-    </comment>
-    <comment ref="D33" authorId="0" shapeId="0">
-      <text>
-        <t>Sioux Falls: 2024 NTD purchased-transportation paid $11.07M (first Via network deal).</t>
-      </text>
-    </comment>
-    <comment ref="E33" authorId="0" shapeId="0">
-      <text>
-        <t>Sioux Falls ~$11.4M + Mobile $12.1M/yr (from Oct 2025).</t>
-      </text>
-    </comment>
-    <comment ref="F34" authorId="0" shapeId="0">
-      <text>
-        <t>FY26: Twin Cities MI (Apr), Rochester $14.6M (Sep), part of 2026 wins (&gt;$40M ACV). Signed book ~$70M once launched. Mid-sized US cities only (thesis 1.1).</t>
-      </text>
-    </comment>
-    <comment ref="F35" authorId="0" shapeId="0">
-      <text>
-        <t>Share of a year's launched contract value earned in the launch year. FY26 H2-weighted (Rochester from Sep).</t>
-      </text>
-    </comment>
-    <comment ref="E38" authorId="0" shapeId="0">
-      <text>
-        <t>10-K: one-time revenue 3% of total in FY24 and FY25 (97% recurring). FY23 assumed the same.</t>
-      </text>
-    </comment>
-    <comment ref="F38" authorId="0" shapeId="0">
-      <text>
-        <t>3% (10-K FY24-25; 1H26 also 3%).</t>
-      </text>
-    </comment>
-    <comment ref="F41" authorId="0" shapeId="0">
-      <text>
-        <t>Software gross margin (Bleecker assumption; reported cost split implies ~73%).</t>
-      </text>
-    </comment>
-    <comment ref="F42" authorId="0" shapeId="0">
-      <text>
-        <t>Microtransit/paratransit services gross margin (Bleecker TaaS GM, arithmetic corrected and updated to 2026 contract pricing).</t>
-      </text>
-    </comment>
-    <comment ref="F43" authorId="0" shapeId="0">
-      <text>
-        <t>ASSUMPTION (undisclosed): bus-operator economics. Labor is 72% of mid-sized bus system cost (NTD 2024); CFO: 'some accretive, some less.'</t>
-      </text>
-    </comment>
-    <comment ref="F44" authorId="0" shapeId="0">
       <text>
         <t>Implementation / consulting.</t>
       </text>
@@ -1958,7 +1903,7 @@
         </is>
       </c>
       <c r="M6" s="223" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -2856,7 +2801,7 @@
         </is>
       </c>
       <c r="M27" s="250" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
@@ -2983,23 +2928,23 @@
         <v/>
       </c>
       <c r="F32" s="257">
-        <f>1-'Revenue Build'!F46</f>
+        <f>1-'Revenue Build'!F29</f>
         <v/>
       </c>
       <c r="G32" s="258">
-        <f>1-'Revenue Build'!G46</f>
+        <f>1-'Revenue Build'!G29</f>
         <v/>
       </c>
       <c r="H32" s="258">
-        <f>1-'Revenue Build'!H46</f>
+        <f>1-'Revenue Build'!H29</f>
         <v/>
       </c>
       <c r="I32" s="258">
-        <f>1-'Revenue Build'!I46</f>
+        <f>1-'Revenue Build'!I29</f>
         <v/>
       </c>
       <c r="J32" s="258">
-        <f>1-'Revenue Build'!J46</f>
+        <f>1-'Revenue Build'!J29</f>
         <v/>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -3107,16 +3052,16 @@
         <v>0.12</v>
       </c>
       <c r="G35" s="262" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H35" s="262" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I35" s="262" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J35" s="262" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="L35" s="22" t="inlineStr">
         <is>
@@ -3580,36 +3525,33 @@
           <t>Software (platform)</t>
         </is>
       </c>
-      <c r="C4" s="274">
-        <f>(C9-C8)*C22</f>
-        <v/>
-      </c>
-      <c r="D4" s="274">
-        <f>(D9-D8)*D22</f>
-        <v/>
-      </c>
-      <c r="E4" s="275">
-        <f>(E9-E8)*E22</f>
-        <v/>
+      <c r="C4" s="274" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D4" s="274" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E4" s="275" t="n">
+        <v>101.1</v>
       </c>
       <c r="F4" s="276">
-        <f>F18*F20/1000</f>
+        <f>E4*(1+F17)</f>
         <v/>
       </c>
       <c r="G4" s="276">
-        <f>G18*G20/1000</f>
+        <f>F4*(1+G17)</f>
         <v/>
       </c>
       <c r="H4" s="276">
-        <f>H18*H20/1000</f>
+        <f>G4*(1+H17)</f>
         <v/>
       </c>
       <c r="I4" s="276">
-        <f>I18*I20/1000</f>
+        <f>H4*(1+I17)</f>
         <v/>
       </c>
       <c r="J4" s="276">
-        <f>J18*J20/1000</f>
+        <f>I4*(1+J17)</f>
         <v/>
       </c>
     </row>
@@ -3671,23 +3613,23 @@
         <v/>
       </c>
       <c r="F6" s="276">
-        <f>F25*F29</f>
+        <f>E6*(1+F18)</f>
         <v/>
       </c>
       <c r="G6" s="276">
-        <f>G25*G29</f>
+        <f>F6*(1+G18)</f>
         <v/>
       </c>
       <c r="H6" s="276">
-        <f>H25*H29</f>
+        <f>G6*(1+H18)</f>
         <v/>
       </c>
       <c r="I6" s="276">
-        <f>I25*I29</f>
+        <f>H6*(1+I18)</f>
         <v/>
       </c>
       <c r="J6" s="276">
-        <f>J25*J29</f>
+        <f>I6*(1+J18)</f>
         <v/>
       </c>
     </row>
@@ -3707,23 +3649,23 @@
         <v>14.4</v>
       </c>
       <c r="F7" s="276">
-        <f>E33+F34*F35</f>
+        <f>E20+0.5*F19</f>
         <v/>
       </c>
       <c r="G7" s="276">
-        <f>F33+G34*G35</f>
+        <f>F20+0.5*G19</f>
         <v/>
       </c>
       <c r="H7" s="276">
-        <f>G33+H34*H35</f>
+        <f>G20+0.5*H19</f>
         <v/>
       </c>
       <c r="I7" s="276">
-        <f>H33+I34*I35</f>
+        <f>H20+0.5*I19</f>
         <v/>
       </c>
       <c r="J7" s="276">
-        <f>I33+J34*J35</f>
+        <f>I20+0.5*J19</f>
         <v/>
       </c>
     </row>
@@ -3734,35 +3676,35 @@
         </is>
       </c>
       <c r="C8" s="274">
-        <f>C9*C38</f>
+        <f>C9*C21</f>
         <v/>
       </c>
       <c r="D8" s="274">
-        <f>D9*D38</f>
+        <f>D9*D21</f>
         <v/>
       </c>
       <c r="E8" s="275">
-        <f>E9*E38</f>
+        <f>E9*E21</f>
         <v/>
       </c>
       <c r="F8" s="276">
-        <f>(F4+F5)*F38/(1-F38)</f>
+        <f>(F4+F5)*F21/(1-F21)</f>
         <v/>
       </c>
       <c r="G8" s="276">
-        <f>(G4+G5)*G38/(1-G38)</f>
+        <f>(G4+G5)*G21/(1-G21)</f>
         <v/>
       </c>
       <c r="H8" s="276">
-        <f>(H4+H5)*H38/(1-H38)</f>
+        <f>(H4+H5)*H21/(1-H21)</f>
         <v/>
       </c>
       <c r="I8" s="276">
-        <f>(I4+I5)*I38/(1-I38)</f>
+        <f>(I4+I5)*I21/(1-I21)</f>
         <v/>
       </c>
       <c r="J8" s="276">
-        <f>(J4+J5)*J38/(1-J38)</f>
+        <f>(J4+J5)*J21/(1-J21)</f>
         <v/>
       </c>
     </row>
@@ -3985,824 +3927,444 @@
       <c r="J16" s="296" t="n"/>
     </row>
     <row r="17" ht="12.75" customFormat="1" customHeight="1" s="8">
-      <c r="B17" s="84" t="inlineStr">
-        <is>
-          <t>SOFTWARE</t>
+      <c r="B17" s="85" t="inlineStr">
+        <is>
+          <t>Software revenue % growth</t>
         </is>
       </c>
       <c r="C17" s="297" t="n"/>
-      <c r="D17" s="297" t="n"/>
-      <c r="E17" s="298" t="n"/>
-      <c r="F17" s="299" t="n"/>
-      <c r="G17" s="299" t="n"/>
-      <c r="H17" s="299" t="n"/>
-      <c r="I17" s="299" t="n"/>
-      <c r="J17" s="299" t="n"/>
+      <c r="D17" s="297">
+        <f>D4/C4-1</f>
+        <v/>
+      </c>
+      <c r="E17" s="298">
+        <f>E4/D4-1</f>
+        <v/>
+      </c>
+      <c r="F17" s="299" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G17" s="300" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H17" s="300" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="300" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J17" s="301" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Customers (year-end, #)</t>
-        </is>
-      </c>
-      <c r="C18" s="300" t="n">
-        <v>597</v>
-      </c>
-      <c r="D18" s="300" t="n">
-        <v>665</v>
-      </c>
-      <c r="E18" s="301" t="n">
-        <v>821</v>
-      </c>
-      <c r="F18" s="302">
-        <f>E18*(1+F19)</f>
-        <v/>
-      </c>
-      <c r="G18" s="302">
-        <f>F18*(1+G19)</f>
-        <v/>
-      </c>
-      <c r="H18" s="302">
-        <f>G18*(1+H19)</f>
-        <v/>
-      </c>
-      <c r="I18" s="302">
-        <f>H18*(1+I19)</f>
-        <v/>
-      </c>
-      <c r="J18" s="302">
-        <f>I18*(1+J19)</f>
-        <v/>
+      <c r="B18" s="85" t="inlineStr">
+        <is>
+          <t>Microtransit &amp; paratransit % growth (net of downsell)</t>
+        </is>
+      </c>
+      <c r="C18" s="297" t="n"/>
+      <c r="D18" s="297">
+        <f>D6/C6-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="298">
+        <f>E6/D6-1</f>
+        <v/>
+      </c>
+      <c r="F18" s="299" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G18" s="300" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H18" s="300" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I18" s="300" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J18" s="301" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="B19" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">   % growth</t>
-        </is>
-      </c>
-      <c r="C19" s="303" t="n"/>
-      <c r="D19" s="303">
-        <f>D18/C18-1</f>
-        <v/>
-      </c>
-      <c r="E19" s="304">
-        <f>E18/D18-1</f>
-        <v/>
-      </c>
-      <c r="F19" s="305" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G19" s="306" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H19" s="306" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I19" s="306" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J19" s="307" t="n">
-        <v>0.06</v>
+          <t>Network: new contract value launched ($mm)</t>
+        </is>
+      </c>
+      <c r="C19" s="302" t="n"/>
+      <c r="D19" s="302">
+        <f>D20-C20</f>
+        <v/>
+      </c>
+      <c r="E19" s="303">
+        <f>E20-D20</f>
+        <v/>
+      </c>
+      <c r="F19" s="304" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="305" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="305" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" s="305" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" s="306" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Software revenue per customer ($000)</t>
-        </is>
-      </c>
-      <c r="C20" s="300">
-        <f>C4/C18*1000</f>
-        <v/>
-      </c>
-      <c r="D20" s="300">
-        <f>D4/D18*1000</f>
-        <v/>
-      </c>
-      <c r="E20" s="301">
-        <f>E4/E18*1000</f>
-        <v/>
+          <t>Network: contract run-rate, year-end ($mm)</t>
+        </is>
+      </c>
+      <c r="C20" s="307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="307" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" s="308" t="n">
+        <v>23.5</v>
       </c>
       <c r="F20" s="302">
-        <f>E20*(1+F21)</f>
+        <f>E20+F19</f>
         <v/>
       </c>
       <c r="G20" s="302">
-        <f>F20*(1+G21)</f>
+        <f>F20+G19</f>
         <v/>
       </c>
       <c r="H20" s="302">
-        <f>G20*(1+H21)</f>
+        <f>G20+H19</f>
         <v/>
       </c>
       <c r="I20" s="302">
-        <f>H20*(1+I21)</f>
+        <f>H20+I19</f>
         <v/>
       </c>
       <c r="J20" s="302">
-        <f>I20*(1+J21)</f>
+        <f>I20+J19</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="12.75" customFormat="1" customHeight="1" s="29">
       <c r="B21" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">   % growth</t>
-        </is>
-      </c>
-      <c r="C21" s="303" t="n"/>
-      <c r="D21" s="303">
-        <f>D20/C20-1</f>
-        <v/>
-      </c>
-      <c r="E21" s="304">
-        <f>E20/D20-1</f>
-        <v/>
-      </c>
-      <c r="F21" s="305" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G21" s="306" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H21" s="306" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I21" s="306" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J21" s="307" t="n">
-        <v>0.02</v>
+          <t>One-time revenue % of total</t>
+        </is>
+      </c>
+      <c r="C21" s="309" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D21" s="309" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E21" s="223" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F21" s="299" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G21" s="300" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H21" s="300" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I21" s="300" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J21" s="301" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="29" t="n"/>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Software share of recurring revenue</t>
-        </is>
-      </c>
-      <c r="C22" s="259" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D22" s="259" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E22" s="260" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F22" s="292">
-        <f>F4/(F4+F5)</f>
-        <v/>
-      </c>
-      <c r="G22" s="292">
-        <f>G4/(G4+G5)</f>
-        <v/>
-      </c>
-      <c r="H22" s="292">
-        <f>H4/(H4+H5)</f>
-        <v/>
-      </c>
-      <c r="I22" s="292">
-        <f>I4/(I4+I5)</f>
-        <v/>
-      </c>
-      <c r="J22" s="292">
-        <f>J4/(J4+J5)</f>
-        <v/>
-      </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="29" t="n"/>
+      <c r="B23" s="84" t="inlineStr">
+        <is>
+          <t>GROSS MARGIN BY STREAM</t>
+        </is>
+      </c>
+      <c r="C23" s="310" t="n"/>
+      <c r="D23" s="310" t="n"/>
+      <c r="E23" s="311" t="n"/>
+      <c r="F23" s="312" t="n"/>
+      <c r="G23" s="312" t="n"/>
+      <c r="H23" s="312" t="n"/>
+      <c r="I23" s="312" t="n"/>
+      <c r="J23" s="312" t="n"/>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="B24" s="84" t="inlineStr">
-        <is>
-          <t>MICROTRANSIT &amp; PARATRANSIT</t>
+      <c r="B24" s="85" t="inlineStr">
+        <is>
+          <t>Software</t>
         </is>
       </c>
       <c r="C24" s="297" t="n"/>
       <c r="D24" s="297" t="n"/>
       <c r="E24" s="298" t="n"/>
-      <c r="F24" s="299" t="n"/>
-      <c r="G24" s="299" t="n"/>
-      <c r="H24" s="299" t="n"/>
-      <c r="I24" s="299" t="n"/>
-      <c r="J24" s="299" t="n"/>
+      <c r="F24" s="299" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G24" s="300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H24" s="300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I24" s="300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J24" s="301" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Vehicle-hours (mm)</t>
-        </is>
-      </c>
-      <c r="C25" s="308">
-        <f>C6/C29</f>
-        <v/>
-      </c>
-      <c r="D25" s="308">
-        <f>D6/D29</f>
-        <v/>
-      </c>
-      <c r="E25" s="309">
-        <f>E6/E29</f>
-        <v/>
-      </c>
-      <c r="F25" s="310">
-        <f>E25*(1+F28)</f>
-        <v/>
-      </c>
-      <c r="G25" s="310">
-        <f>F25*(1+G28)</f>
-        <v/>
-      </c>
-      <c r="H25" s="310">
-        <f>G25*(1+H28)</f>
-        <v/>
-      </c>
-      <c r="I25" s="310">
-        <f>H25*(1+I28)</f>
-        <v/>
-      </c>
-      <c r="J25" s="310">
-        <f>I25*(1+J28)</f>
-        <v/>
+      <c r="B25" s="85" t="inlineStr">
+        <is>
+          <t>Microtransit &amp; paratransit</t>
+        </is>
+      </c>
+      <c r="C25" s="297" t="n"/>
+      <c r="D25" s="297" t="n"/>
+      <c r="E25" s="298" t="n"/>
+      <c r="F25" s="299" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="G25" s="300" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="H25" s="300" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="I25" s="300" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="J25" s="301" t="n">
+        <v>0.293</v>
       </c>
     </row>
     <row r="26" ht="12.75" customFormat="1" customHeight="1" s="29">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Expansion (existing + new customers)</t>
-        </is>
-      </c>
-      <c r="C26" s="303" t="n"/>
-      <c r="D26" s="303" t="n"/>
-      <c r="E26" s="304" t="n"/>
-      <c r="F26" s="305" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G26" s="306" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H26" s="306" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I26" s="306" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J26" s="307" t="n">
-        <v>0.13</v>
+          <t>Network deals</t>
+        </is>
+      </c>
+      <c r="C26" s="297" t="n"/>
+      <c r="D26" s="297" t="n"/>
+      <c r="E26" s="298" t="n"/>
+      <c r="F26" s="299" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G26" s="300" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H26" s="300" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I26" s="300" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J26" s="301" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="29" t="n"/>
       <c r="B27" s="85" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Downsell / budget cuts</t>
-        </is>
-      </c>
-      <c r="C27" s="303" t="n"/>
-      <c r="D27" s="303" t="n"/>
-      <c r="E27" s="304" t="n"/>
-      <c r="F27" s="305" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G27" s="306" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="H27" s="306" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I27" s="306" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J27" s="307" t="n">
-        <v>-0.05</v>
+          <t>One-time</t>
+        </is>
+      </c>
+      <c r="C27" s="297" t="n"/>
+      <c r="D27" s="297" t="n"/>
+      <c r="E27" s="298" t="n"/>
+      <c r="F27" s="299" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G27" s="300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H27" s="300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I27" s="300" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J27" s="301" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="28" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Net hours growth</t>
-        </is>
-      </c>
-      <c r="C28" s="259" t="n"/>
-      <c r="D28" s="259">
-        <f>D25/C25-1</f>
-        <v/>
-      </c>
-      <c r="E28" s="260">
-        <f>E25/D25-1</f>
-        <v/>
-      </c>
-      <c r="F28" s="292">
-        <f>F26+F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="292">
-        <f>G26+G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="292">
-        <f>H26+H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="292">
-        <f>I26+I27</f>
-        <v/>
-      </c>
-      <c r="J28" s="292">
-        <f>J26+J27</f>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Gross profit ($mm)</t>
+        </is>
+      </c>
+      <c r="C28" s="278">
+        <f>'Annual IS'!B10</f>
+        <v/>
+      </c>
+      <c r="D28" s="278">
+        <f>'Annual IS'!C10</f>
+        <v/>
+      </c>
+      <c r="E28" s="279">
+        <f>'Annual IS'!D10</f>
+        <v/>
+      </c>
+      <c r="F28" s="277">
+        <f>F4*F24+F6*F25+F7*F26+F8*F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="277">
+        <f>G4*G24+G6*G25+G7*G26+G8*G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="277">
+        <f>H4*H24+H6*H25+H7*H26+H8*H27</f>
+        <v/>
+      </c>
+      <c r="I28" s="277">
+        <f>I4*I24+I6*I25+I7*I26+I8*I27</f>
+        <v/>
+      </c>
+      <c r="J28" s="277">
+        <f>J4*J24+J6*J25+J7*J26+J8*J27</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Price per vehicle-hour ($)</t>
-        </is>
-      </c>
-      <c r="C29" s="311" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="D29" s="311" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="E29" s="312" t="n">
-        <v>60</v>
-      </c>
-      <c r="F29" s="313">
-        <f>E29*(1+F30)</f>
-        <v/>
-      </c>
-      <c r="G29" s="313">
-        <f>F29*(1+G30)</f>
-        <v/>
-      </c>
-      <c r="H29" s="313">
-        <f>G29*(1+H30)</f>
-        <v/>
-      </c>
-      <c r="I29" s="313">
-        <f>H29*(1+I30)</f>
-        <v/>
-      </c>
-      <c r="J29" s="313">
-        <f>I29*(1+J30)</f>
+      <c r="B29" s="280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Gross margin</t>
+        </is>
+      </c>
+      <c r="C29" s="281">
+        <f>C28/C9</f>
+        <v/>
+      </c>
+      <c r="D29" s="282">
+        <f>D28/D9</f>
+        <v/>
+      </c>
+      <c r="E29" s="283">
+        <f>E28/E9</f>
+        <v/>
+      </c>
+      <c r="F29" s="282">
+        <f>F28/F9</f>
+        <v/>
+      </c>
+      <c r="G29" s="282">
+        <f>G28/G9</f>
+        <v/>
+      </c>
+      <c r="H29" s="282">
+        <f>H28/H9</f>
+        <v/>
+      </c>
+      <c r="I29" s="282">
+        <f>I28/I9</f>
+        <v/>
+      </c>
+      <c r="J29" s="282">
+        <f>J28/J9</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="B30" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   % growth</t>
-        </is>
-      </c>
-      <c r="C30" s="303" t="n"/>
-      <c r="D30" s="303">
-        <f>D29/C29-1</f>
-        <v/>
-      </c>
-      <c r="E30" s="304">
-        <f>E29/D29-1</f>
-        <v/>
-      </c>
-      <c r="F30" s="305" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G30" s="306" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H30" s="306" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I30" s="306" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J30" s="307" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="B30" s="288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Consensus gross margin (CapIQ)</t>
+        </is>
+      </c>
+      <c r="C30" s="289">
+        <f>C29</f>
+        <v/>
+      </c>
+      <c r="D30" s="289">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="290">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F30" s="313">
+        <f>'Key Stats'!F20</f>
+        <v/>
+      </c>
+      <c r="G30" s="313">
+        <f>'Key Stats'!G20</f>
+        <v/>
+      </c>
+      <c r="H30" s="313">
+        <f>'Key Stats'!H20</f>
+        <v/>
+      </c>
+      <c r="I30" s="291" t="n"/>
+      <c r="J30" s="291" t="n"/>
     </row>
     <row r="31" ht="12.75" customHeight="1"/>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="29" t="n"/>
-      <c r="B32" s="84" t="inlineStr">
-        <is>
-          <t>NETWORK DEALS</t>
-        </is>
-      </c>
-      <c r="C32" s="297" t="n"/>
-      <c r="D32" s="297" t="n"/>
-      <c r="E32" s="298" t="n"/>
-      <c r="F32" s="299" t="n"/>
-      <c r="G32" s="299" t="n"/>
-      <c r="H32" s="299" t="n"/>
-      <c r="I32" s="299" t="n"/>
-      <c r="J32" s="299" t="n"/>
+      <c r="B32" s="314" t="inlineStr">
+        <is>
+          <t>Colour key: blue = hardcoded input, black = formula, green = link to another tab. Hover over cells with a red corner for sources.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Contract run-rate, year-end ($mm)</t>
-        </is>
-      </c>
-      <c r="C33" s="314" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="314" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" s="315" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F33" s="316">
-        <f>E33+F34</f>
-        <v/>
-      </c>
-      <c r="G33" s="316">
-        <f>F33+G34</f>
-        <v/>
-      </c>
-      <c r="H33" s="316">
-        <f>G33+H34</f>
-        <v/>
-      </c>
-      <c r="I33" s="316">
-        <f>H33+I34</f>
-        <v/>
-      </c>
-      <c r="J33" s="316">
-        <f>I33+J34</f>
-        <v/>
+      <c r="B33" s="314" t="inlineStr">
+        <is>
+          <t>Thesis 1: network deals are bus-operator contracts priced at ~95-107% of the city's transit budget, so they carry a 25% gross margin vs ~29% on microtransit and 75% on software.</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="B34" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   New contract value launched ($mm)</t>
-        </is>
-      </c>
-      <c r="C34" s="316" t="n"/>
-      <c r="D34" s="316">
-        <f>D33-C33</f>
-        <v/>
-      </c>
-      <c r="E34" s="317">
-        <f>E33-D33</f>
-        <v/>
-      </c>
-      <c r="F34" s="318" t="n">
-        <v>30</v>
-      </c>
-      <c r="G34" s="319" t="n">
-        <v>25</v>
-      </c>
-      <c r="H34" s="319" t="n">
-        <v>20</v>
-      </c>
-      <c r="I34" s="319" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" s="320" t="n">
-        <v>20</v>
+      <c r="B34" s="314" t="inlineStr">
+        <is>
+          <t>Thesis 3: microtransit/paratransit growth is net of budget-driven downsell and rebid price resets.</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="B35" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Launch-year revenue factor</t>
-        </is>
-      </c>
-      <c r="C35" s="310" t="n"/>
-      <c r="D35" s="310" t="n"/>
-      <c r="E35" s="321" t="n"/>
-      <c r="F35" s="322" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G35" s="323" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H35" s="323" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I35" s="323" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J35" s="324" t="n">
-        <v>0.5</v>
+      <c r="B35" s="314" t="inlineStr">
+        <is>
+          <t>Consensus: CapIQ (Key Stats tab) FY26-28E. FY29-30 have no consensus.</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1">
-      <c r="B37" s="84" t="inlineStr">
-        <is>
-          <t>ONE-TIME</t>
-        </is>
-      </c>
-      <c r="C37" s="297" t="n"/>
-      <c r="D37" s="297" t="n"/>
-      <c r="E37" s="298" t="n"/>
-      <c r="F37" s="299" t="n"/>
-      <c r="G37" s="299" t="n"/>
-      <c r="H37" s="299" t="n"/>
-      <c r="I37" s="299" t="n"/>
-      <c r="J37" s="299" t="n"/>
-    </row>
-    <row r="38" ht="12.75" customHeight="1">
-      <c r="B38" s="85" t="inlineStr">
-        <is>
-          <t>One-time revenue % of total</t>
-        </is>
-      </c>
-      <c r="C38" s="325" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D38" s="325" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E38" s="223" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F38" s="305" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G38" s="306" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H38" s="306" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I38" s="306" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J38" s="307" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
     <row r="39" ht="12.75" customHeight="1"/>
-    <row r="40" ht="12.75" customHeight="1">
-      <c r="B40" s="84" t="inlineStr">
-        <is>
-          <t>GROSS PROFIT BY STREAM</t>
-        </is>
-      </c>
-      <c r="C40" s="297" t="n"/>
-      <c r="D40" s="297" t="n"/>
-      <c r="E40" s="298" t="n"/>
-      <c r="F40" s="299" t="n"/>
-      <c r="G40" s="299" t="n"/>
-      <c r="H40" s="299" t="n"/>
-      <c r="I40" s="299" t="n"/>
-      <c r="J40" s="299" t="n"/>
-    </row>
-    <row r="41" ht="12.75" customHeight="1">
-      <c r="B41" s="85" t="inlineStr">
-        <is>
-          <t>Software gross margin</t>
-        </is>
-      </c>
-      <c r="C41" s="303" t="n"/>
-      <c r="D41" s="303" t="n"/>
-      <c r="E41" s="304" t="n"/>
-      <c r="F41" s="305" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G41" s="306" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H41" s="306" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I41" s="306" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J41" s="307" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="42" ht="12.75" customHeight="1">
-      <c r="B42" s="85" t="inlineStr">
-        <is>
-          <t>Microtransit &amp; paratransit gross margin</t>
-        </is>
-      </c>
-      <c r="C42" s="303" t="n"/>
-      <c r="D42" s="303" t="n"/>
-      <c r="E42" s="304" t="n"/>
-      <c r="F42" s="305" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="G42" s="306" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="H42" s="306" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="I42" s="306" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="J42" s="307" t="n">
-        <v>0.293</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="85" t="inlineStr">
-        <is>
-          <t>Network gross margin</t>
-        </is>
-      </c>
-      <c r="C43" s="303" t="n"/>
-      <c r="D43" s="303" t="n"/>
-      <c r="E43" s="304" t="n"/>
-      <c r="F43" s="305" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G43" s="306" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H43" s="306" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I43" s="306" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J43" s="307" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="85" t="inlineStr">
-        <is>
-          <t>One-time gross margin</t>
-        </is>
-      </c>
-      <c r="C44" s="303" t="n"/>
-      <c r="D44" s="303" t="n"/>
-      <c r="E44" s="304" t="n"/>
-      <c r="F44" s="305" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G44" s="306" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H44" s="306" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I44" s="306" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J44" s="307" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="45" ht="12.75" customHeight="1">
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>Gross profit ($mm)</t>
-        </is>
-      </c>
-      <c r="C45" s="278">
-        <f>'Annual IS'!B10</f>
-        <v/>
-      </c>
-      <c r="D45" s="278">
-        <f>'Annual IS'!C10</f>
-        <v/>
-      </c>
-      <c r="E45" s="279">
-        <f>'Annual IS'!D10</f>
-        <v/>
-      </c>
-      <c r="F45" s="277">
-        <f>F4*F41+F6*F42+F7*F43+F8*F44</f>
-        <v/>
-      </c>
-      <c r="G45" s="277">
-        <f>G4*G41+G6*G42+G7*G43+G8*G44</f>
-        <v/>
-      </c>
-      <c r="H45" s="277">
-        <f>H4*H41+H6*H42+H7*H43+H8*H44</f>
-        <v/>
-      </c>
-      <c r="I45" s="277">
-        <f>I4*I41+I6*I42+I7*I43+I8*I44</f>
-        <v/>
-      </c>
-      <c r="J45" s="277">
-        <f>J4*J41+J6*J42+J7*J43+J8*J44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="12.75" customHeight="1">
-      <c r="B46" s="280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Gross margin</t>
-        </is>
-      </c>
-      <c r="C46" s="281">
-        <f>C45/C9</f>
-        <v/>
-      </c>
-      <c r="D46" s="282">
-        <f>D45/D9</f>
-        <v/>
-      </c>
-      <c r="E46" s="283">
-        <f>E45/E9</f>
-        <v/>
-      </c>
-      <c r="F46" s="282">
-        <f>F45/F9</f>
-        <v/>
-      </c>
-      <c r="G46" s="282">
-        <f>G45/G9</f>
-        <v/>
-      </c>
-      <c r="H46" s="282">
-        <f>H45/H9</f>
-        <v/>
-      </c>
-      <c r="I46" s="282">
-        <f>I45/I9</f>
-        <v/>
-      </c>
-      <c r="J46" s="282">
-        <f>J45/J9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="12.75" customHeight="1">
-      <c r="B47" s="288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Consensus gross margin (CapIQ)</t>
-        </is>
-      </c>
-      <c r="C47" s="289">
-        <f>C46</f>
-        <v/>
-      </c>
-      <c r="D47" s="289">
-        <f>D46</f>
-        <v/>
-      </c>
-      <c r="E47" s="290">
-        <f>E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="326">
-        <f>'Key Stats'!F20</f>
-        <v/>
-      </c>
-      <c r="G47" s="326">
-        <f>'Key Stats'!G20</f>
-        <v/>
-      </c>
-      <c r="H47" s="326">
-        <f>'Key Stats'!H20</f>
-        <v/>
-      </c>
-      <c r="I47" s="291" t="n"/>
-      <c r="J47" s="291" t="n"/>
-    </row>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
     <row r="48" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1">
-      <c r="B49" s="327" t="inlineStr">
-        <is>
-          <t>Colour key: blue = hardcoded input, black = formula, green = link to another tab. Hover over cells with a red corner for sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="12.75" customHeight="1">
-      <c r="B50" s="327" t="inlineStr">
-        <is>
-          <t>Revenue = Software (customers x revenue per customer) + Services (microtransit/paratransit hours x $/hr, and network contract run-rate) + one-time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="12.75" customHeight="1">
-      <c r="B51" s="327" t="inlineStr">
-        <is>
-          <t>Thesis 1: network deals are bus-operator contracts priced at ~95-107% of the city's transit budget, so their gross margin is set at 20% (operator economics).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="327" t="inlineStr">
-        <is>
-          <t>Thesis 3: hours growth = expansion less budget-driven downsell; price per hour grows 2%/yr after FY26 because rebids reset price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="27.75" customHeight="1">
-      <c r="B53" s="327" t="inlineStr">
-        <is>
-          <t>Consensus: CapIQ (Key Stats tab) FY26-28E. FY29-30 have no consensus.</t>
-        </is>
-      </c>
-    </row>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52"/>
+    <row r="53" ht="27.75" customHeight="1"/>
     <row r="54" ht="27.75" customHeight="1"/>
     <row r="55" ht="27.75" customHeight="1"/>
     <row r="56" ht="27.75" customHeight="1"/>
@@ -4821,13 +4383,12 @@
     <row r="69"/>
     <row r="70"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="B50:J50"/>
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="B53:J53"/>
-    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B35:J35"/>
     <mergeCell ref="F2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4866,7 +4427,7 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="C3" s="328" t="inlineStr">
+      <c r="C3" s="315" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -4878,7 +4439,7 @@
           <t>Equity</t>
         </is>
       </c>
-      <c r="C4" s="329">
+      <c r="C4" s="316">
         <f>C17</f>
         <v/>
       </c>
@@ -4889,7 +4450,7 @@
           <t>% Debt</t>
         </is>
       </c>
-      <c r="C5" s="330" t="n">
+      <c r="C5" s="317" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4899,7 +4460,7 @@
           <t>% Equity</t>
         </is>
       </c>
-      <c r="C6" s="330" t="n">
+      <c r="C6" s="317" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="85" t="n"/>
@@ -4910,7 +4471,7 @@
           <t>Cost of Debt</t>
         </is>
       </c>
-      <c r="C7" s="331" t="inlineStr">
+      <c r="C7" s="318" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -4926,7 +4487,7 @@
           <t>After-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="C8" s="331" t="inlineStr">
+      <c r="C8" s="318" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -4940,7 +4501,7 @@
           <t>Cost of Equity</t>
         </is>
       </c>
-      <c r="C9" s="330">
+      <c r="C9" s="317">
         <f>C10+(C11*C12)</f>
         <v/>
       </c>
@@ -4985,7 +4546,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C13" s="332">
+      <c r="C13" s="319">
         <f>C9</f>
         <v/>
       </c>
@@ -4996,7 +4557,7 @@
           <t>Share Price ($)</t>
         </is>
       </c>
-      <c r="C15" s="333">
+      <c r="C15" s="320">
         <f>'Key Stats'!B50</f>
         <v/>
       </c>
@@ -5007,7 +4568,7 @@
           <t>Shares Oustanding (mm)</t>
         </is>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <f>'Key Stats'!B51</f>
         <v/>
       </c>
@@ -5018,7 +4579,7 @@
           <t>Market Cap (mm)</t>
         </is>
       </c>
-      <c r="C17" s="335">
+      <c r="C17" s="322">
         <f>C15*C16</f>
         <v/>
       </c>
@@ -5355,16 +4916,16 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="336" t="n">
+      <c r="B5" s="323" t="n">
         <v>248.854</v>
       </c>
-      <c r="C5" s="336" t="n">
+      <c r="C5" s="323" t="n">
         <v>337.63</v>
       </c>
-      <c r="D5" s="336" t="n">
+      <c r="D5" s="323" t="n">
         <v>434.337</v>
       </c>
-      <c r="E5" s="336" t="n">
+      <c r="E5" s="323" t="n">
         <v>491.703</v>
       </c>
       <c r="F5" s="196" t="n"/>
@@ -5376,22 +4937,22 @@
           <t>Other Revenue</t>
         </is>
       </c>
-      <c r="B6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="336" t="inlineStr">
+      <c r="B6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5405,16 +4966,16 @@
           <t xml:space="preserve">  Total Revenue</t>
         </is>
       </c>
-      <c r="B7" s="337" t="n">
+      <c r="B7" s="324" t="n">
         <v>248.854</v>
       </c>
-      <c r="C7" s="337" t="n">
+      <c r="C7" s="324" t="n">
         <v>337.63</v>
       </c>
-      <c r="D7" s="337" t="n">
+      <c r="D7" s="324" t="n">
         <v>434.337</v>
       </c>
-      <c r="E7" s="337" t="n">
+      <c r="E7" s="324" t="n">
         <v>491.703</v>
       </c>
       <c r="F7" s="196" t="n"/>
@@ -5435,16 +4996,16 @@
           <t>Cost Of Goods Sold</t>
         </is>
       </c>
-      <c r="B9" s="336" t="n">
+      <c r="B9" s="323" t="n">
         <v>149.446</v>
       </c>
-      <c r="C9" s="336" t="n">
+      <c r="C9" s="323" t="n">
         <v>206.79</v>
       </c>
-      <c r="D9" s="336" t="n">
+      <c r="D9" s="323" t="n">
         <v>262.534</v>
       </c>
-      <c r="E9" s="336" t="n">
+      <c r="E9" s="323" t="n">
         <v>296</v>
       </c>
       <c r="F9" s="196" t="n"/>
@@ -5456,16 +5017,16 @@
           <t xml:space="preserve">  Gross Profit</t>
         </is>
       </c>
-      <c r="B10" s="337" t="n">
+      <c r="B10" s="324" t="n">
         <v>99.408</v>
       </c>
-      <c r="C10" s="337" t="n">
+      <c r="C10" s="324" t="n">
         <v>130.84</v>
       </c>
-      <c r="D10" s="337" t="n">
+      <c r="D10" s="324" t="n">
         <v>171.803</v>
       </c>
-      <c r="E10" s="337" t="n">
+      <c r="E10" s="324" t="n">
         <v>195.703</v>
       </c>
       <c r="F10" s="196" t="n"/>
@@ -5486,16 +5047,16 @@
           <t>Selling General &amp; Admin Exp.</t>
         </is>
       </c>
-      <c r="B12" s="336" t="n">
+      <c r="B12" s="323" t="n">
         <v>118.03</v>
       </c>
-      <c r="C12" s="336" t="n">
+      <c r="C12" s="323" t="n">
         <v>125.749</v>
       </c>
-      <c r="D12" s="336" t="n">
+      <c r="D12" s="323" t="n">
         <v>155.205</v>
       </c>
-      <c r="E12" s="336" t="n">
+      <c r="E12" s="323" t="n">
         <v>184.556</v>
       </c>
       <c r="F12" s="196" t="n"/>
@@ -5507,16 +5068,16 @@
           <t>R &amp; D Exp.</t>
         </is>
       </c>
-      <c r="B13" s="336" t="n">
+      <c r="B13" s="323" t="n">
         <v>95.833</v>
       </c>
-      <c r="C13" s="336" t="n">
+      <c r="C13" s="323" t="n">
         <v>88.98699999999999</v>
       </c>
-      <c r="D13" s="336" t="n">
+      <c r="D13" s="323" t="n">
         <v>92.303</v>
       </c>
-      <c r="E13" s="336" t="n">
+      <c r="E13" s="323" t="n">
         <v>98.85599999999999</v>
       </c>
       <c r="F13" s="196" t="n"/>
@@ -5528,22 +5089,22 @@
           <t>Depreciation &amp; Amort.</t>
         </is>
       </c>
-      <c r="B14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="336" t="inlineStr">
+      <c r="B14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5804,20 +5365,20 @@
           <t>Other Operating Expense/(Income)</t>
         </is>
       </c>
-      <c r="B15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="336" t="n">
+      <c r="B15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="323" t="n">
         <v>0.911</v>
       </c>
-      <c r="E15" s="336" t="n">
+      <c r="E15" s="323" t="n">
         <v>0.911</v>
       </c>
       <c r="F15" s="196" t="n"/>
@@ -5838,16 +5399,16 @@
           <t xml:space="preserve">  Other Operating Exp., Total</t>
         </is>
       </c>
-      <c r="B17" s="337" t="n">
+      <c r="B17" s="324" t="n">
         <v>213.863</v>
       </c>
-      <c r="C17" s="337" t="n">
+      <c r="C17" s="324" t="n">
         <v>214.736</v>
       </c>
-      <c r="D17" s="337" t="n">
+      <c r="D17" s="324" t="n">
         <v>248.419</v>
       </c>
-      <c r="E17" s="337" t="n">
+      <c r="E17" s="324" t="n">
         <v>284.323</v>
       </c>
       <c r="F17" s="196" t="n"/>
@@ -5868,16 +5429,16 @@
           <t xml:space="preserve">  Operating Income</t>
         </is>
       </c>
-      <c r="B19" s="338" t="n">
+      <c r="B19" s="325" t="n">
         <v>-114.5</v>
       </c>
-      <c r="C19" s="338" t="n">
+      <c r="C19" s="325" t="n">
         <v>-83.90000000000001</v>
       </c>
-      <c r="D19" s="338" t="n">
+      <c r="D19" s="325" t="n">
         <v>-76.59999999999999</v>
       </c>
-      <c r="E19" s="338" t="n">
+      <c r="E19" s="325" t="n">
         <v>-88.59999999999999</v>
       </c>
       <c r="F19" s="196" t="n"/>
@@ -5898,16 +5459,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B21" s="336" t="n">
+      <c r="B21" s="323" t="n">
         <v>-0.7</v>
       </c>
-      <c r="C21" s="336" t="n">
+      <c r="C21" s="323" t="n">
         <v>-4.3</v>
       </c>
-      <c r="D21" s="336" t="n">
+      <c r="D21" s="323" t="n">
         <v>-7.3</v>
       </c>
-      <c r="E21" s="336" t="n">
+      <c r="E21" s="323" t="n">
         <v>-3</v>
       </c>
       <c r="F21" s="196" t="n"/>
@@ -5919,16 +5480,16 @@
           <t>Interest and Invest. Income</t>
         </is>
       </c>
-      <c r="B22" s="336" t="n">
+      <c r="B22" s="323" t="n">
         <v>3.599</v>
       </c>
-      <c r="C22" s="336" t="n">
+      <c r="C22" s="323" t="n">
         <v>2.195</v>
       </c>
-      <c r="D22" s="336" t="n">
+      <c r="D22" s="323" t="n">
         <v>5.272</v>
       </c>
-      <c r="E22" s="336" t="n">
+      <c r="E22" s="323" t="n">
         <v>9.795999999999999</v>
       </c>
       <c r="F22" s="196" t="n"/>
@@ -5940,16 +5501,16 @@
           <t xml:space="preserve">  Net Interest Exp.</t>
         </is>
       </c>
-      <c r="B23" s="337" t="n">
+      <c r="B23" s="324" t="n">
         <v>2.946</v>
       </c>
-      <c r="C23" s="337" t="n">
+      <c r="C23" s="324" t="n">
         <v>-2.1</v>
       </c>
-      <c r="D23" s="337" t="n">
+      <c r="D23" s="324" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E23" s="337" t="n">
+      <c r="E23" s="324" t="n">
         <v>6.767</v>
       </c>
       <c r="F23" s="196" t="n"/>
@@ -5970,16 +5531,16 @@
           <t>Currency Exchange Gains (Loss)</t>
         </is>
       </c>
-      <c r="B25" s="336" t="n">
+      <c r="B25" s="323" t="n">
         <v>-1.5</v>
       </c>
-      <c r="C25" s="336" t="n">
+      <c r="C25" s="323" t="n">
         <v>0.326</v>
       </c>
-      <c r="D25" s="336" t="n">
+      <c r="D25" s="323" t="n">
         <v>0.475</v>
       </c>
-      <c r="E25" s="336" t="n">
+      <c r="E25" s="323" t="n">
         <v>-1.3</v>
       </c>
       <c r="F25" s="196" t="n"/>
@@ -5991,16 +5552,16 @@
           <t>Other Non-Operating Inc. (Exp.)</t>
         </is>
       </c>
-      <c r="B26" s="336" t="n">
+      <c r="B26" s="323" t="n">
         <v>-2.1</v>
       </c>
-      <c r="C26" s="336" t="n">
+      <c r="C26" s="323" t="n">
         <v>-4.9</v>
       </c>
-      <c r="D26" s="336" t="n">
+      <c r="D26" s="323" t="n">
         <v>-7.2</v>
       </c>
-      <c r="E26" s="336" t="n">
+      <c r="E26" s="323" t="n">
         <v>-5.2</v>
       </c>
       <c r="F26" s="196" t="n"/>
@@ -6012,16 +5573,16 @@
           <t xml:space="preserve">  EBT Excl. Unusual Items</t>
         </is>
       </c>
-      <c r="B27" s="337" t="n">
+      <c r="B27" s="324" t="n">
         <v>-115.1</v>
       </c>
-      <c r="C27" s="337" t="n">
+      <c r="C27" s="324" t="n">
         <v>-90.5</v>
       </c>
-      <c r="D27" s="337" t="n">
+      <c r="D27" s="324" t="n">
         <v>-85.40000000000001</v>
       </c>
-      <c r="E27" s="337" t="n">
+      <c r="E27" s="324" t="n">
         <v>-88.40000000000001</v>
       </c>
       <c r="F27" s="196" t="n"/>
@@ -6042,22 +5603,22 @@
           <t>Impairment of Goodwill</t>
         </is>
       </c>
-      <c r="B29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="336" t="inlineStr">
+      <c r="B29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6071,18 +5632,18 @@
           <t>Other Unusual Items</t>
         </is>
       </c>
-      <c r="B30" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="336" t="n">
+      <c r="B30" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="323" t="n">
         <v>1.857</v>
       </c>
-      <c r="D30" s="336" t="n">
+      <c r="D30" s="323" t="n">
         <v>-8.5</v>
       </c>
-      <c r="E30" s="336" t="n">
+      <c r="E30" s="323" t="n">
         <v>-8.5</v>
       </c>
       <c r="F30" s="196" t="n"/>
@@ -6094,16 +5655,16 @@
           <t xml:space="preserve">  EBT Incl. Unusual Items</t>
         </is>
       </c>
-      <c r="B31" s="337" t="n">
+      <c r="B31" s="324" t="n">
         <v>-115.1</v>
       </c>
-      <c r="C31" s="337" t="n">
+      <c r="C31" s="324" t="n">
         <v>-88.7</v>
       </c>
-      <c r="D31" s="337" t="n">
+      <c r="D31" s="324" t="n">
         <v>-93.8</v>
       </c>
-      <c r="E31" s="337" t="n">
+      <c r="E31" s="324" t="n">
         <v>-96.90000000000001</v>
       </c>
       <c r="F31" s="196" t="n"/>
@@ -6124,16 +5685,16 @@
           <t>Income Tax Expense</t>
         </is>
       </c>
-      <c r="B33" s="336" t="n">
+      <c r="B33" s="323" t="n">
         <v>1.815</v>
       </c>
-      <c r="C33" s="336" t="n">
+      <c r="C33" s="323" t="n">
         <v>1.89</v>
       </c>
-      <c r="D33" s="336" t="n">
+      <c r="D33" s="323" t="n">
         <v>2.521</v>
       </c>
-      <c r="E33" s="336" t="n">
+      <c r="E33" s="323" t="n">
         <v>1.599</v>
       </c>
       <c r="F33" s="196" t="n"/>
@@ -6145,16 +5706,16 @@
           <t xml:space="preserve">  Earnings from Cont. Ops.</t>
         </is>
       </c>
-      <c r="B34" s="337" t="n">
+      <c r="B34" s="324" t="n">
         <v>-117</v>
       </c>
-      <c r="C34" s="337" t="n">
+      <c r="C34" s="324" t="n">
         <v>-90.59999999999999</v>
       </c>
-      <c r="D34" s="337" t="n">
+      <c r="D34" s="324" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E34" s="337" t="n">
+      <c r="E34" s="324" t="n">
         <v>-98.5</v>
       </c>
       <c r="F34" s="196" t="n"/>
@@ -6175,22 +5736,22 @@
           <t>Earnings of Discontinued Ops.</t>
         </is>
       </c>
-      <c r="B36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="336" t="inlineStr">
+      <c r="B36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6204,22 +5765,22 @@
           <t>Extraord. Item &amp; Account. Change</t>
         </is>
       </c>
-      <c r="B37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="336" t="inlineStr">
+      <c r="B37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6233,16 +5794,16 @@
           <t xml:space="preserve">  Net Income to Company</t>
         </is>
       </c>
-      <c r="B38" s="337" t="n">
+      <c r="B38" s="324" t="n">
         <v>-117</v>
       </c>
-      <c r="C38" s="337" t="n">
+      <c r="C38" s="324" t="n">
         <v>-90.59999999999999</v>
       </c>
-      <c r="D38" s="337" t="n">
+      <c r="D38" s="324" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E38" s="337" t="n">
+      <c r="E38" s="324" t="n">
         <v>-98.5</v>
       </c>
       <c r="F38" s="196" t="n"/>
@@ -6263,18 +5824,18 @@
           <t>Minority Int. in Earnings</t>
         </is>
       </c>
-      <c r="B40" s="336" t="n">
+      <c r="B40" s="323" t="n">
         <v>0.278</v>
       </c>
-      <c r="C40" s="336" t="n">
+      <c r="C40" s="323" t="n">
         <v>0.271</v>
       </c>
-      <c r="D40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="336" t="inlineStr">
+      <c r="D40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6288,16 +5849,16 @@
           <t xml:space="preserve">  Net Income</t>
         </is>
       </c>
-      <c r="B41" s="339" t="n">
+      <c r="B41" s="326" t="n">
         <v>-116.7</v>
       </c>
-      <c r="C41" s="339" t="n">
+      <c r="C41" s="326" t="n">
         <v>-90.3</v>
       </c>
-      <c r="D41" s="339" t="n">
+      <c r="D41" s="326" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E41" s="339" t="n">
+      <c r="E41" s="326" t="n">
         <v>-98.5</v>
       </c>
       <c r="F41" s="196" t="n"/>
@@ -6318,22 +5879,22 @@
           <t>Pref. Dividends and Other Adj.</t>
         </is>
       </c>
-      <c r="B43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="336" t="inlineStr">
+      <c r="B43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6356,16 +5917,16 @@
           <t xml:space="preserve">  NI to Common Incl Extra Items</t>
         </is>
       </c>
-      <c r="B45" s="338" t="n">
+      <c r="B45" s="325" t="n">
         <v>-116.7</v>
       </c>
-      <c r="C45" s="338" t="n">
+      <c r="C45" s="325" t="n">
         <v>-90.3</v>
       </c>
-      <c r="D45" s="338" t="n">
+      <c r="D45" s="325" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E45" s="338" t="n">
+      <c r="E45" s="325" t="n">
         <v>-98.5</v>
       </c>
       <c r="F45" s="196" t="n"/>
@@ -6377,16 +5938,16 @@
           <t xml:space="preserve">  NI to Common Excl. Extra Items</t>
         </is>
       </c>
-      <c r="B46" s="338" t="n">
+      <c r="B46" s="325" t="n">
         <v>-116.7</v>
       </c>
-      <c r="C46" s="338" t="n">
+      <c r="C46" s="325" t="n">
         <v>-90.3</v>
       </c>
-      <c r="D46" s="338" t="n">
+      <c r="D46" s="325" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E46" s="338" t="n">
+      <c r="E46" s="325" t="n">
         <v>-98.5</v>
       </c>
       <c r="F46" s="196" t="n"/>
@@ -6420,16 +5981,16 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B49" s="340" t="n">
+      <c r="B49" s="327" t="n">
         <v>-9.6</v>
       </c>
-      <c r="C49" s="340" t="n">
+      <c r="C49" s="327" t="n">
         <v>-7.21</v>
       </c>
-      <c r="D49" s="340" t="n">
+      <c r="D49" s="327" t="n">
         <v>-2.92</v>
       </c>
-      <c r="E49" s="340" t="n">
+      <c r="E49" s="327" t="n">
         <v>-1.47</v>
       </c>
       <c r="F49" s="196" t="n"/>
@@ -6441,16 +6002,16 @@
           <t>Basic EPS Excl. Extra Items</t>
         </is>
       </c>
-      <c r="B50" s="341" t="n">
+      <c r="B50" s="328" t="n">
         <v>-9.6</v>
       </c>
-      <c r="C50" s="341" t="n">
+      <c r="C50" s="328" t="n">
         <v>-7.21</v>
       </c>
-      <c r="D50" s="341" t="n">
+      <c r="D50" s="328" t="n">
         <v>-2.92</v>
       </c>
-      <c r="E50" s="341" t="n">
+      <c r="E50" s="328" t="n">
         <v>-1.47</v>
       </c>
       <c r="F50" s="196" t="n"/>
@@ -6462,16 +6023,16 @@
           <t>Weighted Avg. Basic Shares Out.</t>
         </is>
       </c>
-      <c r="B51" s="336" t="n">
+      <c r="B51" s="323" t="n">
         <v>12.15567</v>
       </c>
-      <c r="C51" s="336" t="n">
+      <c r="C51" s="323" t="n">
         <v>12.525706</v>
       </c>
-      <c r="D51" s="336" t="n">
+      <c r="D51" s="323" t="n">
         <v>32.949511</v>
       </c>
-      <c r="E51" s="336" t="n">
+      <c r="E51" s="323" t="n">
         <v>67.181601</v>
       </c>
       <c r="F51" s="196" t="n"/>
@@ -6492,16 +6053,16 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B53" s="340" t="n">
+      <c r="B53" s="327" t="n">
         <v>-9.6</v>
       </c>
-      <c r="C53" s="340" t="n">
+      <c r="C53" s="327" t="n">
         <v>-7.21</v>
       </c>
-      <c r="D53" s="340" t="n">
+      <c r="D53" s="327" t="n">
         <v>-2.92</v>
       </c>
-      <c r="E53" s="340" t="n">
+      <c r="E53" s="327" t="n">
         <v>-1.47</v>
       </c>
       <c r="F53" s="196" t="n"/>
@@ -6513,16 +6074,16 @@
           <t>Diluted EPS Excl. Extra Items</t>
         </is>
       </c>
-      <c r="B54" s="341" t="n">
+      <c r="B54" s="328" t="n">
         <v>-9.6</v>
       </c>
-      <c r="C54" s="341" t="n">
+      <c r="C54" s="328" t="n">
         <v>-7.21</v>
       </c>
-      <c r="D54" s="341" t="n">
+      <c r="D54" s="328" t="n">
         <v>-2.92</v>
       </c>
-      <c r="E54" s="341" t="n">
+      <c r="E54" s="328" t="n">
         <v>-1.47</v>
       </c>
       <c r="F54" s="196" t="n"/>
@@ -6534,16 +6095,16 @@
           <t>Weighted Avg. Diluted Shares Out.</t>
         </is>
       </c>
-      <c r="B55" s="336" t="n">
+      <c r="B55" s="323" t="n">
         <v>12.15567</v>
       </c>
-      <c r="C55" s="336" t="n">
+      <c r="C55" s="323" t="n">
         <v>12.525706</v>
       </c>
-      <c r="D55" s="336" t="n">
+      <c r="D55" s="323" t="n">
         <v>32.949511</v>
       </c>
-      <c r="E55" s="336" t="n">
+      <c r="E55" s="323" t="n">
         <v>67.181601</v>
       </c>
       <c r="F55" s="196" t="n"/>
@@ -6564,16 +6125,16 @@
           <t>Normalized Basic EPS</t>
         </is>
       </c>
-      <c r="B57" s="340" t="n">
+      <c r="B57" s="327" t="n">
         <v>-5.9</v>
       </c>
-      <c r="C57" s="340" t="n">
+      <c r="C57" s="327" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D57" s="340" t="n">
+      <c r="D57" s="327" t="n">
         <v>-1.62</v>
       </c>
-      <c r="E57" s="340" t="n">
+      <c r="E57" s="327" t="n">
         <v>-0.82</v>
       </c>
       <c r="F57" s="196" t="n"/>
@@ -6585,16 +6146,16 @@
           <t>Normalized Diluted EPS</t>
         </is>
       </c>
-      <c r="B58" s="341" t="n">
+      <c r="B58" s="328" t="n">
         <v>-5.9</v>
       </c>
-      <c r="C58" s="341" t="n">
+      <c r="C58" s="328" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D58" s="341" t="n">
+      <c r="D58" s="328" t="n">
         <v>-1.62</v>
       </c>
-      <c r="E58" s="341" t="n">
+      <c r="E58" s="328" t="n">
         <v>-0.82</v>
       </c>
       <c r="F58" s="196" t="n"/>
@@ -6615,22 +6176,22 @@
           <t>Dividends per Share</t>
         </is>
       </c>
-      <c r="B60" s="341" t="inlineStr">
+      <c r="B60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C60" s="341" t="inlineStr">
+      <c r="C60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D60" s="341" t="inlineStr">
+      <c r="D60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E60" s="341" t="inlineStr">
+      <c r="E60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6666,16 +6227,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B63" s="336" t="n">
+      <c r="B63" s="323" t="n">
         <v>-106.4</v>
       </c>
-      <c r="C63" s="336" t="n">
+      <c r="C63" s="323" t="n">
         <v>-74.8</v>
       </c>
-      <c r="D63" s="336" t="n">
+      <c r="D63" s="323" t="n">
         <v>-68.09999999999999</v>
       </c>
-      <c r="E63" s="336" t="n">
+      <c r="E63" s="323" t="n">
         <v>-79.7</v>
       </c>
       <c r="F63" s="196" t="n"/>
@@ -6687,16 +6248,16 @@
           <t>EBITA</t>
         </is>
       </c>
-      <c r="B64" s="336" t="n">
+      <c r="B64" s="323" t="n">
         <v>-109.5</v>
       </c>
-      <c r="C64" s="336" t="n">
+      <c r="C64" s="323" t="n">
         <v>-78.3</v>
       </c>
-      <c r="D64" s="336" t="n">
+      <c r="D64" s="323" t="n">
         <v>-72</v>
       </c>
-      <c r="E64" s="336" t="n">
+      <c r="E64" s="323" t="n">
         <v>-83.59999999999999</v>
       </c>
       <c r="F64" s="196" t="n"/>
@@ -6708,16 +6269,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B65" s="336" t="n">
+      <c r="B65" s="323" t="n">
         <v>-114.5</v>
       </c>
-      <c r="C65" s="336" t="n">
+      <c r="C65" s="323" t="n">
         <v>-83.90000000000001</v>
       </c>
-      <c r="D65" s="336" t="n">
+      <c r="D65" s="323" t="n">
         <v>-76.59999999999999</v>
       </c>
-      <c r="E65" s="336" t="n">
+      <c r="E65" s="323" t="n">
         <v>-88.59999999999999</v>
       </c>
       <c r="F65" s="196" t="n"/>
@@ -6729,16 +6290,16 @@
           <t>EBITDAR</t>
         </is>
       </c>
-      <c r="B66" s="336" t="n">
+      <c r="B66" s="323" t="n">
         <v>-100.1</v>
       </c>
-      <c r="C66" s="336" t="n">
+      <c r="C66" s="323" t="n">
         <v>-65.90000000000001</v>
       </c>
-      <c r="D66" s="336" t="n">
+      <c r="D66" s="323" t="n">
         <v>-56.7</v>
       </c>
-      <c r="E66" s="336" t="inlineStr">
+      <c r="E66" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6752,22 +6313,22 @@
           <t>Effective Tax Rate %</t>
         </is>
       </c>
-      <c r="B67" s="342" t="inlineStr">
+      <c r="B67" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="C67" s="342" t="inlineStr">
+      <c r="C67" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="D67" s="342" t="inlineStr">
+      <c r="D67" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="E67" s="342" t="inlineStr">
+      <c r="E67" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
@@ -6781,16 +6342,16 @@
           <t>Current Domestic Taxes</t>
         </is>
       </c>
-      <c r="B68" s="336" t="n">
+      <c r="B68" s="323" t="n">
         <v>0.148</v>
       </c>
-      <c r="C68" s="336" t="n">
+      <c r="C68" s="323" t="n">
         <v>0.169</v>
       </c>
-      <c r="D68" s="336" t="n">
+      <c r="D68" s="323" t="n">
         <v>0.243</v>
       </c>
-      <c r="E68" s="336" t="n">
+      <c r="E68" s="323" t="n">
         <v>0.243</v>
       </c>
       <c r="F68" s="196" t="n"/>
@@ -6802,16 +6363,16 @@
           <t>Current Foreign Taxes</t>
         </is>
       </c>
-      <c r="B69" s="336" t="n">
+      <c r="B69" s="323" t="n">
         <v>1.5</v>
       </c>
-      <c r="C69" s="336" t="n">
+      <c r="C69" s="323" t="n">
         <v>1.499</v>
       </c>
-      <c r="D69" s="336" t="n">
+      <c r="D69" s="323" t="n">
         <v>1.685</v>
       </c>
-      <c r="E69" s="336" t="n">
+      <c r="E69" s="323" t="n">
         <v>1.685</v>
       </c>
       <c r="F69" s="196" t="n"/>
@@ -6823,16 +6384,16 @@
           <t>Total Current Taxes</t>
         </is>
       </c>
-      <c r="B70" s="336" t="n">
+      <c r="B70" s="323" t="n">
         <v>1.648</v>
       </c>
-      <c r="C70" s="336" t="n">
+      <c r="C70" s="323" t="n">
         <v>1.668</v>
       </c>
-      <c r="D70" s="336" t="n">
+      <c r="D70" s="323" t="n">
         <v>1.928</v>
       </c>
-      <c r="E70" s="336" t="n">
+      <c r="E70" s="323" t="n">
         <v>1.928</v>
       </c>
       <c r="F70" s="196" t="n"/>
@@ -6844,16 +6405,16 @@
           <t>Deferred Foreign Taxes</t>
         </is>
       </c>
-      <c r="B71" s="336" t="n">
+      <c r="B71" s="323" t="n">
         <v>0.167</v>
       </c>
-      <c r="C71" s="336" t="n">
+      <c r="C71" s="323" t="n">
         <v>0.222</v>
       </c>
-      <c r="D71" s="336" t="n">
+      <c r="D71" s="323" t="n">
         <v>0.593</v>
       </c>
-      <c r="E71" s="336" t="n">
+      <c r="E71" s="323" t="n">
         <v>0.593</v>
       </c>
       <c r="F71" s="196" t="n"/>
@@ -6865,16 +6426,16 @@
           <t>Total Deferred Taxes</t>
         </is>
       </c>
-      <c r="B72" s="336" t="n">
+      <c r="B72" s="323" t="n">
         <v>0.167</v>
       </c>
-      <c r="C72" s="336" t="n">
+      <c r="C72" s="323" t="n">
         <v>0.222</v>
       </c>
-      <c r="D72" s="336" t="n">
+      <c r="D72" s="323" t="n">
         <v>0.593</v>
       </c>
-      <c r="E72" s="336" t="n">
+      <c r="E72" s="323" t="n">
         <v>0.593</v>
       </c>
       <c r="F72" s="196" t="n"/>
@@ -6895,16 +6456,16 @@
           <t>Normalized Net Income</t>
         </is>
       </c>
-      <c r="B74" s="336" t="n">
+      <c r="B74" s="323" t="n">
         <v>-71.7</v>
       </c>
-      <c r="C74" s="336" t="n">
+      <c r="C74" s="323" t="n">
         <v>-56.3</v>
       </c>
-      <c r="D74" s="336" t="n">
+      <c r="D74" s="323" t="n">
         <v>-53.4</v>
       </c>
-      <c r="E74" s="336" t="n">
+      <c r="E74" s="323" t="n">
         <v>-55.3</v>
       </c>
       <c r="F74" s="196" t="n"/>
@@ -6916,18 +6477,18 @@
           <t>Interest on Long Term Debt</t>
         </is>
       </c>
-      <c r="B75" s="336" t="inlineStr">
+      <c r="B75" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C75" s="336" t="n">
+      <c r="C75" s="323" t="n">
         <v>3.2</v>
       </c>
-      <c r="D75" s="336" t="n">
+      <c r="D75" s="323" t="n">
         <v>4.6</v>
       </c>
-      <c r="E75" s="336" t="inlineStr">
+      <c r="E75" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6941,16 +6502,16 @@
           <t>Filing Date</t>
         </is>
       </c>
-      <c r="B76" s="343" t="n">
+      <c r="B76" s="330" t="n">
         <v>46087</v>
       </c>
-      <c r="C76" s="343" t="n">
+      <c r="C76" s="330" t="n">
         <v>46087</v>
       </c>
-      <c r="D76" s="343" t="n">
+      <c r="D76" s="330" t="n">
         <v>46087</v>
       </c>
-      <c r="E76" s="343" t="n">
+      <c r="E76" s="330" t="n">
         <v>46240</v>
       </c>
       <c r="F76" s="196" t="n"/>
@@ -7042,16 +6603,16 @@
           <t>Advertising Exp.</t>
         </is>
       </c>
-      <c r="B81" s="336" t="n">
+      <c r="B81" s="323" t="n">
         <v>4.6</v>
       </c>
-      <c r="C81" s="336" t="n">
+      <c r="C81" s="323" t="n">
         <v>5.2</v>
       </c>
-      <c r="D81" s="336" t="n">
+      <c r="D81" s="323" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E81" s="336" t="inlineStr">
+      <c r="E81" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7065,16 +6626,16 @@
           <t>Selling and Marketing Exp.</t>
         </is>
       </c>
-      <c r="B82" s="336" t="n">
+      <c r="B82" s="323" t="n">
         <v>53.799</v>
       </c>
-      <c r="C82" s="336" t="n">
+      <c r="C82" s="323" t="n">
         <v>55.484</v>
       </c>
-      <c r="D82" s="336" t="n">
+      <c r="D82" s="323" t="n">
         <v>67.20399999999999</v>
       </c>
-      <c r="E82" s="336" t="n">
+      <c r="E82" s="323" t="n">
         <v>77.661</v>
       </c>
       <c r="F82" s="196" t="n"/>
@@ -7086,16 +6647,16 @@
           <t>General and Administrative Exp.</t>
         </is>
       </c>
-      <c r="B83" s="336" t="n">
+      <c r="B83" s="323" t="n">
         <v>64.23099999999999</v>
       </c>
-      <c r="C83" s="336" t="n">
+      <c r="C83" s="323" t="n">
         <v>70.265</v>
       </c>
-      <c r="D83" s="336" t="n">
+      <c r="D83" s="323" t="n">
         <v>88.001</v>
       </c>
-      <c r="E83" s="336" t="n">
+      <c r="E83" s="323" t="n">
         <v>106.895</v>
       </c>
       <c r="F83" s="196" t="n"/>
@@ -7107,16 +6668,16 @@
           <t>R&amp;D Exp.</t>
         </is>
       </c>
-      <c r="B84" s="336" t="n">
+      <c r="B84" s="323" t="n">
         <v>95.833</v>
       </c>
-      <c r="C84" s="336" t="n">
+      <c r="C84" s="323" t="n">
         <v>88.98699999999999</v>
       </c>
-      <c r="D84" s="336" t="n">
+      <c r="D84" s="323" t="n">
         <v>92.352</v>
       </c>
-      <c r="E84" s="336" t="n">
+      <c r="E84" s="323" t="n">
         <v>98.905</v>
       </c>
       <c r="F84" s="196" t="n"/>
@@ -7128,16 +6689,16 @@
           <t>Net Rental Exp.</t>
         </is>
       </c>
-      <c r="B85" s="336" t="n">
+      <c r="B85" s="323" t="n">
         <v>6.316</v>
       </c>
-      <c r="C85" s="336" t="n">
+      <c r="C85" s="323" t="n">
         <v>8.866</v>
       </c>
-      <c r="D85" s="336" t="n">
+      <c r="D85" s="323" t="n">
         <v>11.386</v>
       </c>
-      <c r="E85" s="336" t="inlineStr">
+      <c r="E85" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7151,18 +6712,18 @@
           <t>Imputed Oper. Lease Interest Exp.</t>
         </is>
       </c>
-      <c r="B86" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="336" t="n">
+      <c r="B86" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="323" t="n">
         <v>6.060656</v>
       </c>
-      <c r="D86" s="336" t="n">
+      <c r="D86" s="323" t="n">
         <v>13.149282</v>
       </c>
-      <c r="E86" s="336" t="inlineStr">
+      <c r="E86" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7176,18 +6737,18 @@
           <t>Imputed Oper. Lease Depreciation</t>
         </is>
       </c>
-      <c r="B87" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="336" t="n">
+      <c r="B87" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" s="323" t="n">
         <v>2.805344</v>
       </c>
-      <c r="D87" s="336" t="n">
+      <c r="D87" s="323" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E87" s="336" t="inlineStr">
+      <c r="E87" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7210,16 +6771,16 @@
           <t>Stock-Based Comp., COGS</t>
         </is>
       </c>
-      <c r="B89" s="336" t="n">
+      <c r="B89" s="323" t="n">
         <v>0.185</v>
       </c>
-      <c r="C89" s="336" t="n">
+      <c r="C89" s="323" t="n">
         <v>0.227</v>
       </c>
-      <c r="D89" s="336" t="n">
+      <c r="D89" s="323" t="n">
         <v>0.2</v>
       </c>
-      <c r="E89" s="336" t="n">
+      <c r="E89" s="323" t="n">
         <v>0.267</v>
       </c>
       <c r="F89" s="196" t="n"/>
@@ -7231,16 +6792,16 @@
           <t>Stock-Based Comp., R&amp;D Exp.</t>
         </is>
       </c>
-      <c r="B90" s="336" t="n">
+      <c r="B90" s="323" t="n">
         <v>4.959</v>
       </c>
-      <c r="C90" s="336" t="n">
+      <c r="C90" s="323" t="n">
         <v>6.583</v>
       </c>
-      <c r="D90" s="336" t="n">
+      <c r="D90" s="323" t="n">
         <v>8.577</v>
       </c>
-      <c r="E90" s="336" t="n">
+      <c r="E90" s="323" t="n">
         <v>13.746</v>
       </c>
       <c r="F90" s="196" t="n"/>
@@ -7252,16 +6813,16 @@
           <t>Stock-Based Comp., S&amp;M Exp.</t>
         </is>
       </c>
-      <c r="B91" s="336" t="n">
+      <c r="B91" s="323" t="n">
         <v>3.134</v>
       </c>
-      <c r="C91" s="336" t="n">
+      <c r="C91" s="323" t="n">
         <v>4.023</v>
       </c>
-      <c r="D91" s="336" t="n">
+      <c r="D91" s="323" t="n">
         <v>7.121</v>
       </c>
-      <c r="E91" s="336" t="n">
+      <c r="E91" s="323" t="n">
         <v>11.533</v>
       </c>
       <c r="F91" s="196" t="n"/>
@@ -7273,16 +6834,16 @@
           <t>Stock-Based Comp., G&amp;A Exp.</t>
         </is>
       </c>
-      <c r="B92" s="336" t="n">
+      <c r="B92" s="323" t="n">
         <v>4.848</v>
       </c>
-      <c r="C92" s="336" t="n">
+      <c r="C92" s="323" t="n">
         <v>10.393</v>
       </c>
-      <c r="D92" s="336" t="n">
+      <c r="D92" s="323" t="n">
         <v>14.443</v>
       </c>
-      <c r="E92" s="336" t="n">
+      <c r="E92" s="323" t="n">
         <v>27.016</v>
       </c>
       <c r="F92" s="196" t="n"/>
@@ -7294,16 +6855,16 @@
           <t xml:space="preserve">  Stock-Based Comp., Total</t>
         </is>
       </c>
-      <c r="B93" s="338" t="n">
+      <c r="B93" s="325" t="n">
         <v>13.126</v>
       </c>
-      <c r="C93" s="338" t="n">
+      <c r="C93" s="325" t="n">
         <v>21.226</v>
       </c>
-      <c r="D93" s="338" t="n">
+      <c r="D93" s="325" t="n">
         <v>30.341</v>
       </c>
-      <c r="E93" s="338" t="n">
+      <c r="E93" s="325" t="n">
         <v>52.562</v>
       </c>
       <c r="F93" s="196" t="n"/>
@@ -8100,25 +7661,25 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B16" s="344" t="n">
+      <c r="B16" s="331" t="n">
         <v>248.854</v>
       </c>
-      <c r="C16" s="344" t="n">
+      <c r="C16" s="331" t="n">
         <v>337.63</v>
       </c>
-      <c r="D16" s="344" t="n">
+      <c r="D16" s="331" t="n">
         <v>434.337</v>
       </c>
-      <c r="E16" s="344" t="n">
+      <c r="E16" s="331" t="n">
         <v>491.703</v>
       </c>
-      <c r="F16" s="345" t="n">
+      <c r="F16" s="332" t="n">
         <v>551.73774</v>
       </c>
-      <c r="G16" s="345" t="n">
+      <c r="G16" s="332" t="n">
         <v>674.03932</v>
       </c>
-      <c r="H16" s="345" t="n">
+      <c r="H16" s="332" t="n">
         <v>814.01794</v>
       </c>
     </row>
@@ -8133,22 +7694,22 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="C17" s="346" t="n">
+      <c r="C17" s="333" t="n">
         <v>0.356739</v>
       </c>
-      <c r="D17" s="346" t="n">
+      <c r="D17" s="333" t="n">
         <v>0.286428</v>
       </c>
-      <c r="E17" s="346" t="n">
+      <c r="E17" s="333" t="n">
         <v>0.291328</v>
       </c>
-      <c r="F17" s="347" t="n">
+      <c r="F17" s="334" t="n">
         <v>0.27029873117</v>
       </c>
-      <c r="G17" s="347" t="n">
+      <c r="G17" s="334" t="n">
         <v>0.221666148848</v>
       </c>
-      <c r="H17" s="347" t="n">
+      <c r="H17" s="334" t="n">
         <v>0.207671297277</v>
       </c>
     </row>
@@ -8168,29 +7729,29 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B19" s="344" t="n">
+      <c r="B19" s="331" t="n">
         <v>99.408</v>
       </c>
-      <c r="C19" s="344" t="n">
+      <c r="C19" s="331" t="n">
         <v>130.84</v>
       </c>
-      <c r="D19" s="344" t="n">
+      <c r="D19" s="331" t="n">
         <v>171.803</v>
       </c>
-      <c r="E19" s="344" t="n">
+      <c r="E19" s="331" t="n">
         <v>195.703</v>
       </c>
-      <c r="F19" s="344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="344" t="inlineStr">
+      <c r="F19" s="331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8202,25 +7763,25 @@
           <t xml:space="preserve">  Margin %</t>
         </is>
       </c>
-      <c r="B20" s="346" t="n">
+      <c r="B20" s="333" t="n">
         <v>0.399463</v>
       </c>
-      <c r="C20" s="346" t="n">
+      <c r="C20" s="333" t="n">
         <v>0.387524</v>
       </c>
-      <c r="D20" s="346" t="n">
+      <c r="D20" s="333" t="n">
         <v>0.395552</v>
       </c>
-      <c r="E20" s="346" t="n">
+      <c r="E20" s="333" t="n">
         <v>0.39801</v>
       </c>
-      <c r="F20" s="347" t="n">
+      <c r="F20" s="334" t="n">
         <v>0.403</v>
       </c>
-      <c r="G20" s="347" t="n">
+      <c r="G20" s="334" t="n">
         <v>0.409875</v>
       </c>
-      <c r="H20" s="347" t="n">
+      <c r="H20" s="334" t="n">
         <v>0.4195</v>
       </c>
     </row>
@@ -8240,25 +7801,25 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B22" s="344" t="n">
+      <c r="B22" s="331" t="n">
         <v>-106.4</v>
       </c>
-      <c r="C22" s="344" t="n">
+      <c r="C22" s="331" t="n">
         <v>-74.8</v>
       </c>
-      <c r="D22" s="344" t="n">
+      <c r="D22" s="331" t="n">
         <v>-68.09999999999999</v>
       </c>
-      <c r="E22" s="344" t="n">
+      <c r="E22" s="331" t="n">
         <v>-79.7</v>
       </c>
-      <c r="F22" s="345" t="n">
+      <c r="F22" s="332" t="n">
         <v>-10.78</v>
       </c>
-      <c r="G22" s="345" t="n">
+      <c r="G22" s="332" t="n">
         <v>30.0682</v>
       </c>
-      <c r="H22" s="345" t="n">
+      <c r="H22" s="332" t="n">
         <v>67.45326</v>
       </c>
     </row>
@@ -8268,16 +7829,16 @@
           <t xml:space="preserve">  Margin %</t>
         </is>
       </c>
-      <c r="B23" s="346" t="n">
+      <c r="B23" s="333" t="n">
         <v>-0.4277</v>
       </c>
-      <c r="C23" s="346" t="n">
+      <c r="C23" s="333" t="n">
         <v>-0.221455</v>
       </c>
-      <c r="D23" s="346" t="n">
+      <c r="D23" s="333" t="n">
         <v>-0.15676</v>
       </c>
-      <c r="E23" s="346" t="n">
+      <c r="E23" s="333" t="n">
         <v>-0.161998</v>
       </c>
       <c r="F23" s="178" t="inlineStr">
@@ -8285,10 +7846,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="347" t="n">
+      <c r="G23" s="334" t="n">
         <v>0.04460897029</v>
       </c>
-      <c r="H23" s="347" t="n">
+      <c r="H23" s="334" t="n">
         <v>0.08286458649800001</v>
       </c>
     </row>
@@ -8308,25 +7869,25 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B25" s="344" t="n">
+      <c r="B25" s="331" t="n">
         <v>-114.5</v>
       </c>
-      <c r="C25" s="344" t="n">
+      <c r="C25" s="331" t="n">
         <v>-83.90000000000001</v>
       </c>
-      <c r="D25" s="344" t="n">
+      <c r="D25" s="331" t="n">
         <v>-76.59999999999999</v>
       </c>
-      <c r="E25" s="344" t="n">
+      <c r="E25" s="331" t="n">
         <v>-88.59999999999999</v>
       </c>
-      <c r="F25" s="345" t="n">
+      <c r="F25" s="332" t="n">
         <v>-81.17</v>
       </c>
-      <c r="G25" s="345" t="n">
+      <c r="G25" s="332" t="n">
         <v>-45.42</v>
       </c>
-      <c r="H25" s="345" t="n">
+      <c r="H25" s="332" t="n">
         <v>-21.93</v>
       </c>
     </row>
@@ -8336,16 +7897,16 @@
           <t xml:space="preserve">  Margin %</t>
         </is>
       </c>
-      <c r="B26" s="346" t="n">
+      <c r="B26" s="333" t="n">
         <v>-0.459928</v>
       </c>
-      <c r="C26" s="346" t="n">
+      <c r="C26" s="333" t="n">
         <v>-0.248485</v>
       </c>
-      <c r="D26" s="346" t="n">
+      <c r="D26" s="333" t="n">
         <v>-0.176397</v>
       </c>
-      <c r="E26" s="346" t="n">
+      <c r="E26" s="333" t="n">
         <v>-0.18023</v>
       </c>
       <c r="F26" s="178" t="inlineStr">
@@ -8380,29 +7941,29 @@
           <t>Earnings from Cont. Ops.</t>
         </is>
       </c>
-      <c r="B28" s="344" t="n">
+      <c r="B28" s="331" t="n">
         <v>-117</v>
       </c>
-      <c r="C28" s="344" t="n">
+      <c r="C28" s="331" t="n">
         <v>-90.59999999999999</v>
       </c>
-      <c r="D28" s="344" t="n">
+      <c r="D28" s="331" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E28" s="344" t="n">
+      <c r="E28" s="331" t="n">
         <v>-98.5</v>
       </c>
-      <c r="F28" s="344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="344" t="inlineStr">
+      <c r="F28" s="331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8414,16 +7975,16 @@
           <t xml:space="preserve">  Margin %</t>
         </is>
       </c>
-      <c r="B29" s="346" t="n">
+      <c r="B29" s="333" t="n">
         <v>-0.47001</v>
       </c>
-      <c r="C29" s="346" t="n">
+      <c r="C29" s="333" t="n">
         <v>-0.268198</v>
       </c>
-      <c r="D29" s="346" t="n">
+      <c r="D29" s="333" t="n">
         <v>-0.221857</v>
       </c>
-      <c r="E29" s="346" t="n">
+      <c r="E29" s="333" t="n">
         <v>-0.200381</v>
       </c>
       <c r="F29" s="178" t="inlineStr">
@@ -8458,25 +8019,25 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B31" s="344" t="n">
+      <c r="B31" s="331" t="n">
         <v>-116.7</v>
       </c>
-      <c r="C31" s="344" t="n">
+      <c r="C31" s="331" t="n">
         <v>-90.3</v>
       </c>
-      <c r="D31" s="344" t="n">
+      <c r="D31" s="331" t="n">
         <v>-96.40000000000001</v>
       </c>
-      <c r="E31" s="344" t="n">
+      <c r="E31" s="331" t="n">
         <v>-98.5</v>
       </c>
-      <c r="F31" s="345" t="n">
+      <c r="F31" s="332" t="n">
         <v>-2.55</v>
       </c>
-      <c r="G31" s="345" t="n">
+      <c r="G31" s="332" t="n">
         <v>37.93337</v>
       </c>
-      <c r="H31" s="345" t="n">
+      <c r="H31" s="332" t="n">
         <v>73.18674</v>
       </c>
     </row>
@@ -8486,25 +8047,25 @@
           <t xml:space="preserve">  Margin %</t>
         </is>
       </c>
-      <c r="B32" s="346" t="n">
+      <c r="B32" s="333" t="n">
         <v>-0.468893</v>
       </c>
-      <c r="C32" s="346" t="n">
+      <c r="C32" s="333" t="n">
         <v>-0.267396</v>
       </c>
-      <c r="D32" s="346" t="n">
+      <c r="D32" s="333" t="n">
         <v>-0.221857</v>
       </c>
-      <c r="E32" s="346" t="n">
+      <c r="E32" s="333" t="n">
         <v>-0.200381</v>
       </c>
-      <c r="F32" s="347" t="n">
+      <c r="F32" s="334" t="n">
         <v>-0.004625694084</v>
       </c>
-      <c r="G32" s="347" t="n">
+      <c r="G32" s="334" t="n">
         <v>0.056277681249</v>
       </c>
-      <c r="H32" s="347" t="n">
+      <c r="H32" s="334" t="n">
         <v>0.089908018489</v>
       </c>
     </row>
@@ -8524,25 +8085,25 @@
           <t>Diluted EPS Excl. Extra Items³</t>
         </is>
       </c>
-      <c r="B34" s="345" t="n">
+      <c r="B34" s="332" t="n">
         <v>-9.6</v>
       </c>
-      <c r="C34" s="345" t="n">
+      <c r="C34" s="332" t="n">
         <v>-7.21</v>
       </c>
-      <c r="D34" s="345" t="n">
+      <c r="D34" s="332" t="n">
         <v>-2.92</v>
       </c>
-      <c r="E34" s="345" t="n">
+      <c r="E34" s="332" t="n">
         <v>-1.47</v>
       </c>
-      <c r="F34" s="345" t="n">
+      <c r="F34" s="332" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G34" s="345" t="n">
+      <c r="G34" s="332" t="n">
         <v>0.42981</v>
       </c>
-      <c r="H34" s="345" t="n">
+      <c r="H34" s="332" t="n">
         <v>0.79631</v>
       </c>
     </row>
@@ -8557,17 +8118,17 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="C35" s="346" t="inlineStr">
+      <c r="C35" s="333" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="D35" s="346" t="inlineStr">
+      <c r="D35" s="333" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="E35" s="346" t="inlineStr">
+      <c r="E35" s="333" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
@@ -8582,7 +8143,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H35" s="347" t="n">
+      <c r="H35" s="334" t="n">
         <v>0.852702356855</v>
       </c>
     </row>
@@ -8682,25 +8243,25 @@
           <t>Exchange Rate</t>
         </is>
       </c>
-      <c r="B39" s="348" t="n">
+      <c r="B39" s="335" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="348" t="n">
+      <c r="C39" s="335" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="348" t="n">
+      <c r="D39" s="335" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="348" t="n">
+      <c r="E39" s="335" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="348" t="n">
+      <c r="F39" s="335" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="348" t="n">
+      <c r="G39" s="335" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="348" t="n">
+      <c r="H39" s="335" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9064,7 +8625,7 @@
           <t>Share Price</t>
         </is>
       </c>
-      <c r="B50" s="349" t="n">
+      <c r="B50" s="336" t="n">
         <v>27.98</v>
       </c>
     </row>
@@ -9074,7 +8635,7 @@
           <t>Shares Out.</t>
         </is>
       </c>
-      <c r="B51" s="348" t="n">
+      <c r="B51" s="335" t="n">
         <v>81.505613</v>
       </c>
     </row>
@@ -9088,7 +8649,7 @@
           <t>Market Capitalization</t>
         </is>
       </c>
-      <c r="B53" s="344" t="n">
+      <c r="B53" s="331" t="n">
         <v>2280.527051</v>
       </c>
     </row>
@@ -9098,7 +8659,7 @@
           <t>Class A Common Stock Shares Out</t>
         </is>
       </c>
-      <c r="B54" s="348" t="n">
+      <c r="B54" s="335" t="n">
         <v>77.65943</v>
       </c>
     </row>
@@ -9108,7 +8669,7 @@
           <t>* Class A Common Stock Share Price</t>
         </is>
       </c>
-      <c r="B55" s="348" t="n">
+      <c r="B55" s="335" t="n">
         <v>27.98</v>
       </c>
     </row>
@@ -9118,7 +8679,7 @@
           <t>= Class A Common Stock Market Capitalization</t>
         </is>
       </c>
-      <c r="B56" s="348" t="n">
+      <c r="B56" s="335" t="n">
         <v>2172.910851</v>
       </c>
     </row>
@@ -9128,7 +8689,7 @@
           <t>+ Class B Common Stock Shares Out</t>
         </is>
       </c>
-      <c r="B57" s="348" t="n">
+      <c r="B57" s="335" t="n">
         <v>3.846183</v>
       </c>
     </row>
@@ -9138,7 +8699,7 @@
           <t>* Class B Common Stock Share Price</t>
         </is>
       </c>
-      <c r="B58" s="348" t="n">
+      <c r="B58" s="335" t="n">
         <v>27.98</v>
       </c>
     </row>
@@ -9148,7 +8709,7 @@
           <t>= Class B Common Stock Market Capitalization</t>
         </is>
       </c>
-      <c r="B59" s="348" t="n">
+      <c r="B59" s="335" t="n">
         <v>107.6162</v>
       </c>
     </row>
@@ -9158,7 +8719,7 @@
           <t>+ Class C Common Stock Shares Out</t>
         </is>
       </c>
-      <c r="B60" s="348" t="n">
+      <c r="B60" s="335" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9168,7 +8729,7 @@
           <t>* Class C Common Stock Share Price</t>
         </is>
       </c>
-      <c r="B61" s="348" t="n">
+      <c r="B61" s="335" t="n">
         <v>27.98</v>
       </c>
     </row>
@@ -9178,7 +8739,7 @@
           <t>= Class C Common Stock Market Capitalization</t>
         </is>
       </c>
-      <c r="B62" s="348" t="n">
+      <c r="B62" s="335" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9188,7 +8749,7 @@
           <t>- Cash &amp; Short Term Investments</t>
         </is>
       </c>
-      <c r="B63" s="348" t="n">
+      <c r="B63" s="335" t="n">
         <v>335.915</v>
       </c>
     </row>
@@ -9198,7 +8759,7 @@
           <t>+ Total Debt</t>
         </is>
       </c>
-      <c r="B64" s="348" t="n">
+      <c r="B64" s="335" t="n">
         <v>18.025</v>
       </c>
     </row>
@@ -9208,7 +8769,7 @@
           <t>+ Pref. Equity</t>
         </is>
       </c>
-      <c r="B65" s="348" t="inlineStr">
+      <c r="B65" s="335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9220,7 +8781,7 @@
           <t>+ Total Minority Interest</t>
         </is>
       </c>
-      <c r="B66" s="348" t="inlineStr">
+      <c r="B66" s="335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9232,7 +8793,7 @@
           <t>- Long Term Marketable Securities</t>
         </is>
       </c>
-      <c r="B67" s="348" t="inlineStr">
+      <c r="B67" s="335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9244,7 +8805,7 @@
           <t>= Total Enterprise Value (TEV)</t>
         </is>
       </c>
-      <c r="B68" s="344" t="n">
+      <c r="B68" s="331" t="n">
         <v>1962.637051</v>
       </c>
     </row>
@@ -9258,7 +8819,7 @@
           <t>Book Value of Common Equity</t>
         </is>
       </c>
-      <c r="B70" s="348" t="n">
+      <c r="B70" s="335" t="n">
         <v>618.309</v>
       </c>
     </row>
@@ -9268,7 +8829,7 @@
           <t>+ Pref. Equity</t>
         </is>
       </c>
-      <c r="B71" s="348" t="inlineStr">
+      <c r="B71" s="335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9280,7 +8841,7 @@
           <t>+ Total Minority Interest</t>
         </is>
       </c>
-      <c r="B72" s="348" t="inlineStr">
+      <c r="B72" s="335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9292,7 +8853,7 @@
           <t>+ Total Debt</t>
         </is>
       </c>
-      <c r="B73" s="348" t="n">
+      <c r="B73" s="335" t="n">
         <v>18.025</v>
       </c>
     </row>
@@ -9302,7 +8863,7 @@
           <t>= Total Capital</t>
         </is>
       </c>
-      <c r="B74" s="344" t="n">
+      <c r="B74" s="331" t="n">
         <v>636.3339999999999</v>
       </c>
     </row>
@@ -9660,19 +9221,19 @@
           <t>TEV/Total Revenue</t>
         </is>
       </c>
-      <c r="B87" s="350" t="n">
+      <c r="B87" s="337" t="n">
         <v>4.440653</v>
       </c>
-      <c r="C87" s="350" t="n">
+      <c r="C87" s="337" t="n">
         <v>3.991509</v>
       </c>
-      <c r="D87" s="351" t="n">
+      <c r="D87" s="338" t="n">
         <v>3.557191958158</v>
       </c>
-      <c r="E87" s="351" t="n">
+      <c r="E87" s="338" t="n">
         <v>2.911754542361</v>
       </c>
-      <c r="F87" s="351" t="n">
+      <c r="F87" s="338" t="n">
         <v>2.411048891306</v>
       </c>
     </row>
@@ -9705,10 +9266,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E89" s="351" t="n">
+      <c r="E89" s="338" t="n">
         <v>65.27284811661499</v>
       </c>
-      <c r="F89" s="351" t="n">
+      <c r="F89" s="338" t="n">
         <v>29.09625200828</v>
       </c>
     </row>
@@ -9781,10 +9342,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E93" s="351" t="n">
+      <c r="E93" s="338" t="n">
         <v>65.098531909448</v>
       </c>
-      <c r="F93" s="351" t="n">
+      <c r="F93" s="338" t="n">
         <v>35.137069734149</v>
       </c>
     </row>
@@ -9802,19 +9363,19 @@
           <t>P/BV</t>
         </is>
       </c>
-      <c r="B95" s="350" t="n">
+      <c r="B95" s="337" t="n">
         <v>3.615879</v>
       </c>
-      <c r="C95" s="350" t="n">
+      <c r="C95" s="337" t="n">
         <v>3.685557</v>
       </c>
-      <c r="D95" s="351" t="n">
+      <c r="D95" s="338" t="n">
         <v>3.684080243955</v>
       </c>
-      <c r="E95" s="351" t="n">
+      <c r="E95" s="338" t="n">
         <v>3.40017839392</v>
       </c>
-      <c r="F95" s="351" t="n">
+      <c r="F95" s="338" t="n">
         <v>3.035932068036</v>
       </c>
     </row>
@@ -9832,10 +9393,10 @@
           <t>Price/Tang BV</t>
         </is>
       </c>
-      <c r="B97" s="350" t="n">
+      <c r="B97" s="337" t="n">
         <v>5.682983</v>
       </c>
-      <c r="C97" s="350" t="n">
+      <c r="C97" s="337" t="n">
         <v>5.774732</v>
       </c>
       <c r="D97" s="173" t="inlineStr">
@@ -10214,22 +9775,22 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="336" t="n">
+      <c r="B5" s="323" t="n">
         <v>98.642</v>
       </c>
-      <c r="C5" s="336" t="n">
+      <c r="C5" s="323" t="n">
         <v>107.133</v>
       </c>
-      <c r="D5" s="336" t="n">
+      <c r="D5" s="323" t="n">
         <v>109.653</v>
       </c>
-      <c r="E5" s="336" t="n">
+      <c r="E5" s="323" t="n">
         <v>118.909</v>
       </c>
-      <c r="F5" s="336" t="n">
+      <c r="F5" s="323" t="n">
         <v>127.434</v>
       </c>
-      <c r="G5" s="336" t="n">
+      <c r="G5" s="323" t="n">
         <v>135.707</v>
       </c>
       <c r="H5" s="196" t="n"/>
@@ -10241,32 +9802,32 @@
           <t>Other Revenue</t>
         </is>
       </c>
-      <c r="B6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="336" t="inlineStr">
+      <c r="B6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10280,22 +9841,22 @@
           <t xml:space="preserve">  Total Revenue</t>
         </is>
       </c>
-      <c r="B7" s="337" t="n">
+      <c r="B7" s="324" t="n">
         <v>98.642</v>
       </c>
-      <c r="C7" s="337" t="n">
+      <c r="C7" s="324" t="n">
         <v>107.133</v>
       </c>
-      <c r="D7" s="337" t="n">
+      <c r="D7" s="324" t="n">
         <v>109.653</v>
       </c>
-      <c r="E7" s="337" t="n">
+      <c r="E7" s="324" t="n">
         <v>118.909</v>
       </c>
-      <c r="F7" s="337" t="n">
+      <c r="F7" s="324" t="n">
         <v>127.434</v>
       </c>
-      <c r="G7" s="337" t="n">
+      <c r="G7" s="324" t="n">
         <v>135.707</v>
       </c>
       <c r="H7" s="196" t="n"/>
@@ -10318,22 +9879,22 @@
           <t>Cost Of Goods Sold</t>
         </is>
       </c>
-      <c r="B9" s="336" t="n">
+      <c r="B9" s="323" t="n">
         <v>58.832</v>
       </c>
-      <c r="C9" s="336" t="n">
+      <c r="C9" s="323" t="n">
         <v>65.182</v>
       </c>
-      <c r="D9" s="336" t="n">
+      <c r="D9" s="323" t="n">
         <v>66.56699999999999</v>
       </c>
-      <c r="E9" s="336" t="n">
+      <c r="E9" s="323" t="n">
         <v>71.953</v>
       </c>
-      <c r="F9" s="336" t="n">
+      <c r="F9" s="323" t="n">
         <v>77.379</v>
       </c>
-      <c r="G9" s="336" t="n">
+      <c r="G9" s="323" t="n">
         <v>80.101</v>
       </c>
       <c r="H9" s="196" t="n"/>
@@ -10345,22 +9906,22 @@
           <t xml:space="preserve">  Gross Profit</t>
         </is>
       </c>
-      <c r="B10" s="337" t="n">
+      <c r="B10" s="324" t="n">
         <v>39.81</v>
       </c>
-      <c r="C10" s="337" t="n">
+      <c r="C10" s="324" t="n">
         <v>41.951</v>
       </c>
-      <c r="D10" s="337" t="n">
+      <c r="D10" s="324" t="n">
         <v>43.086</v>
       </c>
-      <c r="E10" s="337" t="n">
+      <c r="E10" s="324" t="n">
         <v>46.956</v>
       </c>
-      <c r="F10" s="337" t="n">
+      <c r="F10" s="324" t="n">
         <v>50.055</v>
       </c>
-      <c r="G10" s="337" t="n">
+      <c r="G10" s="324" t="n">
         <v>55.606</v>
       </c>
       <c r="H10" s="196" t="n"/>
@@ -10383,22 +9944,22 @@
           <t>Selling General &amp; Admin Exp.</t>
         </is>
       </c>
-      <c r="B12" s="336" t="n">
+      <c r="B12" s="323" t="n">
         <v>35.688</v>
       </c>
-      <c r="C12" s="336" t="n">
+      <c r="C12" s="323" t="n">
         <v>35.324</v>
       </c>
-      <c r="D12" s="336" t="n">
+      <c r="D12" s="323" t="n">
         <v>38.846</v>
       </c>
-      <c r="E12" s="336" t="n">
+      <c r="E12" s="323" t="n">
         <v>45.347</v>
       </c>
-      <c r="F12" s="336" t="n">
+      <c r="F12" s="323" t="n">
         <v>49.111</v>
       </c>
-      <c r="G12" s="336" t="n">
+      <c r="G12" s="323" t="n">
         <v>51.252</v>
       </c>
       <c r="H12" s="196" t="n"/>
@@ -10410,22 +9971,22 @@
           <t>R &amp; D Exp.</t>
         </is>
       </c>
-      <c r="B13" s="336" t="n">
+      <c r="B13" s="323" t="n">
         <v>21.346</v>
       </c>
-      <c r="C13" s="336" t="n">
+      <c r="C13" s="323" t="n">
         <v>22.737</v>
       </c>
-      <c r="D13" s="336" t="n">
+      <c r="D13" s="323" t="n">
         <v>23.131</v>
       </c>
-      <c r="E13" s="336" t="n">
+      <c r="E13" s="323" t="n">
         <v>25.089</v>
       </c>
-      <c r="F13" s="336" t="n">
+      <c r="F13" s="323" t="n">
         <v>24.528</v>
       </c>
-      <c r="G13" s="336" t="n">
+      <c r="G13" s="323" t="n">
         <v>26.108</v>
       </c>
       <c r="H13" s="196" t="n"/>
@@ -10437,32 +9998,32 @@
           <t>Depreciation &amp; Amort.</t>
         </is>
       </c>
-      <c r="B14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="336" t="inlineStr">
+      <c r="B14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10722,30 +10283,30 @@
           <t>Other Operating Expense/(Income)</t>
         </is>
       </c>
-      <c r="B15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="336" t="n">
+      <c r="B15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="323" t="n">
         <v>0.911</v>
       </c>
-      <c r="F15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="336" t="inlineStr">
+      <c r="F15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10770,22 +10331,22 @@
           <t xml:space="preserve">  Other Operating Exp., Total</t>
         </is>
       </c>
-      <c r="B17" s="337" t="n">
+      <c r="B17" s="324" t="n">
         <v>57.034</v>
       </c>
-      <c r="C17" s="337" t="n">
+      <c r="C17" s="324" t="n">
         <v>58.061</v>
       </c>
-      <c r="D17" s="337" t="n">
+      <c r="D17" s="324" t="n">
         <v>61.977</v>
       </c>
-      <c r="E17" s="337" t="n">
+      <c r="E17" s="324" t="n">
         <v>71.34699999999999</v>
       </c>
-      <c r="F17" s="337" t="n">
+      <c r="F17" s="324" t="n">
         <v>73.639</v>
       </c>
-      <c r="G17" s="337" t="n">
+      <c r="G17" s="324" t="n">
         <v>77.36</v>
       </c>
       <c r="H17" s="196" t="n"/>
@@ -10808,22 +10369,22 @@
           <t xml:space="preserve">  Operating Income</t>
         </is>
       </c>
-      <c r="B19" s="338" t="n">
+      <c r="B19" s="325" t="n">
         <v>-17.2</v>
       </c>
-      <c r="C19" s="338" t="n">
+      <c r="C19" s="325" t="n">
         <v>-16.1</v>
       </c>
-      <c r="D19" s="338" t="n">
+      <c r="D19" s="325" t="n">
         <v>-18.9</v>
       </c>
-      <c r="E19" s="338" t="n">
+      <c r="E19" s="325" t="n">
         <v>-24.4</v>
       </c>
-      <c r="F19" s="338" t="n">
+      <c r="F19" s="325" t="n">
         <v>-23.6</v>
       </c>
-      <c r="G19" s="338" t="n">
+      <c r="G19" s="325" t="n">
         <v>-21.8</v>
       </c>
       <c r="H19" s="196" t="n"/>
@@ -10846,22 +10407,22 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B21" s="336" t="n">
+      <c r="B21" s="323" t="n">
         <v>-2.4</v>
       </c>
-      <c r="C21" s="336" t="n">
+      <c r="C21" s="323" t="n">
         <v>-2.4</v>
       </c>
-      <c r="D21" s="336" t="n">
+      <c r="D21" s="323" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E21" s="336" t="n">
+      <c r="E21" s="323" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F21" s="336" t="n">
+      <c r="F21" s="323" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G21" s="336" t="n">
+      <c r="G21" s="323" t="n">
         <v>-0.3</v>
       </c>
       <c r="H21" s="196" t="n"/>
@@ -10873,22 +10434,22 @@
           <t>Interest and Invest. Income</t>
         </is>
       </c>
-      <c r="B22" s="336" t="n">
+      <c r="B22" s="323" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="C22" s="336" t="n">
+      <c r="C22" s="323" t="n">
         <v>0.487</v>
       </c>
-      <c r="D22" s="336" t="n">
+      <c r="D22" s="323" t="n">
         <v>0.883</v>
       </c>
-      <c r="E22" s="336" t="n">
+      <c r="E22" s="323" t="n">
         <v>3.335</v>
       </c>
-      <c r="F22" s="336" t="n">
+      <c r="F22" s="323" t="n">
         <v>2.779</v>
       </c>
-      <c r="G22" s="336" t="n">
+      <c r="G22" s="323" t="n">
         <v>2.799</v>
       </c>
       <c r="H22" s="196" t="n"/>
@@ -10900,22 +10461,22 @@
           <t xml:space="preserve">  Net Interest Exp.</t>
         </is>
       </c>
-      <c r="B23" s="337" t="n">
+      <c r="B23" s="324" t="n">
         <v>-1.8</v>
       </c>
-      <c r="C23" s="337" t="n">
+      <c r="C23" s="324" t="n">
         <v>-1.9</v>
       </c>
-      <c r="D23" s="337" t="n">
+      <c r="D23" s="324" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E23" s="337" t="n">
+      <c r="E23" s="324" t="n">
         <v>2.964</v>
       </c>
-      <c r="F23" s="337" t="n">
+      <c r="F23" s="324" t="n">
         <v>2.55</v>
       </c>
-      <c r="G23" s="337" t="n">
+      <c r="G23" s="324" t="n">
         <v>2.517</v>
       </c>
       <c r="H23" s="196" t="n"/>
@@ -10938,22 +10499,22 @@
           <t>Currency Exchange Gains (Loss)</t>
         </is>
       </c>
-      <c r="B25" s="336" t="n">
+      <c r="B25" s="323" t="n">
         <v>0.408</v>
       </c>
-      <c r="C25" s="336" t="n">
+      <c r="C25" s="323" t="n">
         <v>0.661</v>
       </c>
-      <c r="D25" s="336" t="n">
+      <c r="D25" s="323" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E25" s="336" t="n">
+      <c r="E25" s="323" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F25" s="336" t="n">
+      <c r="F25" s="323" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G25" s="336" t="n">
+      <c r="G25" s="323" t="n">
         <v>-0.3</v>
       </c>
       <c r="H25" s="196" t="n"/>
@@ -10965,22 +10526,22 @@
           <t>Other Non-Operating Inc. (Exp.)</t>
         </is>
       </c>
-      <c r="B26" s="336" t="n">
+      <c r="B26" s="323" t="n">
         <v>1.299</v>
       </c>
-      <c r="C26" s="336" t="n">
+      <c r="C26" s="323" t="n">
         <v>-3</v>
       </c>
-      <c r="D26" s="336" t="n">
+      <c r="D26" s="323" t="n">
         <v>-5.4</v>
       </c>
-      <c r="E26" s="336" t="n">
+      <c r="E26" s="323" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F26" s="336" t="n">
+      <c r="F26" s="323" t="n">
         <v>0.135</v>
       </c>
-      <c r="G26" s="336" t="n">
+      <c r="G26" s="323" t="n">
         <v>0.124</v>
       </c>
       <c r="H26" s="196" t="n"/>
@@ -10992,22 +10553,22 @@
           <t xml:space="preserve">  EBT Excl. Unusual Items</t>
         </is>
       </c>
-      <c r="B27" s="337" t="n">
+      <c r="B27" s="324" t="n">
         <v>-17.4</v>
       </c>
-      <c r="C27" s="337" t="n">
+      <c r="C27" s="324" t="n">
         <v>-20.3</v>
       </c>
-      <c r="D27" s="337" t="n">
+      <c r="D27" s="324" t="n">
         <v>-25.9</v>
       </c>
-      <c r="E27" s="337" t="n">
+      <c r="E27" s="324" t="n">
         <v>-21.8</v>
       </c>
-      <c r="F27" s="337" t="n">
+      <c r="F27" s="324" t="n">
         <v>-21.4</v>
       </c>
-      <c r="G27" s="337" t="n">
+      <c r="G27" s="324" t="n">
         <v>-19.4</v>
       </c>
       <c r="H27" s="196" t="n"/>
@@ -11030,32 +10591,32 @@
           <t>Impairment of Goodwill</t>
         </is>
       </c>
-      <c r="B29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="336" t="inlineStr">
+      <c r="B29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11069,24 +10630,24 @@
           <t>Other Unusual Items</t>
         </is>
       </c>
-      <c r="B30" s="336" t="n">
+      <c r="B30" s="323" t="n">
         <v>1.811</v>
       </c>
-      <c r="C30" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="336" t="n">
+      <c r="C30" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="323" t="n">
         <v>-10.5</v>
       </c>
-      <c r="E30" s="336" t="n">
+      <c r="E30" s="323" t="n">
         <v>0.231</v>
       </c>
-      <c r="F30" s="336" t="n">
+      <c r="F30" s="323" t="n">
         <v>1.758</v>
       </c>
-      <c r="G30" s="336" t="inlineStr">
+      <c r="G30" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11100,22 +10661,22 @@
           <t xml:space="preserve">  EBT Incl. Unusual Items</t>
         </is>
       </c>
-      <c r="B31" s="337" t="n">
+      <c r="B31" s="324" t="n">
         <v>-15.5</v>
       </c>
-      <c r="C31" s="337" t="n">
+      <c r="C31" s="324" t="n">
         <v>-20.3</v>
       </c>
-      <c r="D31" s="337" t="n">
+      <c r="D31" s="324" t="n">
         <v>-36.4</v>
       </c>
-      <c r="E31" s="337" t="n">
+      <c r="E31" s="324" t="n">
         <v>-21.5</v>
       </c>
-      <c r="F31" s="337" t="n">
+      <c r="F31" s="324" t="n">
         <v>-19.6</v>
       </c>
-      <c r="G31" s="337" t="n">
+      <c r="G31" s="324" t="n">
         <v>-19.4</v>
       </c>
       <c r="H31" s="196" t="n"/>
@@ -11138,22 +10699,22 @@
           <t>Income Tax Expense</t>
         </is>
       </c>
-      <c r="B33" s="336" t="n">
+      <c r="B33" s="323" t="n">
         <v>0.772</v>
       </c>
-      <c r="C33" s="336" t="n">
+      <c r="C33" s="323" t="n">
         <v>0.872</v>
       </c>
-      <c r="D33" s="336" t="n">
+      <c r="D33" s="323" t="n">
         <v>0.49</v>
       </c>
-      <c r="E33" s="336" t="n">
+      <c r="E33" s="323" t="n">
         <v>0.387</v>
       </c>
-      <c r="F33" s="336" t="n">
+      <c r="F33" s="323" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="G33" s="336" t="n">
+      <c r="G33" s="323" t="n">
         <v>0.165</v>
       </c>
       <c r="H33" s="196" t="n"/>
@@ -11165,22 +10726,22 @@
           <t xml:space="preserve">  Earnings from Cont. Ops.</t>
         </is>
       </c>
-      <c r="B34" s="337" t="n">
+      <c r="B34" s="324" t="n">
         <v>-16.3</v>
       </c>
-      <c r="C34" s="337" t="n">
+      <c r="C34" s="324" t="n">
         <v>-21.2</v>
       </c>
-      <c r="D34" s="337" t="n">
+      <c r="D34" s="324" t="n">
         <v>-36.9</v>
       </c>
-      <c r="E34" s="337" t="n">
+      <c r="E34" s="324" t="n">
         <v>-21.9</v>
       </c>
-      <c r="F34" s="337" t="n">
+      <c r="F34" s="324" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G34" s="337" t="n">
+      <c r="G34" s="324" t="n">
         <v>-19.6</v>
       </c>
       <c r="H34" s="196" t="n"/>
@@ -11203,32 +10764,32 @@
           <t>Earnings of Discontinued Ops.</t>
         </is>
       </c>
-      <c r="B36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="336" t="inlineStr">
+      <c r="B36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11242,32 +10803,32 @@
           <t>Extraord. Item &amp; Account. Change</t>
         </is>
       </c>
-      <c r="B37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="336" t="inlineStr">
+      <c r="B37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11281,22 +10842,22 @@
           <t xml:space="preserve">  Net Income to Company</t>
         </is>
       </c>
-      <c r="B38" s="337" t="n">
+      <c r="B38" s="324" t="n">
         <v>-16.3</v>
       </c>
-      <c r="C38" s="337" t="n">
+      <c r="C38" s="324" t="n">
         <v>-21.2</v>
       </c>
-      <c r="D38" s="337" t="n">
+      <c r="D38" s="324" t="n">
         <v>-36.9</v>
       </c>
-      <c r="E38" s="337" t="n">
+      <c r="E38" s="324" t="n">
         <v>-21.9</v>
       </c>
-      <c r="F38" s="337" t="n">
+      <c r="F38" s="324" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G38" s="337" t="n">
+      <c r="G38" s="324" t="n">
         <v>-19.6</v>
       </c>
       <c r="H38" s="196" t="n"/>
@@ -11319,32 +10880,32 @@
           <t>Minority Int. in Earnings</t>
         </is>
       </c>
-      <c r="B40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="336" t="inlineStr">
+      <c r="B40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11358,22 +10919,22 @@
           <t xml:space="preserve">  Net Income</t>
         </is>
       </c>
-      <c r="B41" s="339" t="n">
+      <c r="B41" s="326" t="n">
         <v>-16.3</v>
       </c>
-      <c r="C41" s="339" t="n">
+      <c r="C41" s="326" t="n">
         <v>-21.2</v>
       </c>
-      <c r="D41" s="339" t="n">
+      <c r="D41" s="326" t="n">
         <v>-36.9</v>
       </c>
-      <c r="E41" s="339" t="n">
+      <c r="E41" s="326" t="n">
         <v>-21.9</v>
       </c>
-      <c r="F41" s="339" t="n">
+      <c r="F41" s="326" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G41" s="339" t="n">
+      <c r="G41" s="326" t="n">
         <v>-19.6</v>
       </c>
       <c r="H41" s="196" t="n"/>
@@ -11396,32 +10957,32 @@
           <t>Pref. Dividends and Other Adj.</t>
         </is>
       </c>
-      <c r="B43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="336" t="inlineStr">
+      <c r="B43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11446,22 +11007,22 @@
           <t xml:space="preserve">  NI to Common Incl Extra Items</t>
         </is>
       </c>
-      <c r="B45" s="338" t="n">
+      <c r="B45" s="325" t="n">
         <v>-16.3</v>
       </c>
-      <c r="C45" s="338" t="n">
+      <c r="C45" s="325" t="n">
         <v>-21.2</v>
       </c>
-      <c r="D45" s="338" t="n">
+      <c r="D45" s="325" t="n">
         <v>-36.9</v>
       </c>
-      <c r="E45" s="338" t="n">
+      <c r="E45" s="325" t="n">
         <v>-21.9</v>
       </c>
-      <c r="F45" s="338" t="n">
+      <c r="F45" s="325" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G45" s="338" t="n">
+      <c r="G45" s="325" t="n">
         <v>-19.6</v>
       </c>
       <c r="H45" s="196" t="n"/>
@@ -11473,22 +11034,22 @@
           <t xml:space="preserve">  NI to Common Excl. Extra Items</t>
         </is>
       </c>
-      <c r="B46" s="338" t="n">
+      <c r="B46" s="325" t="n">
         <v>-16.3</v>
       </c>
-      <c r="C46" s="338" t="n">
+      <c r="C46" s="325" t="n">
         <v>-21.2</v>
       </c>
-      <c r="D46" s="338" t="n">
+      <c r="D46" s="325" t="n">
         <v>-36.9</v>
       </c>
-      <c r="E46" s="338" t="n">
+      <c r="E46" s="325" t="n">
         <v>-21.9</v>
       </c>
-      <c r="F46" s="338" t="n">
+      <c r="F46" s="325" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G46" s="338" t="n">
+      <c r="G46" s="325" t="n">
         <v>-19.6</v>
       </c>
       <c r="H46" s="196" t="n"/>
@@ -11526,22 +11087,22 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B49" s="340" t="n">
+      <c r="B49" s="327" t="n">
         <v>-1.28</v>
       </c>
-      <c r="C49" s="340" t="n">
+      <c r="C49" s="327" t="n">
         <v>-1.66</v>
       </c>
-      <c r="D49" s="340" t="n">
+      <c r="D49" s="327" t="n">
         <v>-1.49</v>
       </c>
-      <c r="E49" s="340" t="n">
+      <c r="E49" s="327" t="n">
         <v>-0.27</v>
       </c>
-      <c r="F49" s="340" t="n">
+      <c r="F49" s="327" t="n">
         <v>-0.25</v>
       </c>
-      <c r="G49" s="340" t="n">
+      <c r="G49" s="327" t="n">
         <v>-0.24</v>
       </c>
       <c r="H49" s="196" t="n"/>
@@ -11553,22 +11114,22 @@
           <t>Basic EPS Excl. Extra Items</t>
         </is>
       </c>
-      <c r="B50" s="341" t="n">
+      <c r="B50" s="328" t="n">
         <v>-1.28</v>
       </c>
-      <c r="C50" s="341" t="n">
+      <c r="C50" s="328" t="n">
         <v>-1.66</v>
       </c>
-      <c r="D50" s="341" t="n">
+      <c r="D50" s="328" t="n">
         <v>-1.49</v>
       </c>
-      <c r="E50" s="341" t="n">
+      <c r="E50" s="328" t="n">
         <v>-0.27</v>
       </c>
-      <c r="F50" s="341" t="n">
+      <c r="F50" s="328" t="n">
         <v>-0.25</v>
       </c>
-      <c r="G50" s="341" t="n">
+      <c r="G50" s="328" t="n">
         <v>-0.24</v>
       </c>
       <c r="H50" s="196" t="n"/>
@@ -11580,22 +11141,22 @@
           <t>Weighted Avg. Basic Shares Out.</t>
         </is>
       </c>
-      <c r="B51" s="336" t="n">
+      <c r="B51" s="323" t="n">
         <v>12.753056</v>
       </c>
-      <c r="C51" s="336" t="n">
+      <c r="C51" s="323" t="n">
         <v>12.793403</v>
       </c>
-      <c r="D51" s="336" t="n">
+      <c r="D51" s="323" t="n">
         <v>24.730353</v>
       </c>
-      <c r="E51" s="336" t="n">
+      <c r="E51" s="323" t="n">
         <v>81.349711</v>
       </c>
-      <c r="F51" s="336" t="n">
+      <c r="F51" s="323" t="n">
         <v>81.177074</v>
       </c>
-      <c r="G51" s="336" t="n">
+      <c r="G51" s="323" t="n">
         <v>81.337205</v>
       </c>
       <c r="H51" s="196" t="n"/>
@@ -11618,22 +11179,22 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B53" s="340" t="n">
+      <c r="B53" s="327" t="n">
         <v>-1.28</v>
       </c>
-      <c r="C53" s="340" t="n">
+      <c r="C53" s="327" t="n">
         <v>-1.66</v>
       </c>
-      <c r="D53" s="340" t="n">
+      <c r="D53" s="327" t="n">
         <v>-1.49</v>
       </c>
-      <c r="E53" s="340" t="n">
+      <c r="E53" s="327" t="n">
         <v>-0.27</v>
       </c>
-      <c r="F53" s="340" t="n">
+      <c r="F53" s="327" t="n">
         <v>-0.25</v>
       </c>
-      <c r="G53" s="340" t="n">
+      <c r="G53" s="327" t="n">
         <v>-0.24</v>
       </c>
       <c r="H53" s="196" t="n"/>
@@ -11645,22 +11206,22 @@
           <t>Diluted EPS Excl. Extra Items</t>
         </is>
       </c>
-      <c r="B54" s="341" t="n">
+      <c r="B54" s="328" t="n">
         <v>-1.28</v>
       </c>
-      <c r="C54" s="341" t="n">
+      <c r="C54" s="328" t="n">
         <v>-1.66</v>
       </c>
-      <c r="D54" s="341" t="n">
+      <c r="D54" s="328" t="n">
         <v>-1.49</v>
       </c>
-      <c r="E54" s="341" t="n">
+      <c r="E54" s="328" t="n">
         <v>-0.27</v>
       </c>
-      <c r="F54" s="341" t="n">
+      <c r="F54" s="328" t="n">
         <v>-0.25</v>
       </c>
-      <c r="G54" s="341" t="n">
+      <c r="G54" s="328" t="n">
         <v>-0.24</v>
       </c>
       <c r="H54" s="196" t="n"/>
@@ -11672,22 +11233,22 @@
           <t>Weighted Avg. Diluted Shares Out.</t>
         </is>
       </c>
-      <c r="B55" s="336" t="n">
+      <c r="B55" s="323" t="n">
         <v>12.753056</v>
       </c>
-      <c r="C55" s="336" t="n">
+      <c r="C55" s="323" t="n">
         <v>12.793403</v>
       </c>
-      <c r="D55" s="336" t="n">
+      <c r="D55" s="323" t="n">
         <v>24.730353</v>
       </c>
-      <c r="E55" s="336" t="n">
+      <c r="E55" s="323" t="n">
         <v>81.349711</v>
       </c>
-      <c r="F55" s="336" t="n">
+      <c r="F55" s="323" t="n">
         <v>81.177074</v>
       </c>
-      <c r="G55" s="336" t="n">
+      <c r="G55" s="323" t="n">
         <v>81.337205</v>
       </c>
       <c r="H55" s="196" t="n"/>
@@ -11710,22 +11271,22 @@
           <t>Normalized Basic EPS</t>
         </is>
       </c>
-      <c r="B57" s="340" t="n">
+      <c r="B57" s="327" t="n">
         <v>-0.85</v>
       </c>
-      <c r="C57" s="340" t="n">
+      <c r="C57" s="327" t="n">
         <v>-0.99</v>
       </c>
-      <c r="D57" s="340" t="n">
+      <c r="D57" s="327" t="n">
         <v>-0.65</v>
       </c>
-      <c r="E57" s="340" t="n">
+      <c r="E57" s="327" t="n">
         <v>-0.17</v>
       </c>
-      <c r="F57" s="340" t="n">
+      <c r="F57" s="327" t="n">
         <v>-0.16</v>
       </c>
-      <c r="G57" s="340" t="n">
+      <c r="G57" s="327" t="n">
         <v>-0.15</v>
       </c>
       <c r="H57" s="196" t="n"/>
@@ -11737,22 +11298,22 @@
           <t>Normalized Diluted EPS</t>
         </is>
       </c>
-      <c r="B58" s="341" t="n">
+      <c r="B58" s="328" t="n">
         <v>-0.85</v>
       </c>
-      <c r="C58" s="341" t="n">
+      <c r="C58" s="328" t="n">
         <v>-0.99</v>
       </c>
-      <c r="D58" s="341" t="n">
+      <c r="D58" s="328" t="n">
         <v>-0.65</v>
       </c>
-      <c r="E58" s="341" t="n">
+      <c r="E58" s="328" t="n">
         <v>-0.17</v>
       </c>
-      <c r="F58" s="341" t="n">
+      <c r="F58" s="328" t="n">
         <v>-0.16</v>
       </c>
-      <c r="G58" s="341" t="n">
+      <c r="G58" s="328" t="n">
         <v>-0.15</v>
       </c>
       <c r="H58" s="196" t="n"/>
@@ -11775,32 +11336,32 @@
           <t>Dividends per Share</t>
         </is>
       </c>
-      <c r="B60" s="341" t="inlineStr">
+      <c r="B60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C60" s="341" t="inlineStr">
+      <c r="C60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D60" s="341" t="inlineStr">
+      <c r="D60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E60" s="341" t="inlineStr">
+      <c r="E60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="F60" s="341" t="inlineStr">
+      <c r="F60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G60" s="341" t="inlineStr">
+      <c r="G60" s="328" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -11840,22 +11401,22 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B63" s="336" t="n">
+      <c r="B63" s="323" t="n">
         <v>-14.9</v>
       </c>
-      <c r="C63" s="336" t="n">
+      <c r="C63" s="323" t="n">
         <v>-14</v>
       </c>
-      <c r="D63" s="336" t="n">
+      <c r="D63" s="323" t="n">
         <v>-16.8</v>
       </c>
-      <c r="E63" s="336" t="n">
+      <c r="E63" s="323" t="n">
         <v>-22.3</v>
       </c>
-      <c r="F63" s="336" t="n">
+      <c r="F63" s="323" t="n">
         <v>-21.2</v>
       </c>
-      <c r="G63" s="336" t="n">
+      <c r="G63" s="323" t="n">
         <v>-19.4</v>
       </c>
       <c r="H63" s="196" t="n"/>
@@ -11867,22 +11428,22 @@
           <t>EBITA</t>
         </is>
       </c>
-      <c r="B64" s="336" t="n">
+      <c r="B64" s="323" t="n">
         <v>-15.9</v>
       </c>
-      <c r="C64" s="336" t="n">
+      <c r="C64" s="323" t="n">
         <v>-15</v>
       </c>
-      <c r="D64" s="336" t="n">
+      <c r="D64" s="323" t="n">
         <v>-17.8</v>
       </c>
-      <c r="E64" s="336" t="n">
+      <c r="E64" s="323" t="n">
         <v>-23.3</v>
       </c>
-      <c r="F64" s="336" t="n">
+      <c r="F64" s="323" t="n">
         <v>-22.2</v>
       </c>
-      <c r="G64" s="336" t="n">
+      <c r="G64" s="323" t="n">
         <v>-20.4</v>
       </c>
       <c r="H64" s="196" t="n"/>
@@ -11894,22 +11455,22 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B65" s="336" t="n">
+      <c r="B65" s="323" t="n">
         <v>-17.2</v>
       </c>
-      <c r="C65" s="336" t="n">
+      <c r="C65" s="323" t="n">
         <v>-16.1</v>
       </c>
-      <c r="D65" s="336" t="n">
+      <c r="D65" s="323" t="n">
         <v>-18.9</v>
       </c>
-      <c r="E65" s="336" t="n">
+      <c r="E65" s="323" t="n">
         <v>-24.4</v>
       </c>
-      <c r="F65" s="336" t="n">
+      <c r="F65" s="323" t="n">
         <v>-23.6</v>
       </c>
-      <c r="G65" s="336" t="n">
+      <c r="G65" s="323" t="n">
         <v>-21.8</v>
       </c>
       <c r="H65" s="196" t="n"/>
@@ -11921,32 +11482,32 @@
           <t>Effective Tax Rate %</t>
         </is>
       </c>
-      <c r="B66" s="342" t="inlineStr">
+      <c r="B66" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="C66" s="342" t="inlineStr">
+      <c r="C66" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="D66" s="342" t="inlineStr">
+      <c r="D66" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="E66" s="342" t="inlineStr">
+      <c r="E66" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="F66" s="342" t="inlineStr">
+      <c r="F66" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
       </c>
-      <c r="G66" s="342" t="inlineStr">
+      <c r="G66" s="329" t="inlineStr">
         <is>
           <t>NM</t>
         </is>
@@ -11960,30 +11521,30 @@
           <t>Current Domestic Taxes</t>
         </is>
       </c>
-      <c r="B67" s="336" t="inlineStr">
+      <c r="B67" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C67" s="336" t="inlineStr">
+      <c r="C67" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D67" s="336" t="inlineStr">
+      <c r="D67" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E67" s="336" t="n">
+      <c r="E67" s="323" t="n">
         <v>0.243</v>
       </c>
-      <c r="F67" s="336" t="inlineStr">
+      <c r="F67" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G67" s="336" t="inlineStr">
+      <c r="G67" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -11997,30 +11558,30 @@
           <t>Current Foreign Taxes</t>
         </is>
       </c>
-      <c r="B68" s="336" t="inlineStr">
+      <c r="B68" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C68" s="336" t="inlineStr">
+      <c r="C68" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D68" s="336" t="inlineStr">
+      <c r="D68" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E68" s="336" t="n">
+      <c r="E68" s="323" t="n">
         <v>1.685</v>
       </c>
-      <c r="F68" s="336" t="inlineStr">
+      <c r="F68" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G68" s="336" t="inlineStr">
+      <c r="G68" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12034,30 +11595,30 @@
           <t>Total Current Taxes</t>
         </is>
       </c>
-      <c r="B69" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="336" t="n">
+      <c r="B69" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="323" t="n">
         <v>1.928</v>
       </c>
-      <c r="F69" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="336" t="inlineStr">
+      <c r="F69" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12071,30 +11632,30 @@
           <t>Deferred Foreign Taxes</t>
         </is>
       </c>
-      <c r="B70" s="336" t="inlineStr">
+      <c r="B70" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C70" s="336" t="inlineStr">
+      <c r="C70" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D70" s="336" t="inlineStr">
+      <c r="D70" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E70" s="336" t="n">
+      <c r="E70" s="323" t="n">
         <v>0.593</v>
       </c>
-      <c r="F70" s="336" t="inlineStr">
+      <c r="F70" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G70" s="336" t="inlineStr">
+      <c r="G70" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12108,30 +11669,30 @@
           <t>Total Deferred Taxes</t>
         </is>
       </c>
-      <c r="B71" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="336" t="n">
+      <c r="B71" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" s="323" t="n">
         <v>0.593</v>
       </c>
-      <c r="F71" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="336" t="inlineStr">
+      <c r="F71" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12156,22 +11717,22 @@
           <t>Normalized Net Income</t>
         </is>
       </c>
-      <c r="B73" s="336" t="n">
+      <c r="B73" s="323" t="n">
         <v>-10.8</v>
       </c>
-      <c r="C73" s="336" t="n">
+      <c r="C73" s="323" t="n">
         <v>-12.7</v>
       </c>
-      <c r="D73" s="336" t="n">
+      <c r="D73" s="323" t="n">
         <v>-16.2</v>
       </c>
-      <c r="E73" s="336" t="n">
+      <c r="E73" s="323" t="n">
         <v>-13.6</v>
       </c>
-      <c r="F73" s="336" t="n">
+      <c r="F73" s="323" t="n">
         <v>-13.3</v>
       </c>
-      <c r="G73" s="336" t="n">
+      <c r="G73" s="323" t="n">
         <v>-12.1</v>
       </c>
       <c r="H73" s="196" t="n"/>
@@ -12183,24 +11744,24 @@
           <t>Interest on Long Term Debt</t>
         </is>
       </c>
-      <c r="B74" s="336" t="n">
+      <c r="B74" s="323" t="n">
         <v>2.406</v>
       </c>
-      <c r="C74" s="336" t="n">
+      <c r="C74" s="323" t="n">
         <v>2.419</v>
       </c>
-      <c r="D74" s="336" t="n">
+      <c r="D74" s="323" t="n">
         <v>2.147</v>
       </c>
-      <c r="E74" s="336" t="inlineStr">
+      <c r="E74" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="F74" s="336" t="n">
+      <c r="F74" s="323" t="n">
         <v>0.229</v>
       </c>
-      <c r="G74" s="336" t="n">
+      <c r="G74" s="323" t="n">
         <v>0.282</v>
       </c>
       <c r="H74" s="196" t="n"/>
@@ -12212,22 +11773,22 @@
           <t>Filing Date</t>
         </is>
       </c>
-      <c r="B75" s="343" t="n">
+      <c r="B75" s="330" t="n">
         <v>46154</v>
       </c>
-      <c r="C75" s="343" t="n">
+      <c r="C75" s="330" t="n">
         <v>46240</v>
       </c>
-      <c r="D75" s="343" t="n">
+      <c r="D75" s="330" t="n">
         <v>45975</v>
       </c>
-      <c r="E75" s="343" t="n">
+      <c r="E75" s="330" t="n">
         <v>46087</v>
       </c>
-      <c r="F75" s="343" t="n">
+      <c r="F75" s="330" t="n">
         <v>46154</v>
       </c>
-      <c r="G75" s="343" t="n">
+      <c r="G75" s="330" t="n">
         <v>46240</v>
       </c>
       <c r="H75" s="196" t="n"/>
@@ -12343,22 +11904,22 @@
           <t>Selling and Marketing Exp.</t>
         </is>
       </c>
-      <c r="B80" s="336" t="n">
+      <c r="B80" s="323" t="n">
         <v>15.202</v>
       </c>
-      <c r="C80" s="336" t="n">
+      <c r="C80" s="323" t="n">
         <v>15.973</v>
       </c>
-      <c r="D80" s="336" t="n">
+      <c r="D80" s="323" t="n">
         <v>17.657</v>
       </c>
-      <c r="E80" s="336" t="n">
+      <c r="E80" s="323" t="n">
         <v>18.372</v>
       </c>
-      <c r="F80" s="336" t="n">
+      <c r="F80" s="323" t="n">
         <v>20.49</v>
       </c>
-      <c r="G80" s="336" t="n">
+      <c r="G80" s="323" t="n">
         <v>21.142</v>
       </c>
       <c r="H80" s="196" t="n"/>
@@ -12370,22 +11931,22 @@
           <t>General and Administrative Exp.</t>
         </is>
       </c>
-      <c r="B81" s="336" t="n">
+      <c r="B81" s="323" t="n">
         <v>20.486</v>
       </c>
-      <c r="C81" s="336" t="n">
+      <c r="C81" s="323" t="n">
         <v>19.351</v>
       </c>
-      <c r="D81" s="336" t="n">
+      <c r="D81" s="323" t="n">
         <v>21.189</v>
       </c>
-      <c r="E81" s="336" t="n">
+      <c r="E81" s="323" t="n">
         <v>26.975</v>
       </c>
-      <c r="F81" s="336" t="n">
+      <c r="F81" s="323" t="n">
         <v>28.621</v>
       </c>
-      <c r="G81" s="336" t="n">
+      <c r="G81" s="323" t="n">
         <v>30.11</v>
       </c>
       <c r="H81" s="196" t="n"/>
@@ -12397,22 +11958,22 @@
           <t>R&amp;D Exp.</t>
         </is>
       </c>
-      <c r="B82" s="336" t="n">
+      <c r="B82" s="323" t="n">
         <v>21.346</v>
       </c>
-      <c r="C82" s="336" t="n">
+      <c r="C82" s="323" t="n">
         <v>22.737</v>
       </c>
-      <c r="D82" s="336" t="n">
+      <c r="D82" s="323" t="n">
         <v>23.131</v>
       </c>
-      <c r="E82" s="336" t="n">
+      <c r="E82" s="323" t="n">
         <v>25.138</v>
       </c>
-      <c r="F82" s="336" t="n">
+      <c r="F82" s="323" t="n">
         <v>24.528</v>
       </c>
-      <c r="G82" s="336" t="n">
+      <c r="G82" s="323" t="n">
         <v>26.108</v>
       </c>
       <c r="H82" s="196" t="n"/>
@@ -12435,22 +11996,22 @@
           <t>Stock-Based Comp., COGS</t>
         </is>
       </c>
-      <c r="B84" s="336" t="n">
+      <c r="B84" s="323" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="C84" s="336" t="n">
+      <c r="C84" s="323" t="n">
         <v>0.037</v>
       </c>
-      <c r="D84" s="336" t="n">
+      <c r="D84" s="323" t="n">
         <v>0.038</v>
       </c>
-      <c r="E84" s="336" t="n">
+      <c r="E84" s="323" t="n">
         <v>0.056</v>
       </c>
-      <c r="F84" s="336" t="n">
+      <c r="F84" s="323" t="n">
         <v>0.075</v>
       </c>
-      <c r="G84" s="336" t="n">
+      <c r="G84" s="323" t="n">
         <v>0.098</v>
       </c>
       <c r="H84" s="196" t="n"/>
@@ -12462,22 +12023,22 @@
           <t>Stock-Based Comp., R&amp;D Exp.</t>
         </is>
       </c>
-      <c r="B85" s="336" t="n">
+      <c r="B85" s="323" t="n">
         <v>1.614</v>
       </c>
-      <c r="C85" s="336" t="n">
+      <c r="C85" s="323" t="n">
         <v>1.549</v>
       </c>
-      <c r="D85" s="336" t="n">
+      <c r="D85" s="323" t="n">
         <v>1.874</v>
       </c>
-      <c r="E85" s="336" t="n">
+      <c r="E85" s="323" t="n">
         <v>3.54</v>
       </c>
-      <c r="F85" s="336" t="n">
+      <c r="F85" s="323" t="n">
         <v>4.03</v>
       </c>
-      <c r="G85" s="336" t="n">
+      <c r="G85" s="323" t="n">
         <v>4.302</v>
       </c>
       <c r="H85" s="196" t="n"/>
@@ -12489,22 +12050,22 @@
           <t>Stock-Based Comp., S&amp;M Exp.</t>
         </is>
       </c>
-      <c r="B86" s="336" t="n">
+      <c r="B86" s="323" t="n">
         <v>1.268</v>
       </c>
-      <c r="C86" s="336" t="n">
+      <c r="C86" s="323" t="n">
         <v>1.271</v>
       </c>
-      <c r="D86" s="336" t="n">
+      <c r="D86" s="323" t="n">
         <v>1.687</v>
       </c>
-      <c r="E86" s="336" t="n">
+      <c r="E86" s="323" t="n">
         <v>2.895</v>
       </c>
-      <c r="F86" s="336" t="n">
+      <c r="F86" s="323" t="n">
         <v>3.328</v>
       </c>
-      <c r="G86" s="336" t="n">
+      <c r="G86" s="323" t="n">
         <v>3.623</v>
       </c>
       <c r="H86" s="196" t="n"/>
@@ -12516,22 +12077,22 @@
           <t>Stock-Based Comp., G&amp;A Exp.</t>
         </is>
       </c>
-      <c r="B87" s="336" t="n">
+      <c r="B87" s="323" t="n">
         <v>1.74</v>
       </c>
-      <c r="C87" s="336" t="n">
+      <c r="C87" s="323" t="n">
         <v>1.805</v>
       </c>
-      <c r="D87" s="336" t="n">
+      <c r="D87" s="323" t="n">
         <v>2.993</v>
       </c>
-      <c r="E87" s="336" t="n">
+      <c r="E87" s="323" t="n">
         <v>7.905</v>
       </c>
-      <c r="F87" s="336" t="n">
+      <c r="F87" s="323" t="n">
         <v>8.131</v>
       </c>
-      <c r="G87" s="336" t="n">
+      <c r="G87" s="323" t="n">
         <v>7.987</v>
       </c>
       <c r="H87" s="196" t="n"/>
@@ -12543,22 +12104,22 @@
           <t xml:space="preserve">  Stock-Based Comp., Total</t>
         </is>
       </c>
-      <c r="B88" s="338" t="n">
+      <c r="B88" s="325" t="n">
         <v>4.691</v>
       </c>
-      <c r="C88" s="338" t="n">
+      <c r="C88" s="325" t="n">
         <v>4.662</v>
       </c>
-      <c r="D88" s="338" t="n">
+      <c r="D88" s="325" t="n">
         <v>6.592</v>
       </c>
-      <c r="E88" s="338" t="n">
+      <c r="E88" s="325" t="n">
         <v>14.396</v>
       </c>
-      <c r="F88" s="338" t="n">
+      <c r="F88" s="325" t="n">
         <v>15.564</v>
       </c>
-      <c r="G88" s="338" t="n">
+      <c r="G88" s="325" t="n">
         <v>16.01</v>
       </c>
       <c r="H88" s="196" t="n"/>
@@ -13031,24 +12592,24 @@
           <t>Cash And Equivalents</t>
         </is>
       </c>
-      <c r="B5" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="336" t="n">
+      <c r="B5" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="323" t="n">
         <v>78.212</v>
       </c>
-      <c r="D5" s="336" t="n">
+      <c r="D5" s="323" t="n">
         <v>378.158</v>
       </c>
-      <c r="E5" s="336" t="n">
+      <c r="E5" s="323" t="n">
         <v>370.914</v>
       </c>
-      <c r="F5" s="336" t="n">
+      <c r="F5" s="323" t="n">
         <v>348.158</v>
       </c>
-      <c r="G5" s="336" t="n">
+      <c r="G5" s="323" t="n">
         <v>335.915</v>
       </c>
       <c r="H5" s="196" t="n"/>
@@ -13059,22 +12620,22 @@
           <t xml:space="preserve">  Total Cash &amp; ST Investments</t>
         </is>
       </c>
-      <c r="B6" s="337" t="n">
+      <c r="B6" s="324" t="n">
         <v>77.905</v>
       </c>
-      <c r="C6" s="337" t="n">
+      <c r="C6" s="324" t="n">
         <v>78.212</v>
       </c>
-      <c r="D6" s="337" t="n">
+      <c r="D6" s="324" t="n">
         <v>378.158</v>
       </c>
-      <c r="E6" s="337" t="n">
+      <c r="E6" s="324" t="n">
         <v>370.914</v>
       </c>
-      <c r="F6" s="337" t="n">
+      <c r="F6" s="324" t="n">
         <v>348.158</v>
       </c>
-      <c r="G6" s="337" t="n">
+      <c r="G6" s="324" t="n">
         <v>335.915</v>
       </c>
       <c r="H6" s="196" t="n"/>
@@ -13095,24 +12656,24 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="B8" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="336" t="n">
+      <c r="B8" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="323" t="n">
         <v>82.22799999999999</v>
       </c>
-      <c r="D8" s="336" t="n">
+      <c r="D8" s="323" t="n">
         <v>84.307</v>
       </c>
-      <c r="E8" s="336" t="n">
+      <c r="E8" s="323" t="n">
         <v>81.572</v>
       </c>
-      <c r="F8" s="336" t="n">
+      <c r="F8" s="323" t="n">
         <v>94.916</v>
       </c>
-      <c r="G8" s="336" t="n">
+      <c r="G8" s="323" t="n">
         <v>104.679</v>
       </c>
       <c r="H8" s="196" t="n"/>
@@ -13123,24 +12684,24 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B9" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="337" t="n">
+      <c r="B9" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="324" t="n">
         <v>82.22799999999999</v>
       </c>
-      <c r="D9" s="337" t="n">
+      <c r="D9" s="324" t="n">
         <v>84.307</v>
       </c>
-      <c r="E9" s="337" t="n">
+      <c r="E9" s="324" t="n">
         <v>81.572</v>
       </c>
-      <c r="F9" s="337" t="n">
+      <c r="F9" s="324" t="n">
         <v>94.916</v>
       </c>
-      <c r="G9" s="337" t="n">
+      <c r="G9" s="324" t="n">
         <v>104.679</v>
       </c>
       <c r="H9" s="196" t="n"/>
@@ -13161,24 +12722,24 @@
           <t>Prepaid Exp.</t>
         </is>
       </c>
-      <c r="B11" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="336" t="n">
+      <c r="B11" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="323" t="n">
         <v>12.19</v>
       </c>
-      <c r="D11" s="336" t="n">
+      <c r="D11" s="323" t="n">
         <v>15.641</v>
       </c>
-      <c r="E11" s="336" t="n">
+      <c r="E11" s="323" t="n">
         <v>16.265</v>
       </c>
-      <c r="F11" s="336" t="n">
+      <c r="F11" s="323" t="n">
         <v>17.204</v>
       </c>
-      <c r="G11" s="336" t="n">
+      <c r="G11" s="323" t="n">
         <v>16.812</v>
       </c>
       <c r="H11" s="196" t="n"/>
@@ -13189,24 +12750,24 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B12" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="336" t="n">
+      <c r="B12" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="323" t="n">
         <v>0.9</v>
       </c>
-      <c r="D12" s="336" t="n">
+      <c r="D12" s="323" t="n">
         <v>0.8</v>
       </c>
-      <c r="E12" s="336" t="n">
+      <c r="E12" s="323" t="n">
         <v>0.8</v>
       </c>
-      <c r="F12" s="336" t="n">
+      <c r="F12" s="323" t="n">
         <v>0.9</v>
       </c>
-      <c r="G12" s="336" t="n">
+      <c r="G12" s="323" t="n">
         <v>0.8</v>
       </c>
       <c r="H12" s="196" t="n"/>
@@ -13217,24 +12778,24 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B13" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="337" t="n">
+      <c r="B13" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="324" t="n">
         <v>173.53</v>
       </c>
-      <c r="D13" s="337" t="n">
+      <c r="D13" s="324" t="n">
         <v>478.906</v>
       </c>
-      <c r="E13" s="337" t="n">
+      <c r="E13" s="324" t="n">
         <v>469.551</v>
       </c>
-      <c r="F13" s="337" t="n">
+      <c r="F13" s="324" t="n">
         <v>461.178</v>
       </c>
-      <c r="G13" s="337" t="n">
+      <c r="G13" s="324" t="n">
         <v>458.206</v>
       </c>
       <c r="H13" s="196" t="n"/>
@@ -13502,24 +13063,24 @@
           <t>Gross Property, Plant &amp; Equipment</t>
         </is>
       </c>
-      <c r="B15" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="336" t="n">
+      <c r="B15" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="323" t="n">
         <v>44.389</v>
       </c>
-      <c r="D15" s="336" t="n">
+      <c r="D15" s="323" t="n">
         <v>44.638</v>
       </c>
-      <c r="E15" s="336" t="n">
+      <c r="E15" s="323" t="n">
         <v>47.997</v>
       </c>
-      <c r="F15" s="336" t="n">
+      <c r="F15" s="323" t="n">
         <v>50.603</v>
       </c>
-      <c r="G15" s="336" t="n">
+      <c r="G15" s="323" t="n">
         <v>51.203</v>
       </c>
       <c r="H15" s="196" t="n"/>
@@ -13530,24 +13091,24 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B16" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="336" t="n">
+      <c r="B16" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="323" t="n">
         <v>-14.5</v>
       </c>
-      <c r="D16" s="336" t="n">
+      <c r="D16" s="323" t="n">
         <v>-15.4</v>
       </c>
-      <c r="E16" s="336" t="n">
+      <c r="E16" s="323" t="n">
         <v>-16.3</v>
       </c>
-      <c r="F16" s="336" t="n">
+      <c r="F16" s="323" t="n">
         <v>-17.1</v>
       </c>
-      <c r="G16" s="336" t="n">
+      <c r="G16" s="323" t="n">
         <v>-18.1</v>
       </c>
       <c r="H16" s="196" t="n"/>
@@ -13558,24 +13119,24 @@
           <t xml:space="preserve">  Net Property, Plant &amp; Equipment</t>
         </is>
       </c>
-      <c r="B17" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="337" t="n">
+      <c r="B17" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="324" t="n">
         <v>29.865</v>
       </c>
-      <c r="D17" s="337" t="n">
+      <c r="D17" s="324" t="n">
         <v>29.254</v>
       </c>
-      <c r="E17" s="337" t="n">
+      <c r="E17" s="324" t="n">
         <v>31.714</v>
       </c>
-      <c r="F17" s="337" t="n">
+      <c r="F17" s="324" t="n">
         <v>33.459</v>
       </c>
-      <c r="G17" s="337" t="n">
+      <c r="G17" s="324" t="n">
         <v>33.136</v>
       </c>
       <c r="H17" s="196" t="n"/>
@@ -13596,24 +13157,24 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B19" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="336" t="n">
+      <c r="B19" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="323" t="n">
         <v>167.011</v>
       </c>
-      <c r="D19" s="336" t="n">
+      <c r="D19" s="323" t="n">
         <v>165.962</v>
       </c>
-      <c r="E19" s="336" t="n">
+      <c r="E19" s="323" t="n">
         <v>192.305</v>
       </c>
-      <c r="F19" s="336" t="n">
+      <c r="F19" s="323" t="n">
         <v>191.005</v>
       </c>
-      <c r="G19" s="336" t="n">
+      <c r="G19" s="323" t="n">
         <v>190.72</v>
       </c>
       <c r="H19" s="196" t="n"/>
@@ -13624,24 +13185,24 @@
           <t>Other Intangibles</t>
         </is>
       </c>
-      <c r="B20" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="336" t="n">
+      <c r="B20" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="323" t="n">
         <v>25.521</v>
       </c>
-      <c r="D20" s="336" t="n">
+      <c r="D20" s="323" t="n">
         <v>24.127</v>
       </c>
-      <c r="E20" s="336" t="n">
+      <c r="E20" s="323" t="n">
         <v>36.025</v>
       </c>
-      <c r="F20" s="336" t="n">
+      <c r="F20" s="323" t="n">
         <v>34.336</v>
       </c>
-      <c r="G20" s="336" t="n">
+      <c r="G20" s="323" t="n">
         <v>32.971</v>
       </c>
       <c r="H20" s="196" t="n"/>
@@ -13652,24 +13213,24 @@
           <t>Deferred Tax Assets, LT</t>
         </is>
       </c>
-      <c r="B21" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="336" t="n">
+      <c r="B21" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="323" t="n">
         <v>0.361</v>
       </c>
-      <c r="D21" s="336" t="n">
+      <c r="D21" s="323" t="n">
         <v>1.183</v>
       </c>
-      <c r="E21" s="336" t="n">
+      <c r="E21" s="323" t="n">
         <v>0.529</v>
       </c>
-      <c r="F21" s="336" t="n">
+      <c r="F21" s="323" t="n">
         <v>0.437</v>
       </c>
-      <c r="G21" s="336" t="n">
+      <c r="G21" s="323" t="n">
         <v>0.401</v>
       </c>
       <c r="H21" s="196" t="n"/>
@@ -13680,24 +13241,24 @@
           <t>Deferred Charges, LT</t>
         </is>
       </c>
-      <c r="B22" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="336" t="n">
+      <c r="B22" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="323" t="n">
         <v>0.8</v>
       </c>
-      <c r="D22" s="336" t="n">
+      <c r="D22" s="323" t="n">
         <v>0.8</v>
       </c>
-      <c r="E22" s="336" t="n">
+      <c r="E22" s="323" t="n">
         <v>0.7</v>
       </c>
-      <c r="F22" s="336" t="n">
+      <c r="F22" s="323" t="n">
         <v>0.6</v>
       </c>
-      <c r="G22" s="336" t="n">
+      <c r="G22" s="323" t="n">
         <v>0.6</v>
       </c>
       <c r="H22" s="196" t="n"/>
@@ -13708,24 +13269,24 @@
           <t>Other Long-Term Assets</t>
         </is>
       </c>
-      <c r="B23" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="336" t="n">
+      <c r="B23" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="323" t="n">
         <v>1.782</v>
       </c>
-      <c r="D23" s="336" t="n">
+      <c r="D23" s="323" t="n">
         <v>1.826</v>
       </c>
-      <c r="E23" s="336" t="n">
+      <c r="E23" s="323" t="n">
         <v>2.271</v>
       </c>
-      <c r="F23" s="336" t="n">
+      <c r="F23" s="323" t="n">
         <v>2.305</v>
       </c>
-      <c r="G23" s="336" t="n">
+      <c r="G23" s="323" t="n">
         <v>2.315</v>
       </c>
       <c r="H23" s="196" t="n"/>
@@ -13736,24 +13297,24 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B24" s="339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="339" t="n">
+      <c r="B24" s="326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="326" t="n">
         <v>398.87</v>
       </c>
-      <c r="D24" s="339" t="n">
+      <c r="D24" s="326" t="n">
         <v>702.058</v>
       </c>
-      <c r="E24" s="339" t="n">
+      <c r="E24" s="326" t="n">
         <v>733.095</v>
       </c>
-      <c r="F24" s="339" t="n">
+      <c r="F24" s="326" t="n">
         <v>723.3200000000001</v>
       </c>
-      <c r="G24" s="339" t="n">
+      <c r="G24" s="326" t="n">
         <v>718.349</v>
       </c>
       <c r="H24" s="196" t="n"/>
@@ -13788,24 +13349,24 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="B27" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="336" t="n">
+      <c r="B27" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C27" s="323" t="n">
         <v>6.9</v>
       </c>
-      <c r="D27" s="336" t="n">
+      <c r="D27" s="323" t="n">
         <v>5.663</v>
       </c>
-      <c r="E27" s="336" t="n">
+      <c r="E27" s="323" t="n">
         <v>4.427</v>
       </c>
-      <c r="F27" s="336" t="n">
+      <c r="F27" s="323" t="n">
         <v>7.222</v>
       </c>
-      <c r="G27" s="336" t="n">
+      <c r="G27" s="323" t="n">
         <v>6.039</v>
       </c>
       <c r="H27" s="196" t="n"/>
@@ -13816,24 +13377,24 @@
           <t>Accrued Exp.</t>
         </is>
       </c>
-      <c r="B28" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="336" t="n">
+      <c r="B28" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" s="323" t="n">
         <v>44.954</v>
       </c>
-      <c r="D28" s="336" t="n">
+      <c r="D28" s="323" t="n">
         <v>50.169</v>
       </c>
-      <c r="E28" s="336" t="n">
+      <c r="E28" s="323" t="n">
         <v>51.546</v>
       </c>
-      <c r="F28" s="336" t="n">
+      <c r="F28" s="323" t="n">
         <v>47.694</v>
       </c>
-      <c r="G28" s="336" t="n">
+      <c r="G28" s="323" t="n">
         <v>50.76</v>
       </c>
       <c r="H28" s="196" t="n"/>
@@ -13844,24 +13405,24 @@
           <t>Curr. Port. of Leases</t>
         </is>
       </c>
-      <c r="B29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="336" t="n">
+      <c r="B29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="323" t="n">
         <v>7.954</v>
       </c>
-      <c r="D29" s="336" t="n">
+      <c r="D29" s="323" t="n">
         <v>8.106</v>
       </c>
-      <c r="E29" s="336" t="n">
+      <c r="E29" s="323" t="n">
         <v>9.749000000000001</v>
       </c>
-      <c r="F29" s="336" t="n">
+      <c r="F29" s="323" t="n">
         <v>10.021</v>
       </c>
-      <c r="G29" s="336" t="n">
+      <c r="G29" s="323" t="n">
         <v>9.829000000000001</v>
       </c>
       <c r="H29" s="196" t="n"/>
@@ -13872,24 +13433,24 @@
           <t>Curr. Income Taxes Payable</t>
         </is>
       </c>
-      <c r="B30" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="336" t="n">
+      <c r="B30" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="323" t="n">
         <v>1.746</v>
       </c>
-      <c r="D30" s="336" t="n">
+      <c r="D30" s="323" t="n">
         <v>1.345</v>
       </c>
-      <c r="E30" s="336" t="n">
+      <c r="E30" s="323" t="n">
         <v>1.62</v>
       </c>
-      <c r="F30" s="336" t="n">
+      <c r="F30" s="323" t="n">
         <v>1.733</v>
       </c>
-      <c r="G30" s="336" t="n">
+      <c r="G30" s="323" t="n">
         <v>1.358</v>
       </c>
       <c r="H30" s="196" t="n"/>
@@ -13900,24 +13461,24 @@
           <t>Unearned Revenue, Current</t>
         </is>
       </c>
-      <c r="B31" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="336" t="n">
+      <c r="B31" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C31" s="323" t="n">
         <v>21.26</v>
       </c>
-      <c r="D31" s="336" t="n">
+      <c r="D31" s="323" t="n">
         <v>24.103</v>
       </c>
-      <c r="E31" s="336" t="n">
+      <c r="E31" s="323" t="n">
         <v>26.893</v>
       </c>
-      <c r="F31" s="336" t="n">
+      <c r="F31" s="323" t="n">
         <v>23.954</v>
       </c>
-      <c r="G31" s="336" t="n">
+      <c r="G31" s="323" t="n">
         <v>22.81</v>
       </c>
       <c r="H31" s="196" t="n"/>
@@ -13928,30 +13489,30 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="336" t="n">
+      <c r="B32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="323" t="n">
         <v>3.319</v>
       </c>
-      <c r="E32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="336" t="inlineStr">
+      <c r="E32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -13964,24 +13525,24 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B33" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" s="337" t="n">
+      <c r="B33" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="324" t="n">
         <v>82.81399999999999</v>
       </c>
-      <c r="D33" s="337" t="n">
+      <c r="D33" s="324" t="n">
         <v>92.705</v>
       </c>
-      <c r="E33" s="337" t="n">
+      <c r="E33" s="324" t="n">
         <v>94.235</v>
       </c>
-      <c r="F33" s="337" t="n">
+      <c r="F33" s="324" t="n">
         <v>90.624</v>
       </c>
-      <c r="G33" s="337" t="n">
+      <c r="G33" s="324" t="n">
         <v>90.79600000000001</v>
       </c>
       <c r="H33" s="196" t="n"/>
@@ -14002,28 +13563,28 @@
           <t>Long-Term Debt</t>
         </is>
       </c>
-      <c r="B35" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="336" t="n">
+      <c r="B35" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="323" t="n">
         <v>70.881</v>
       </c>
-      <c r="D35" s="336" t="n">
+      <c r="D35" s="323" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="336" t="inlineStr">
+      <c r="E35" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -14036,24 +13597,24 @@
           <t>Long-Term Leases</t>
         </is>
       </c>
-      <c r="B36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="336" t="n">
+      <c r="B36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="323" t="n">
         <v>9.602</v>
       </c>
-      <c r="D36" s="336" t="n">
+      <c r="D36" s="323" t="n">
         <v>8.409000000000001</v>
       </c>
-      <c r="E36" s="336" t="n">
+      <c r="E36" s="323" t="n">
         <v>9.378</v>
       </c>
-      <c r="F36" s="336" t="n">
+      <c r="F36" s="323" t="n">
         <v>9.249000000000001</v>
       </c>
-      <c r="G36" s="336" t="n">
+      <c r="G36" s="323" t="n">
         <v>8.196</v>
       </c>
       <c r="H36" s="196" t="n"/>
@@ -14064,24 +13625,24 @@
           <t>Unearned Revenue, Non-Current</t>
         </is>
       </c>
-      <c r="B37" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="336" t="n">
+      <c r="B37" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" s="323" t="n">
         <v>1.499</v>
       </c>
-      <c r="D37" s="336" t="n">
+      <c r="D37" s="323" t="n">
         <v>1.354</v>
       </c>
-      <c r="E37" s="336" t="n">
+      <c r="E37" s="323" t="n">
         <v>1.746</v>
       </c>
-      <c r="F37" s="336" t="n">
+      <c r="F37" s="323" t="n">
         <v>1.321</v>
       </c>
-      <c r="G37" s="336" t="n">
+      <c r="G37" s="323" t="n">
         <v>1.048</v>
       </c>
       <c r="H37" s="196" t="n"/>
@@ -14092,30 +13653,30 @@
           <t>Other Non-Current Liabilities</t>
         </is>
       </c>
-      <c r="B38" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="336" t="n">
+      <c r="B38" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" s="323" t="n">
         <v>17.675</v>
       </c>
-      <c r="D38" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="336" t="inlineStr">
+      <c r="D38" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -14128,24 +13689,24 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B39" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="337" t="n">
+      <c r="B39" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" s="324" t="n">
         <v>182.471</v>
       </c>
-      <c r="D39" s="337" t="n">
+      <c r="D39" s="324" t="n">
         <v>127.468</v>
       </c>
-      <c r="E39" s="337" t="n">
+      <c r="E39" s="324" t="n">
         <v>105.359</v>
       </c>
-      <c r="F39" s="337" t="n">
+      <c r="F39" s="324" t="n">
         <v>101.194</v>
       </c>
-      <c r="G39" s="337" t="n">
+      <c r="G39" s="324" t="n">
         <v>100.04</v>
       </c>
       <c r="H39" s="196" t="n"/>
@@ -14166,30 +13727,30 @@
           <t>Pref. Stock, Convertible</t>
         </is>
       </c>
-      <c r="B41" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="336" t="n">
+      <c r="B41" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" s="323" t="n">
         <v>1220.005</v>
       </c>
-      <c r="D41" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="336" t="inlineStr">
+      <c r="D41" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -14202,28 +13763,28 @@
           <t xml:space="preserve">  Total Pref. Equity</t>
         </is>
       </c>
-      <c r="B42" s="337" t="n">
+      <c r="B42" s="324" t="n">
         <v>1195.058</v>
       </c>
-      <c r="C42" s="337" t="n">
+      <c r="C42" s="324" t="n">
         <v>1220.005</v>
       </c>
-      <c r="D42" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="337" t="inlineStr">
+      <c r="D42" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="324" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -14246,26 +13807,26 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="B44" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="336" t="n">
+      <c r="B44" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="323" t="n">
         <v>0.001</v>
       </c>
-      <c r="E44" s="336" t="n">
+      <c r="E44" s="323" t="n">
         <v>0.001</v>
       </c>
-      <c r="F44" s="336" t="n">
+      <c r="F44" s="323" t="n">
         <v>0.001</v>
       </c>
-      <c r="G44" s="336" t="n">
+      <c r="G44" s="323" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" s="196" t="n"/>
@@ -14276,24 +13837,24 @@
           <t>Additional Paid In Capital</t>
         </is>
       </c>
-      <c r="B45" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="336" t="n">
+      <c r="B45" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" s="323" t="n">
         <v>120.091</v>
       </c>
-      <c r="D45" s="336" t="n">
+      <c r="D45" s="323" t="n">
         <v>1736.317</v>
       </c>
-      <c r="E45" s="336" t="n">
+      <c r="E45" s="323" t="n">
         <v>1811.349</v>
       </c>
-      <c r="F45" s="336" t="n">
+      <c r="F45" s="323" t="n">
         <v>1827.909</v>
       </c>
-      <c r="G45" s="336" t="n">
+      <c r="G45" s="323" t="n">
         <v>1844.614</v>
       </c>
       <c r="H45" s="196" t="n"/>
@@ -14304,24 +13865,24 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="B46" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="336" t="n">
+      <c r="B46" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C46" s="323" t="n">
         <v>-1132.5</v>
       </c>
-      <c r="D46" s="336" t="n">
+      <c r="D46" s="323" t="n">
         <v>-1169.4</v>
       </c>
-      <c r="E46" s="336" t="n">
+      <c r="E46" s="323" t="n">
         <v>-1191.3</v>
       </c>
-      <c r="F46" s="336" t="n">
+      <c r="F46" s="323" t="n">
         <v>-1211.5</v>
       </c>
-      <c r="G46" s="336" t="n">
+      <c r="G46" s="323" t="n">
         <v>-1231</v>
       </c>
       <c r="H46" s="196" t="n"/>
@@ -14332,32 +13893,32 @@
           <t>Treasury Stock</t>
         </is>
       </c>
-      <c r="B47" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="336" t="inlineStr">
+      <c r="B47" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -14370,24 +13931,24 @@
           <t>Comprehensive Inc. and Other</t>
         </is>
       </c>
-      <c r="B48" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="336" t="n">
+      <c r="B48" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="323" t="n">
         <v>8.795999999999999</v>
       </c>
-      <c r="D48" s="336" t="n">
+      <c r="D48" s="323" t="n">
         <v>7.652</v>
       </c>
-      <c r="E48" s="336" t="n">
+      <c r="E48" s="323" t="n">
         <v>7.702</v>
       </c>
-      <c r="F48" s="336" t="n">
+      <c r="F48" s="323" t="n">
         <v>5.681</v>
       </c>
-      <c r="G48" s="336" t="n">
+      <c r="G48" s="323" t="n">
         <v>4.715</v>
       </c>
       <c r="H48" s="196" t="n"/>
@@ -14398,22 +13959,22 @@
           <t xml:space="preserve">  Total Common Equity</t>
         </is>
       </c>
-      <c r="B49" s="337" t="n">
+      <c r="B49" s="324" t="n">
         <v>-987.1</v>
       </c>
-      <c r="C49" s="337" t="n">
+      <c r="C49" s="324" t="n">
         <v>-1003.6</v>
       </c>
-      <c r="D49" s="337" t="n">
+      <c r="D49" s="324" t="n">
         <v>574.59</v>
       </c>
-      <c r="E49" s="337" t="n">
+      <c r="E49" s="324" t="n">
         <v>627.736</v>
       </c>
-      <c r="F49" s="337" t="n">
+      <c r="F49" s="324" t="n">
         <v>622.126</v>
       </c>
-      <c r="G49" s="337" t="n">
+      <c r="G49" s="324" t="n">
         <v>618.309</v>
       </c>
       <c r="H49" s="196" t="n"/>
@@ -14434,22 +13995,22 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B51" s="352" t="n">
+      <c r="B51" s="339" t="n">
         <v>207.203</v>
       </c>
-      <c r="C51" s="352" t="n">
+      <c r="C51" s="339" t="n">
         <v>216.399</v>
       </c>
-      <c r="D51" s="352" t="n">
+      <c r="D51" s="339" t="n">
         <v>574.59</v>
       </c>
-      <c r="E51" s="352" t="n">
+      <c r="E51" s="339" t="n">
         <v>627.736</v>
       </c>
-      <c r="F51" s="352" t="n">
+      <c r="F51" s="339" t="n">
         <v>622.126</v>
       </c>
-      <c r="G51" s="352" t="n">
+      <c r="G51" s="339" t="n">
         <v>618.309</v>
       </c>
       <c r="H51" s="196" t="n"/>
@@ -14470,24 +14031,24 @@
           <t>Total Liabilities And Equity</t>
         </is>
       </c>
-      <c r="B53" s="353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="353" t="n">
+      <c r="B53" s="340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" s="340" t="n">
         <v>398.87</v>
       </c>
-      <c r="D53" s="353" t="n">
+      <c r="D53" s="340" t="n">
         <v>702.058</v>
       </c>
-      <c r="E53" s="353" t="n">
+      <c r="E53" s="340" t="n">
         <v>733.095</v>
       </c>
-      <c r="F53" s="353" t="n">
+      <c r="F53" s="340" t="n">
         <v>723.3200000000001</v>
       </c>
-      <c r="G53" s="353" t="n">
+      <c r="G53" s="340" t="n">
         <v>718.349</v>
       </c>
       <c r="H53" s="196" t="n"/>
@@ -14522,22 +14083,22 @@
           <t>Total Shares Out. on Filing Date</t>
         </is>
       </c>
-      <c r="B56" s="336" t="n">
+      <c r="B56" s="323" t="n">
         <v>12.753056</v>
       </c>
-      <c r="C56" s="336" t="n">
+      <c r="C56" s="323" t="n">
         <v>12.935746</v>
       </c>
-      <c r="D56" s="336" t="n">
+      <c r="D56" s="323" t="n">
         <v>80.99082</v>
       </c>
-      <c r="E56" s="336" t="n">
+      <c r="E56" s="323" t="n">
         <v>81.18881399999999</v>
       </c>
-      <c r="F56" s="336" t="n">
+      <c r="F56" s="323" t="n">
         <v>81.29587100000001</v>
       </c>
-      <c r="G56" s="336" t="n">
+      <c r="G56" s="323" t="n">
         <v>81.505613</v>
       </c>
       <c r="H56" s="196" t="n"/>
@@ -14548,22 +14109,22 @@
           <t>Total Shares Out. on Balance Sheet Date</t>
         </is>
       </c>
-      <c r="B57" s="336" t="n">
+      <c r="B57" s="323" t="n">
         <v>12.753056</v>
       </c>
-      <c r="C57" s="336" t="n">
+      <c r="C57" s="323" t="n">
         <v>12.935746</v>
       </c>
-      <c r="D57" s="336" t="n">
+      <c r="D57" s="323" t="n">
         <v>79.588847</v>
       </c>
-      <c r="E57" s="336" t="n">
+      <c r="E57" s="323" t="n">
         <v>81.12285799999999</v>
       </c>
-      <c r="F57" s="336" t="n">
+      <c r="F57" s="323" t="n">
         <v>81.26116500000001</v>
       </c>
-      <c r="G57" s="336" t="n">
+      <c r="G57" s="323" t="n">
         <v>81.444356</v>
       </c>
       <c r="H57" s="196" t="n"/>
@@ -14574,22 +14135,22 @@
           <t>Book Value/Share</t>
         </is>
       </c>
-      <c r="B58" s="340" t="n">
+      <c r="B58" s="327" t="n">
         <v>-77.65000000000001</v>
       </c>
-      <c r="C58" s="340" t="n">
+      <c r="C58" s="327" t="n">
         <v>-77.58</v>
       </c>
-      <c r="D58" s="340" t="n">
+      <c r="D58" s="327" t="n">
         <v>7.22</v>
       </c>
-      <c r="E58" s="340" t="n">
+      <c r="E58" s="327" t="n">
         <v>7.74</v>
       </c>
-      <c r="F58" s="340" t="n">
+      <c r="F58" s="327" t="n">
         <v>7.66</v>
       </c>
-      <c r="G58" s="340" t="n">
+      <c r="G58" s="327" t="n">
         <v>7.59</v>
       </c>
       <c r="H58" s="196" t="n"/>
@@ -14600,22 +14161,22 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="B59" s="336" t="n">
+      <c r="B59" s="323" t="n">
         <v>-1173.6</v>
       </c>
-      <c r="C59" s="336" t="n">
+      <c r="C59" s="323" t="n">
         <v>-1196.1</v>
       </c>
-      <c r="D59" s="336" t="n">
+      <c r="D59" s="323" t="n">
         <v>384.501</v>
       </c>
-      <c r="E59" s="336" t="n">
+      <c r="E59" s="323" t="n">
         <v>399.406</v>
       </c>
-      <c r="F59" s="336" t="n">
+      <c r="F59" s="323" t="n">
         <v>396.785</v>
       </c>
-      <c r="G59" s="336" t="n">
+      <c r="G59" s="323" t="n">
         <v>394.618</v>
       </c>
       <c r="H59" s="196" t="n"/>
@@ -14626,22 +14187,22 @@
           <t>Tangible Book Value/Share</t>
         </is>
       </c>
-      <c r="B60" s="340" t="n">
+      <c r="B60" s="327" t="n">
         <v>-92.31999999999999</v>
       </c>
-      <c r="C60" s="340" t="n">
+      <c r="C60" s="327" t="n">
         <v>-92.47</v>
       </c>
-      <c r="D60" s="340" t="n">
+      <c r="D60" s="327" t="n">
         <v>4.83</v>
       </c>
-      <c r="E60" s="340" t="n">
+      <c r="E60" s="327" t="n">
         <v>4.92</v>
       </c>
-      <c r="F60" s="340" t="n">
+      <c r="F60" s="327" t="n">
         <v>4.88</v>
       </c>
-      <c r="G60" s="340" t="n">
+      <c r="G60" s="327" t="n">
         <v>4.85</v>
       </c>
       <c r="H60" s="196" t="n"/>
@@ -14652,22 +14213,22 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="B61" s="336" t="n">
+      <c r="B61" s="323" t="n">
         <v>82.60599999999999</v>
       </c>
-      <c r="C61" s="336" t="n">
+      <c r="C61" s="323" t="n">
         <v>88.437</v>
       </c>
-      <c r="D61" s="336" t="n">
+      <c r="D61" s="323" t="n">
         <v>41.515</v>
       </c>
-      <c r="E61" s="336" t="n">
+      <c r="E61" s="323" t="n">
         <v>19.127</v>
       </c>
-      <c r="F61" s="336" t="n">
+      <c r="F61" s="323" t="n">
         <v>19.27</v>
       </c>
-      <c r="G61" s="336" t="n">
+      <c r="G61" s="323" t="n">
         <v>18.025</v>
       </c>
       <c r="H61" s="196" t="n"/>
@@ -14678,22 +14239,22 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="B62" s="336" t="n">
+      <c r="B62" s="323" t="n">
         <v>4.701</v>
       </c>
-      <c r="C62" s="336" t="n">
+      <c r="C62" s="323" t="n">
         <v>10.225</v>
       </c>
-      <c r="D62" s="336" t="n">
+      <c r="D62" s="323" t="n">
         <v>-336.6</v>
       </c>
-      <c r="E62" s="336" t="n">
+      <c r="E62" s="323" t="n">
         <v>-351.8</v>
       </c>
-      <c r="F62" s="336" t="n">
+      <c r="F62" s="323" t="n">
         <v>-328.9</v>
       </c>
-      <c r="G62" s="336" t="n">
+      <c r="G62" s="323" t="n">
         <v>-317.9</v>
       </c>
       <c r="H62" s="196" t="n"/>
@@ -14704,30 +14265,30 @@
           <t>Total Minority Interest</t>
         </is>
       </c>
-      <c r="B63" s="336" t="n">
+      <c r="B63" s="323" t="n">
         <v>-0.8</v>
       </c>
-      <c r="C63" s="336" t="inlineStr">
+      <c r="C63" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D63" s="336" t="inlineStr">
+      <c r="D63" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E63" s="336" t="inlineStr">
+      <c r="E63" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="F63" s="336" t="inlineStr">
+      <c r="F63" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G63" s="336" t="inlineStr">
+      <c r="G63" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -14740,24 +14301,24 @@
           <t>Machinery</t>
         </is>
       </c>
-      <c r="B64" s="336" t="inlineStr">
+      <c r="B64" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C64" s="336" t="n">
+      <c r="C64" s="323" t="n">
         <v>9.388999999999999</v>
       </c>
-      <c r="D64" s="336" t="n">
+      <c r="D64" s="323" t="n">
         <v>9.513</v>
       </c>
-      <c r="E64" s="336" t="n">
+      <c r="E64" s="323" t="n">
         <v>9.909000000000001</v>
       </c>
-      <c r="F64" s="336" t="n">
+      <c r="F64" s="323" t="n">
         <v>10.062</v>
       </c>
-      <c r="G64" s="336" t="n">
+      <c r="G64" s="323" t="n">
         <v>10.355</v>
       </c>
       <c r="H64" s="196" t="n"/>
@@ -14768,24 +14329,24 @@
           <t>Leasehold Improvements</t>
         </is>
       </c>
-      <c r="B65" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="336" t="n">
+      <c r="B65" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="323" t="n">
         <v>1.174</v>
       </c>
-      <c r="D65" s="336" t="n">
+      <c r="D65" s="323" t="n">
         <v>1.254</v>
       </c>
-      <c r="E65" s="336" t="n">
+      <c r="E65" s="323" t="n">
         <v>1.113</v>
       </c>
-      <c r="F65" s="336" t="n">
+      <c r="F65" s="323" t="n">
         <v>1.113</v>
       </c>
-      <c r="G65" s="336" t="n">
+      <c r="G65" s="323" t="n">
         <v>1.128</v>
       </c>
       <c r="H65" s="196" t="n"/>
@@ -14796,28 +14357,28 @@
           <t>Full Time Employees</t>
         </is>
       </c>
-      <c r="B66" s="354" t="inlineStr">
+      <c r="B66" s="341" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C66" s="354" t="n">
+      <c r="C66" s="341" t="n">
         <v>973</v>
       </c>
-      <c r="D66" s="354" t="inlineStr">
+      <c r="D66" s="341" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E66" s="354" t="n">
+      <c r="E66" s="341" t="n">
         <v>1040</v>
       </c>
-      <c r="F66" s="354" t="inlineStr">
+      <c r="F66" s="341" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G66" s="354" t="inlineStr">
+      <c r="G66" s="341" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -14830,24 +14391,24 @@
           <t>Accum. Allowance for Doubtful Accts</t>
         </is>
       </c>
-      <c r="B67" s="336" t="inlineStr">
+      <c r="B67" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C67" s="336" t="n">
+      <c r="C67" s="323" t="n">
         <v>0.01</v>
       </c>
-      <c r="D67" s="336" t="n">
+      <c r="D67" s="323" t="n">
         <v>0.041</v>
       </c>
-      <c r="E67" s="336" t="n">
+      <c r="E67" s="323" t="n">
         <v>0.024</v>
       </c>
-      <c r="F67" s="336" t="n">
+      <c r="F67" s="323" t="n">
         <v>0.01</v>
       </c>
-      <c r="G67" s="336" t="n">
+      <c r="G67" s="323" t="n">
         <v>0.02</v>
       </c>
       <c r="H67" s="196" t="n"/>
@@ -14863,19 +14424,19 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="C68" s="343" t="n">
+      <c r="C68" s="330" t="n">
         <v>46240</v>
       </c>
-      <c r="D68" s="343" t="n">
+      <c r="D68" s="330" t="n">
         <v>45975</v>
       </c>
-      <c r="E68" s="343" t="n">
+      <c r="E68" s="330" t="n">
         <v>46087</v>
       </c>
-      <c r="F68" s="343" t="n">
+      <c r="F68" s="330" t="n">
         <v>46154</v>
       </c>
-      <c r="G68" s="343" t="n">
+      <c r="G68" s="330" t="n">
         <v>46240</v>
       </c>
       <c r="H68" s="196" t="n"/>
@@ -15367,22 +14928,22 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B5" s="338" t="n">
+      <c r="B5" s="325" t="n">
         <v>-16.3</v>
       </c>
-      <c r="C5" s="338" t="n">
+      <c r="C5" s="325" t="n">
         <v>-21.2</v>
       </c>
-      <c r="D5" s="338" t="n">
+      <c r="D5" s="325" t="n">
         <v>-36.9</v>
       </c>
-      <c r="E5" s="338" t="n">
+      <c r="E5" s="325" t="n">
         <v>-21.9</v>
       </c>
-      <c r="F5" s="338" t="n">
+      <c r="F5" s="325" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G5" s="338" t="n">
+      <c r="G5" s="325" t="n">
         <v>-19.6</v>
       </c>
       <c r="H5" s="196" t="n"/>
@@ -15393,22 +14954,22 @@
           <t>Depreciation &amp; Amort.</t>
         </is>
       </c>
-      <c r="B6" s="336" t="n">
+      <c r="B6" s="323" t="n">
         <v>0.983</v>
       </c>
-      <c r="C6" s="336" t="n">
+      <c r="C6" s="323" t="n">
         <v>0.906</v>
       </c>
-      <c r="D6" s="336" t="n">
+      <c r="D6" s="323" t="n">
         <v>1.014</v>
       </c>
-      <c r="E6" s="336" t="n">
+      <c r="E6" s="323" t="n">
         <v>0.968</v>
       </c>
-      <c r="F6" s="336" t="n">
+      <c r="F6" s="323" t="n">
         <v>0.987</v>
       </c>
-      <c r="G6" s="336" t="n">
+      <c r="G6" s="323" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="196" t="n"/>
@@ -15419,22 +14980,22 @@
           <t>Amort. of Goodwill and Intangibles</t>
         </is>
       </c>
-      <c r="B7" s="336" t="n">
+      <c r="B7" s="323" t="n">
         <v>1.299</v>
       </c>
-      <c r="C7" s="336" t="n">
+      <c r="C7" s="323" t="n">
         <v>1.155</v>
       </c>
-      <c r="D7" s="336" t="n">
+      <c r="D7" s="323" t="n">
         <v>1.119</v>
       </c>
-      <c r="E7" s="336" t="n">
+      <c r="E7" s="323" t="n">
         <v>1.085</v>
       </c>
-      <c r="F7" s="336" t="n">
+      <c r="F7" s="323" t="n">
         <v>1.412</v>
       </c>
-      <c r="G7" s="336" t="n">
+      <c r="G7" s="323" t="n">
         <v>1.38</v>
       </c>
       <c r="H7" s="196" t="n"/>
@@ -15445,22 +15006,22 @@
           <t>Depreciation &amp; Amort., Total</t>
         </is>
       </c>
-      <c r="B8" s="337" t="n">
+      <c r="B8" s="324" t="n">
         <v>2.282</v>
       </c>
-      <c r="C8" s="337" t="n">
+      <c r="C8" s="324" t="n">
         <v>2.061</v>
       </c>
-      <c r="D8" s="337" t="n">
+      <c r="D8" s="324" t="n">
         <v>2.133</v>
       </c>
-      <c r="E8" s="337" t="n">
+      <c r="E8" s="324" t="n">
         <v>2.053</v>
       </c>
-      <c r="F8" s="337" t="n">
+      <c r="F8" s="324" t="n">
         <v>2.399</v>
       </c>
-      <c r="G8" s="337" t="n">
+      <c r="G8" s="324" t="n">
         <v>2.38</v>
       </c>
       <c r="H8" s="196" t="n"/>
@@ -15481,24 +15042,24 @@
           <t>Other Amortization</t>
         </is>
       </c>
-      <c r="B10" s="336" t="n">
+      <c r="B10" s="323" t="n">
         <v>1.618</v>
       </c>
-      <c r="C10" s="336" t="n">
+      <c r="C10" s="323" t="n">
         <v>1.71</v>
       </c>
-      <c r="D10" s="336" t="n">
+      <c r="D10" s="323" t="n">
         <v>1.491</v>
       </c>
-      <c r="E10" s="336" t="n">
+      <c r="E10" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="336" t="inlineStr">
+      <c r="F10" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -15511,22 +15072,22 @@
           <t>Stock-Based Compensation</t>
         </is>
       </c>
-      <c r="B11" s="336" t="n">
+      <c r="B11" s="323" t="n">
         <v>4.691</v>
       </c>
-      <c r="C11" s="336" t="n">
+      <c r="C11" s="323" t="n">
         <v>4.662</v>
       </c>
-      <c r="D11" s="336" t="n">
+      <c r="D11" s="323" t="n">
         <v>6.592</v>
       </c>
-      <c r="E11" s="336" t="n">
+      <c r="E11" s="323" t="n">
         <v>14.396</v>
       </c>
-      <c r="F11" s="336" t="n">
+      <c r="F11" s="323" t="n">
         <v>15.564</v>
       </c>
-      <c r="G11" s="336" t="n">
+      <c r="G11" s="323" t="n">
         <v>16.01</v>
       </c>
       <c r="H11" s="196" t="n"/>
@@ -15537,22 +15098,22 @@
           <t>Other Operating Activities</t>
         </is>
       </c>
-      <c r="B12" s="336" t="n">
+      <c r="B12" s="323" t="n">
         <v>0.708</v>
       </c>
-      <c r="C12" s="336" t="n">
+      <c r="C12" s="323" t="n">
         <v>5.237</v>
       </c>
-      <c r="D12" s="336" t="n">
+      <c r="D12" s="323" t="n">
         <v>17.7</v>
       </c>
-      <c r="E12" s="336" t="n">
+      <c r="E12" s="323" t="n">
         <v>3.264</v>
       </c>
-      <c r="F12" s="336" t="n">
+      <c r="F12" s="323" t="n">
         <v>3.376</v>
       </c>
-      <c r="G12" s="336" t="n">
+      <c r="G12" s="323" t="n">
         <v>2.853</v>
       </c>
       <c r="H12" s="196" t="n"/>
@@ -15563,22 +15124,22 @@
           <t>Change in Acc. Receivable</t>
         </is>
       </c>
-      <c r="B13" s="336" t="n">
+      <c r="B13" s="323" t="n">
         <v>-0.5</v>
       </c>
-      <c r="C13" s="336" t="n">
+      <c r="C13" s="323" t="n">
         <v>-5.8</v>
       </c>
-      <c r="D13" s="336" t="n">
+      <c r="D13" s="323" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E13" s="336" t="n">
+      <c r="E13" s="323" t="n">
         <v>6.615</v>
       </c>
-      <c r="F13" s="336" t="n">
+      <c r="F13" s="323" t="n">
         <v>-13.8</v>
       </c>
-      <c r="G13" s="336" t="n">
+      <c r="G13" s="323" t="n">
         <v>-9.9</v>
       </c>
       <c r="H13" s="196" t="n"/>
@@ -15589,22 +15150,22 @@
           <t>Change in Acc. Payable</t>
         </is>
       </c>
-      <c r="B14" s="336" t="n">
+      <c r="B14" s="323" t="n">
         <v>2.455</v>
       </c>
-      <c r="C14" s="336" t="n">
+      <c r="C14" s="323" t="n">
         <v>0.365</v>
       </c>
-      <c r="D14" s="336" t="n">
+      <c r="D14" s="323" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E14" s="336" t="n">
+      <c r="E14" s="323" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F14" s="336" t="n">
+      <c r="F14" s="323" t="n">
         <v>2.818</v>
       </c>
-      <c r="G14" s="336" t="n">
+      <c r="G14" s="323" t="n">
         <v>-1.2</v>
       </c>
       <c r="H14" s="196" t="n"/>
@@ -15862,22 +15423,22 @@
           <t>Change in Unearned Rev.</t>
         </is>
       </c>
-      <c r="B15" s="336" t="n">
+      <c r="B15" s="323" t="n">
         <v>-1</v>
       </c>
-      <c r="C15" s="336" t="n">
+      <c r="C15" s="323" t="n">
         <v>-1.6</v>
       </c>
-      <c r="D15" s="336" t="n">
+      <c r="D15" s="323" t="n">
         <v>2.672</v>
       </c>
-      <c r="E15" s="336" t="n">
+      <c r="E15" s="323" t="n">
         <v>0.272</v>
       </c>
-      <c r="F15" s="336" t="n">
+      <c r="F15" s="323" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G15" s="336" t="n">
+      <c r="G15" s="323" t="n">
         <v>-1.4</v>
       </c>
       <c r="H15" s="196" t="n"/>
@@ -15888,22 +15449,22 @@
           <t>Change in Other Net Operating Assets</t>
         </is>
       </c>
-      <c r="B16" s="336" t="n">
+      <c r="B16" s="323" t="n">
         <v>0.401</v>
       </c>
-      <c r="C16" s="336" t="n">
+      <c r="C16" s="323" t="n">
         <v>-1.7</v>
       </c>
-      <c r="D16" s="336" t="n">
+      <c r="D16" s="323" t="n">
         <v>1.083</v>
       </c>
-      <c r="E16" s="336" t="n">
+      <c r="E16" s="323" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F16" s="336" t="n">
+      <c r="F16" s="323" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="G16" s="336" t="n">
+      <c r="G16" s="323" t="n">
         <v>0.073</v>
       </c>
       <c r="H16" s="196" t="n"/>
@@ -15914,22 +15475,22 @@
           <t xml:space="preserve">  Cash from Ops.</t>
         </is>
       </c>
-      <c r="B17" s="337" t="n">
+      <c r="B17" s="324" t="n">
         <v>-5.6</v>
       </c>
-      <c r="C17" s="337" t="n">
+      <c r="C17" s="324" t="n">
         <v>-16.3</v>
       </c>
-      <c r="D17" s="337" t="n">
+      <c r="D17" s="324" t="n">
         <v>-8.5</v>
       </c>
-      <c r="E17" s="337" t="n">
+      <c r="E17" s="324" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F17" s="337" t="n">
+      <c r="F17" s="324" t="n">
         <v>-21.2</v>
       </c>
-      <c r="G17" s="337" t="n">
+      <c r="G17" s="324" t="n">
         <v>-10.6</v>
       </c>
       <c r="H17" s="196" t="n"/>
@@ -15950,22 +15511,22 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B19" s="336" t="n">
+      <c r="B19" s="323" t="n">
         <v>-0.4</v>
       </c>
-      <c r="C19" s="336" t="n">
+      <c r="C19" s="323" t="n">
         <v>-0.6</v>
       </c>
-      <c r="D19" s="336" t="n">
+      <c r="D19" s="323" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E19" s="336" t="n">
+      <c r="E19" s="323" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F19" s="336" t="n">
+      <c r="F19" s="323" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G19" s="336" t="n">
+      <c r="G19" s="323" t="n">
         <v>-0.4</v>
       </c>
       <c r="H19" s="196" t="n"/>
@@ -15976,30 +15537,30 @@
           <t>Cash Acquisitions</t>
         </is>
       </c>
-      <c r="B20" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="336" t="n">
+      <c r="B20" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="323" t="n">
         <v>-39.9</v>
       </c>
-      <c r="F20" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="336" t="n">
+      <c r="F20" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="323" t="n">
         <v>0.279</v>
       </c>
       <c r="H20" s="196" t="n"/>
@@ -16010,32 +15571,32 @@
           <t>Divestitures</t>
         </is>
       </c>
-      <c r="B21" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="336" t="inlineStr">
+      <c r="B21" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16048,22 +15609,22 @@
           <t>Sale (Purchase) of Intangible assets</t>
         </is>
       </c>
-      <c r="B22" s="336" t="n">
+      <c r="B22" s="323" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C22" s="336" t="n">
+      <c r="C22" s="323" t="n">
         <v>-1.2</v>
       </c>
-      <c r="D22" s="336" t="n">
+      <c r="D22" s="323" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E22" s="336" t="n">
+      <c r="E22" s="323" t="n">
         <v>-1</v>
       </c>
-      <c r="F22" s="336" t="n">
+      <c r="F22" s="323" t="n">
         <v>-2</v>
       </c>
-      <c r="G22" s="336" t="n">
+      <c r="G22" s="323" t="n">
         <v>-2</v>
       </c>
       <c r="H22" s="196" t="n"/>
@@ -16074,32 +15635,32 @@
           <t>Invest. in Marketable &amp; Equity Securt.</t>
         </is>
       </c>
-      <c r="B23" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="336" t="inlineStr">
+      <c r="B23" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16112,32 +15673,32 @@
           <t>Net (Inc.) Dec. in Loans Originated/Sold</t>
         </is>
       </c>
-      <c r="B24" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="336" t="inlineStr">
+      <c r="B24" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16150,32 +15711,32 @@
           <t>Other Investing Activities</t>
         </is>
       </c>
-      <c r="B25" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="336" t="inlineStr">
+      <c r="B25" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16188,22 +15749,22 @@
           <t xml:space="preserve">  Cash from Investing</t>
         </is>
       </c>
-      <c r="B26" s="337" t="n">
+      <c r="B26" s="324" t="n">
         <v>-1.3</v>
       </c>
-      <c r="C26" s="337" t="n">
+      <c r="C26" s="324" t="n">
         <v>-1.8</v>
       </c>
-      <c r="D26" s="337" t="n">
+      <c r="D26" s="324" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E26" s="337" t="n">
+      <c r="E26" s="324" t="n">
         <v>-41.2</v>
       </c>
-      <c r="F26" s="337" t="n">
+      <c r="F26" s="324" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G26" s="337" t="n">
+      <c r="G26" s="324" t="n">
         <v>-2.1</v>
       </c>
       <c r="H26" s="196" t="n"/>
@@ -16224,32 +15785,32 @@
           <t>Short Term Debt Issued</t>
         </is>
       </c>
-      <c r="B28" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="336" t="inlineStr">
+      <c r="B28" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16262,30 +15823,30 @@
           <t>Long-Term Debt Issued</t>
         </is>
       </c>
-      <c r="B29" s="336" t="n">
+      <c r="B29" s="323" t="n">
         <v>7.5</v>
       </c>
-      <c r="C29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="336" t="inlineStr">
+      <c r="C29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16298,24 +15859,24 @@
           <t>Total Debt Issued</t>
         </is>
       </c>
-      <c r="B30" s="337" t="n">
+      <c r="B30" s="324" t="n">
         <v>7.5</v>
       </c>
-      <c r="C30" s="337" t="n">
+      <c r="C30" s="324" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="337" t="n">
+      <c r="D30" s="324" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="337" t="n">
+      <c r="E30" s="324" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="337" t="inlineStr">
+      <c r="F30" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="324" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16328,32 +15889,32 @@
           <t>Short Term Debt Repaid</t>
         </is>
       </c>
-      <c r="B31" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="336" t="inlineStr">
+      <c r="B31" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C31" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16366,30 +15927,30 @@
           <t>Long-Term Debt Repaid</t>
         </is>
       </c>
-      <c r="B32" s="336" t="n">
+      <c r="B32" s="323" t="n">
         <v>-5</v>
       </c>
-      <c r="C32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="336" t="inlineStr">
+      <c r="C32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16402,24 +15963,24 @@
           <t>Total Debt Repaid</t>
         </is>
       </c>
-      <c r="B33" s="337" t="n">
+      <c r="B33" s="324" t="n">
         <v>-5</v>
       </c>
-      <c r="C33" s="337" t="n">
+      <c r="C33" s="324" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="337" t="n">
+      <c r="D33" s="324" t="n">
         <v>-5</v>
       </c>
-      <c r="E33" s="337" t="n">
+      <c r="E33" s="324" t="n">
         <v>-25</v>
       </c>
-      <c r="F33" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="337" t="inlineStr">
+      <c r="F33" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="324" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16442,22 +16003,22 @@
           <t>Issuance of Common Stock</t>
         </is>
       </c>
-      <c r="B35" s="336" t="n">
+      <c r="B35" s="323" t="n">
         <v>0.68</v>
       </c>
-      <c r="C35" s="336" t="n">
+      <c r="C35" s="323" t="n">
         <v>1.374</v>
       </c>
-      <c r="D35" s="336" t="n">
+      <c r="D35" s="323" t="n">
         <v>314.718</v>
       </c>
-      <c r="E35" s="336" t="n">
+      <c r="E35" s="323" t="n">
         <v>63.388</v>
       </c>
-      <c r="F35" s="336" t="n">
+      <c r="F35" s="323" t="n">
         <v>0.996</v>
       </c>
-      <c r="G35" s="336" t="n">
+      <c r="G35" s="323" t="n">
         <v>0.695</v>
       </c>
       <c r="H35" s="196" t="n"/>
@@ -16468,24 +16029,24 @@
           <t>Issuance of Pref. Stock</t>
         </is>
       </c>
-      <c r="B36" s="336" t="n">
+      <c r="B36" s="323" t="n">
         <v>20</v>
       </c>
-      <c r="C36" s="336" t="n">
+      <c r="C36" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="336" t="n">
+      <c r="D36" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="336" t="n">
+      <c r="E36" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="336" t="inlineStr">
+      <c r="F36" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16508,32 +16069,32 @@
           <t>Total Dividends Paid</t>
         </is>
       </c>
-      <c r="B38" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="337" t="inlineStr">
+      <c r="B38" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="324" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16556,32 +16117,32 @@
           <t>Special Dividend Paid</t>
         </is>
       </c>
-      <c r="B40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="336" t="inlineStr">
+      <c r="B40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16594,24 +16155,24 @@
           <t>Other Financing Activities</t>
         </is>
       </c>
-      <c r="B41" s="336" t="n">
+      <c r="B41" s="323" t="n">
         <v>-0.3</v>
       </c>
-      <c r="C41" s="336" t="n">
+      <c r="C41" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="336" t="n">
+      <c r="D41" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="336" t="n">
+      <c r="E41" s="323" t="n">
         <v>-4</v>
       </c>
-      <c r="F41" s="336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="336" t="inlineStr">
+      <c r="F41" s="323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16624,22 +16185,22 @@
           <t xml:space="preserve">  Cash from Financing</t>
         </is>
       </c>
-      <c r="B42" s="337" t="n">
+      <c r="B42" s="324" t="n">
         <v>22.858</v>
       </c>
-      <c r="C42" s="337" t="n">
+      <c r="C42" s="324" t="n">
         <v>1.374</v>
       </c>
-      <c r="D42" s="337" t="n">
+      <c r="D42" s="324" t="n">
         <v>309.718</v>
       </c>
-      <c r="E42" s="337" t="n">
+      <c r="E42" s="324" t="n">
         <v>34.376</v>
       </c>
-      <c r="F42" s="337" t="n">
+      <c r="F42" s="324" t="n">
         <v>0.996</v>
       </c>
-      <c r="G42" s="337" t="n">
+      <c r="G42" s="324" t="n">
         <v>0.695</v>
       </c>
       <c r="H42" s="196" t="n"/>
@@ -16660,22 +16221,22 @@
           <t>Foreign Exchange Rate Adj.</t>
         </is>
       </c>
-      <c r="B44" s="336" t="n">
+      <c r="B44" s="323" t="n">
         <v>0.322</v>
       </c>
-      <c r="C44" s="336" t="n">
+      <c r="C44" s="323" t="n">
         <v>0.743</v>
       </c>
-      <c r="D44" s="336" t="n">
+      <c r="D44" s="323" t="n">
         <v>0.261</v>
       </c>
-      <c r="E44" s="336" t="n">
+      <c r="E44" s="323" t="n">
         <v>0.119</v>
       </c>
-      <c r="F44" s="336" t="n">
+      <c r="F44" s="323" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G44" s="336" t="n">
+      <c r="G44" s="323" t="n">
         <v>-0.1</v>
       </c>
       <c r="H44" s="196" t="n"/>
@@ -16686,22 +16247,22 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B45" s="339" t="n">
+      <c r="B45" s="326" t="n">
         <v>16.324</v>
       </c>
-      <c r="C45" s="339" t="n">
+      <c r="C45" s="326" t="n">
         <v>-16</v>
       </c>
-      <c r="D45" s="339" t="n">
+      <c r="D45" s="326" t="n">
         <v>299.991</v>
       </c>
-      <c r="E45" s="339" t="n">
+      <c r="E45" s="326" t="n">
         <v>-7.2</v>
       </c>
-      <c r="F45" s="339" t="n">
+      <c r="F45" s="326" t="n">
         <v>-22.7</v>
       </c>
-      <c r="G45" s="339" t="n">
+      <c r="G45" s="326" t="n">
         <v>-12.2</v>
       </c>
       <c r="H45" s="196" t="n"/>
@@ -16736,24 +16297,24 @@
           <t>Cash Interest Paid</t>
         </is>
       </c>
-      <c r="B48" s="336" t="n">
+      <c r="B48" s="323" t="n">
         <v>0.796</v>
       </c>
-      <c r="C48" s="336" t="n">
+      <c r="C48" s="323" t="n">
         <v>0.642</v>
       </c>
-      <c r="D48" s="336" t="n">
+      <c r="D48" s="323" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="E48" s="336" t="n">
+      <c r="E48" s="323" t="n">
         <v>0.529</v>
       </c>
-      <c r="F48" s="336" t="inlineStr">
+      <c r="F48" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G48" s="336" t="n">
+      <c r="G48" s="323" t="n">
         <v>0.41</v>
       </c>
       <c r="H48" s="196" t="n"/>
@@ -16764,22 +16325,22 @@
           <t>Cash Taxes Paid</t>
         </is>
       </c>
-      <c r="B49" s="336" t="n">
+      <c r="B49" s="323" t="n">
         <v>0.328</v>
       </c>
-      <c r="C49" s="336" t="n">
+      <c r="C49" s="323" t="n">
         <v>0.59</v>
       </c>
-      <c r="D49" s="336" t="n">
+      <c r="D49" s="323" t="n">
         <v>2.24</v>
       </c>
-      <c r="E49" s="336" t="n">
+      <c r="E49" s="323" t="n">
         <v>0.26</v>
       </c>
-      <c r="F49" s="336" t="n">
+      <c r="F49" s="323" t="n">
         <v>0.311</v>
       </c>
-      <c r="G49" s="336" t="n">
+      <c r="G49" s="323" t="n">
         <v>0.483</v>
       </c>
       <c r="H49" s="196" t="n"/>
@@ -16790,26 +16351,26 @@
           <t>Levered Free Cash Flow</t>
         </is>
       </c>
-      <c r="B50" s="336" t="inlineStr">
+      <c r="B50" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C50" s="336" t="inlineStr">
+      <c r="C50" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D50" s="336" t="n">
+      <c r="D50" s="323" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E50" s="336" t="n">
+      <c r="E50" s="323" t="n">
         <v>1.61575</v>
       </c>
-      <c r="F50" s="336" t="n">
+      <c r="F50" s="323" t="n">
         <v>-17.5</v>
       </c>
-      <c r="G50" s="336" t="n">
+      <c r="G50" s="323" t="n">
         <v>-6.7</v>
       </c>
       <c r="H50" s="196" t="n"/>
@@ -16820,26 +16381,26 @@
           <t>Unlevered Free Cash Flow</t>
         </is>
       </c>
-      <c r="B51" s="336" t="inlineStr">
+      <c r="B51" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C51" s="336" t="inlineStr">
+      <c r="C51" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D51" s="336" t="n">
+      <c r="D51" s="323" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E51" s="336" t="n">
+      <c r="E51" s="323" t="n">
         <v>1.847625</v>
       </c>
-      <c r="F51" s="336" t="n">
+      <c r="F51" s="323" t="n">
         <v>-17.3</v>
       </c>
-      <c r="G51" s="336" t="n">
+      <c r="G51" s="323" t="n">
         <v>-6.5</v>
       </c>
       <c r="H51" s="196" t="n"/>
@@ -16850,26 +16411,26 @@
           <t>Change in Net Working Capital</t>
         </is>
       </c>
-      <c r="B52" s="336" t="inlineStr">
+      <c r="B52" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="C52" s="336" t="inlineStr">
+      <c r="C52" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D52" s="336" t="n">
+      <c r="D52" s="323" t="n">
         <v>-4.3</v>
       </c>
-      <c r="E52" s="336" t="n">
+      <c r="E52" s="323" t="n">
         <v>-2</v>
       </c>
-      <c r="F52" s="336" t="n">
+      <c r="F52" s="323" t="n">
         <v>18.266</v>
       </c>
-      <c r="G52" s="336" t="n">
+      <c r="G52" s="323" t="n">
         <v>8.907</v>
       </c>
       <c r="H52" s="196" t="n"/>
@@ -16880,24 +16441,24 @@
           <t>Net Debt Issued</t>
         </is>
       </c>
-      <c r="B53" s="336" t="n">
+      <c r="B53" s="323" t="n">
         <v>2.5</v>
       </c>
-      <c r="C53" s="336" t="n">
+      <c r="C53" s="323" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="336" t="n">
+      <c r="D53" s="323" t="n">
         <v>-5</v>
       </c>
-      <c r="E53" s="336" t="n">
+      <c r="E53" s="323" t="n">
         <v>-25</v>
       </c>
-      <c r="F53" s="336" t="inlineStr">
+      <c r="F53" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G53" s="336" t="inlineStr">
+      <c r="G53" s="323" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -16910,22 +16471,22 @@
           <t>Filing Date</t>
         </is>
       </c>
-      <c r="B54" s="343" t="n">
+      <c r="B54" s="330" t="n">
         <v>46154</v>
       </c>
-      <c r="C54" s="343" t="n">
+      <c r="C54" s="330" t="n">
         <v>46240</v>
       </c>
-      <c r="D54" s="343" t="n">
+      <c r="D54" s="330" t="n">
         <v>45975</v>
       </c>
-      <c r="E54" s="343" t="n">
+      <c r="E54" s="330" t="n">
         <v>46087</v>
       </c>
-      <c r="F54" s="343" t="n">
+      <c r="F54" s="330" t="n">
         <v>46154</v>
       </c>
-      <c r="G54" s="343" t="n">
+      <c r="G54" s="330" t="n">
         <v>46240</v>
       </c>
       <c r="H54" s="196" t="n"/>

--- a/model/CX_VIA_Model.xlsx
+++ b/model/CX_VIA_Model.xlsx
@@ -1430,57 +1430,57 @@
         <t>Historical total revenue links to Annual IS (CapIQ).</t>
       </text>
     </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
+    <comment ref="F19" authorId="0" shapeId="0">
       <text>
         <t>Organic customer growth ~9% ex-Downtowner (thesis 3), ~+2%/yr price. FY26 +3%: 94 small Downtowner customers add little. Software fees face near-zero bids (Spare bid $0.01 at LA Metro).</t>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
+    <comment ref="F20" authorId="0" shapeId="0">
       <text>
-        <t>Expansion at existing customers less budget-driven downsell (~4%/yr: Jersey City cut ~half, federal stopgap / ARPA cliff), with price +2%/yr as rebids reset rates. FY26 +28% ties to 1H26 actuals ($263M revenue) plus the H2 ramp.</t>
+        <t>Pilots are budget-bound (thesis 3): expansion at existing customers less downsell (Jersey City cut ~half; federal stopgap / ARPA cliff), price +2%/yr as rebids reset rates. Growth shifts to network deals. FY26 +28% ties to 1H26 actuals ($263M revenue) plus the H2 ramp.</t>
       </text>
     </comment>
-    <comment ref="F19" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="0" shapeId="0">
       <text>
-        <t>FY26: Twin Cities MI (Apr), Rochester $14.6M (Sep) and part of the 2026 wins; FY27: rest of the signed ~$70M book. Then ~2 mid-sized cities a year (thesis 1.1). Earned at half rate in the launch year.</t>
+        <t>The growth engine (thesis 1). FY26: Twin Cities MI (Apr), Rochester $14.6M (Sep), part of the 2026 wins. FY27: rest of the signed ~$70M book (~$27M) plus new wins. FY28+: the &gt;$700M pipeline (doubled YoY) converting at ~8-11% a year, ~5-7 mid-sized cities at $10-15M each. Earned at half rate in the launch year.</t>
       </text>
     </comment>
-    <comment ref="D20" authorId="0" shapeId="0">
+    <comment ref="D22" authorId="0" shapeId="0">
       <text>
         <t>Sioux Falls: 2024 NTD purchased transportation paid $11.07M (Via's first network deal).</t>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0">
+    <comment ref="E22" authorId="0" shapeId="0">
       <text>
         <t>Sioux Falls ~$11.4M + Mobile $12.1M/yr (from Oct 2025).</t>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
+    <comment ref="E23" authorId="0" shapeId="0">
       <text>
         <t>10-K: one-time revenue 3% of total in FY24 and FY25 (97% recurring). FY23 assumed the same.</t>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="0" shapeId="0">
       <text>
         <t>3% (10-K FY24-25; 1H26 also 3%).</t>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
+    <comment ref="F26" authorId="0" shapeId="0">
       <text>
         <t>Bleecker assumption; reported cost split implies ~73%.</t>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F27" authorId="0" shapeId="0">
       <text>
         <t>Bleecker TaaS gross margin, arithmetic corrected and updated to 2026 contract pricing.</t>
       </text>
     </comment>
-    <comment ref="F26" authorId="0" shapeId="0">
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <t>ASSUMPTION (undisclosed): operator economics, below the ~29% on microtransit. Labor is 72% of mid-sized bus system cost (NTD 2024); CFO: 'some accretive, some less.'</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0">
+    <comment ref="F29" authorId="0" shapeId="0">
       <text>
         <t>Implementation / consulting.</t>
       </text>
@@ -2945,23 +2945,23 @@
         <v/>
       </c>
       <c r="F32" s="257">
-        <f>1-'Revenue Build'!F29</f>
+        <f>1-'Revenue Build'!F31</f>
         <v/>
       </c>
       <c r="G32" s="258">
-        <f>1-'Revenue Build'!G29</f>
+        <f>1-'Revenue Build'!G31</f>
         <v/>
       </c>
       <c r="H32" s="258">
-        <f>1-'Revenue Build'!H29</f>
+        <f>1-'Revenue Build'!H31</f>
         <v/>
       </c>
       <c r="I32" s="258">
-        <f>1-'Revenue Build'!I29</f>
+        <f>1-'Revenue Build'!I31</f>
         <v/>
       </c>
       <c r="J32" s="258">
-        <f>1-'Revenue Build'!J29</f>
+        <f>1-'Revenue Build'!J31</f>
         <v/>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -5588,23 +5588,23 @@
         <v>101.1</v>
       </c>
       <c r="F4" s="276">
-        <f>E4*(1+F17)</f>
+        <f>E4*(1+F19)</f>
         <v/>
       </c>
       <c r="G4" s="276">
-        <f>F4*(1+G17)</f>
+        <f>F4*(1+G19)</f>
         <v/>
       </c>
       <c r="H4" s="276">
-        <f>G4*(1+H17)</f>
+        <f>G4*(1+H19)</f>
         <v/>
       </c>
       <c r="I4" s="276">
-        <f>H4*(1+I17)</f>
+        <f>H4*(1+I19)</f>
         <v/>
       </c>
       <c r="J4" s="276">
-        <f>I4*(1+J17)</f>
+        <f>I4*(1+J19)</f>
         <v/>
       </c>
     </row>
@@ -5666,23 +5666,23 @@
         <v/>
       </c>
       <c r="F6" s="276">
-        <f>E6*(1+F18)</f>
+        <f>E6*(1+F20)</f>
         <v/>
       </c>
       <c r="G6" s="276">
-        <f>F6*(1+G18)</f>
+        <f>F6*(1+G20)</f>
         <v/>
       </c>
       <c r="H6" s="276">
-        <f>G6*(1+H18)</f>
+        <f>G6*(1+H20)</f>
         <v/>
       </c>
       <c r="I6" s="276">
-        <f>H6*(1+I18)</f>
+        <f>H6*(1+I20)</f>
         <v/>
       </c>
       <c r="J6" s="276">
-        <f>I6*(1+J18)</f>
+        <f>I6*(1+J20)</f>
         <v/>
       </c>
     </row>
@@ -5702,23 +5702,23 @@
         <v>14.4</v>
       </c>
       <c r="F7" s="276">
-        <f>E20+0.5*F19</f>
+        <f>E22+0.5*F21</f>
         <v/>
       </c>
       <c r="G7" s="276">
-        <f>F20+0.5*G19</f>
+        <f>F22+0.5*G21</f>
         <v/>
       </c>
       <c r="H7" s="276">
-        <f>G20+0.5*H19</f>
+        <f>G22+0.5*H21</f>
         <v/>
       </c>
       <c r="I7" s="276">
-        <f>H20+0.5*I19</f>
+        <f>H22+0.5*I21</f>
         <v/>
       </c>
       <c r="J7" s="276">
-        <f>I20+0.5*J19</f>
+        <f>I22+0.5*J21</f>
         <v/>
       </c>
     </row>
@@ -5729,35 +5729,35 @@
         </is>
       </c>
       <c r="C8" s="274">
-        <f>C9*C21</f>
+        <f>C9*C23</f>
         <v/>
       </c>
       <c r="D8" s="274">
-        <f>D9*D21</f>
+        <f>D9*D23</f>
         <v/>
       </c>
       <c r="E8" s="275">
-        <f>E9*E21</f>
+        <f>E9*E23</f>
         <v/>
       </c>
       <c r="F8" s="276">
-        <f>(F4+F5)*F21/(1-F21)</f>
+        <f>(F4+F5)*F23/(1-F23)</f>
         <v/>
       </c>
       <c r="G8" s="276">
-        <f>(G4+G5)*G21/(1-G21)</f>
+        <f>(G4+G5)*G23/(1-G23)</f>
         <v/>
       </c>
       <c r="H8" s="276">
-        <f>(H4+H5)*H21/(1-H21)</f>
+        <f>(H4+H5)*H23/(1-H23)</f>
         <v/>
       </c>
       <c r="I8" s="276">
-        <f>(I4+I5)*I21/(1-I21)</f>
+        <f>(I4+I5)*I23/(1-I23)</f>
         <v/>
       </c>
       <c r="J8" s="276">
-        <f>(J4+J5)*J21/(1-J21)</f>
+        <f>(J4+J5)*J23/(1-J23)</f>
         <v/>
       </c>
     </row>
@@ -5963,445 +5963,517 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="12.75" customHeight="1"/>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Network deals % of revenue</t>
+        </is>
+      </c>
+      <c r="C15" s="259">
+        <f>C7/C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="259">
+        <f>D7/D9</f>
+        <v/>
+      </c>
+      <c r="E15" s="260">
+        <f>E7/E9</f>
+        <v/>
+      </c>
+      <c r="F15" s="292">
+        <f>F7/F9</f>
+        <v/>
+      </c>
+      <c r="G15" s="292">
+        <f>G7/G9</f>
+        <v/>
+      </c>
+      <c r="H15" s="292">
+        <f>H7/H9</f>
+        <v/>
+      </c>
+      <c r="I15" s="292">
+        <f>I7/I9</f>
+        <v/>
+      </c>
+      <c r="J15" s="292">
+        <f>J7/J9</f>
+        <v/>
+      </c>
+    </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Network deals share of revenue growth</t>
+        </is>
+      </c>
+      <c r="C16" s="259" t="n"/>
+      <c r="D16" s="259">
+        <f>(D7-C7)/(D9-C9)</f>
+        <v/>
+      </c>
+      <c r="E16" s="260">
+        <f>(E7-D7)/(E9-D9)</f>
+        <v/>
+      </c>
+      <c r="F16" s="292">
+        <f>(F7-E7)/(F9-E9)</f>
+        <v/>
+      </c>
+      <c r="G16" s="292">
+        <f>(G7-F7)/(G9-F9)</f>
+        <v/>
+      </c>
+      <c r="H16" s="292">
+        <f>(H7-G7)/(H9-G9)</f>
+        <v/>
+      </c>
+      <c r="I16" s="292">
+        <f>(I7-H7)/(I9-H9)</f>
+        <v/>
+      </c>
+      <c r="J16" s="292">
+        <f>(J7-I7)/(J9-I9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="12.75" customFormat="1" customHeight="1" s="8"/>
+    <row r="18" ht="12.75" customHeight="1">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t>DRIVERS</t>
         </is>
       </c>
-      <c r="C16" s="293" t="n"/>
-      <c r="D16" s="294" t="n"/>
-      <c r="E16" s="295" t="n"/>
-      <c r="F16" s="296" t="n"/>
-      <c r="G16" s="296" t="n"/>
-      <c r="H16" s="296" t="n"/>
-      <c r="I16" s="296" t="n"/>
-      <c r="J16" s="296" t="n"/>
-    </row>
-    <row r="17" ht="12.75" customFormat="1" customHeight="1" s="8">
-      <c r="B17" s="85" t="inlineStr">
-        <is>
-          <t>Software revenue % growth</t>
-        </is>
-      </c>
-      <c r="C17" s="297" t="n"/>
-      <c r="D17" s="297">
-        <f>D4/C4-1</f>
-        <v/>
-      </c>
-      <c r="E17" s="298">
-        <f>E4/D4-1</f>
-        <v/>
-      </c>
-      <c r="F17" s="299" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G17" s="300" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H17" s="300" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" s="300" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J17" s="301" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="18" ht="12.75" customHeight="1">
-      <c r="B18" s="85" t="inlineStr">
-        <is>
-          <t>Microtransit &amp; paratransit % growth (net of downsell)</t>
-        </is>
-      </c>
-      <c r="C18" s="297" t="n"/>
-      <c r="D18" s="297">
-        <f>D6/C6-1</f>
-        <v/>
-      </c>
-      <c r="E18" s="298">
-        <f>E6/D6-1</f>
-        <v/>
-      </c>
-      <c r="F18" s="299" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G18" s="300" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H18" s="300" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I18" s="300" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J18" s="301" t="n">
-        <v>0.11</v>
-      </c>
+      <c r="C18" s="293" t="n"/>
+      <c r="D18" s="294" t="n"/>
+      <c r="E18" s="295" t="n"/>
+      <c r="F18" s="296" t="n"/>
+      <c r="G18" s="296" t="n"/>
+      <c r="H18" s="296" t="n"/>
+      <c r="I18" s="296" t="n"/>
+      <c r="J18" s="296" t="n"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="B19" s="85" t="inlineStr">
         <is>
-          <t>Network: new contract value launched ($mm)</t>
-        </is>
-      </c>
-      <c r="C19" s="302" t="n"/>
-      <c r="D19" s="302">
-        <f>D20-C20</f>
-        <v/>
-      </c>
-      <c r="E19" s="303">
-        <f>E20-D20</f>
-        <v/>
-      </c>
-      <c r="F19" s="304" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" s="305" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="305" t="n">
-        <v>20</v>
-      </c>
-      <c r="I19" s="305" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" s="306" t="n">
-        <v>20</v>
+          <t>Software revenue % growth</t>
+        </is>
+      </c>
+      <c r="C19" s="297" t="n"/>
+      <c r="D19" s="297">
+        <f>D4/C4-1</f>
+        <v/>
+      </c>
+      <c r="E19" s="298">
+        <f>E4/D4-1</f>
+        <v/>
+      </c>
+      <c r="F19" s="299" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G19" s="300" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H19" s="300" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="300" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J19" s="301" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Network: contract run-rate, year-end ($mm)</t>
-        </is>
-      </c>
-      <c r="C20" s="307" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="307" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" s="308" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F20" s="302">
-        <f>E20+F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="302">
-        <f>F20+G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="302">
-        <f>G20+H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="302">
-        <f>H20+I19</f>
-        <v/>
-      </c>
-      <c r="J20" s="302">
-        <f>I20+J19</f>
-        <v/>
+      <c r="B20" s="85" t="inlineStr">
+        <is>
+          <t>Microtransit &amp; paratransit % growth (net of downsell)</t>
+        </is>
+      </c>
+      <c r="C20" s="297" t="n"/>
+      <c r="D20" s="297">
+        <f>D6/C6-1</f>
+        <v/>
+      </c>
+      <c r="E20" s="298">
+        <f>E6/D6-1</f>
+        <v/>
+      </c>
+      <c r="F20" s="299" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G20" s="300" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="300" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I20" s="300" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J20" s="301" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="21" ht="12.75" customFormat="1" customHeight="1" s="29">
       <c r="B21" s="85" t="inlineStr">
         <is>
-          <t>One-time revenue % of total</t>
-        </is>
-      </c>
-      <c r="C21" s="309" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D21" s="309" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E21" s="223" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F21" s="299" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G21" s="300" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H21" s="300" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I21" s="300" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J21" s="301" t="n">
-        <v>0.03</v>
+          <t>Network: new contract value launched ($mm)</t>
+        </is>
+      </c>
+      <c r="C21" s="302" t="n"/>
+      <c r="D21" s="302">
+        <f>D22-C22</f>
+        <v/>
+      </c>
+      <c r="E21" s="303">
+        <f>E22-D22</f>
+        <v/>
+      </c>
+      <c r="F21" s="304" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="305" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" s="305" t="n">
+        <v>60</v>
+      </c>
+      <c r="I21" s="305" t="n">
+        <v>70</v>
+      </c>
+      <c r="J21" s="306" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="29" t="n"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Network: contract run-rate, year-end ($mm)</t>
+        </is>
+      </c>
+      <c r="C22" s="307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="307" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" s="308" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F22" s="302">
+        <f>E22+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="302">
+        <f>F22+G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="302">
+        <f>G22+H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="302">
+        <f>H22+I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="302">
+        <f>I22+J21</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="29" t="n"/>
-      <c r="B23" s="84" t="inlineStr">
+      <c r="B23" s="85" t="inlineStr">
+        <is>
+          <t>One-time revenue % of total</t>
+        </is>
+      </c>
+      <c r="C23" s="309" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D23" s="309" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E23" s="223" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F23" s="299" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G23" s="300" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H23" s="300" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I23" s="300" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J23" s="301" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="24" ht="12.75" customHeight="1"/>
+    <row r="25" ht="12.75" customHeight="1">
+      <c r="B25" s="84" t="inlineStr">
         <is>
           <t>GROSS MARGIN BY STREAM</t>
         </is>
       </c>
-      <c r="C23" s="310" t="n"/>
-      <c r="D23" s="310" t="n"/>
-      <c r="E23" s="311" t="n"/>
-      <c r="F23" s="312" t="n"/>
-      <c r="G23" s="312" t="n"/>
-      <c r="H23" s="312" t="n"/>
-      <c r="I23" s="312" t="n"/>
-      <c r="J23" s="312" t="n"/>
-    </row>
-    <row r="24" ht="12.75" customHeight="1">
-      <c r="B24" s="85" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="C24" s="297" t="n"/>
-      <c r="D24" s="297" t="n"/>
-      <c r="E24" s="298" t="n"/>
-      <c r="F24" s="299" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G24" s="300" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H24" s="300" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I24" s="300" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J24" s="301" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="25" ht="12.75" customHeight="1">
-      <c r="B25" s="85" t="inlineStr">
-        <is>
-          <t>Microtransit &amp; paratransit</t>
-        </is>
-      </c>
-      <c r="C25" s="297" t="n"/>
-      <c r="D25" s="297" t="n"/>
-      <c r="E25" s="298" t="n"/>
-      <c r="F25" s="299" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="G25" s="300" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="H25" s="300" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="I25" s="300" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="J25" s="301" t="n">
-        <v>0.293</v>
-      </c>
+      <c r="C25" s="310" t="n"/>
+      <c r="D25" s="310" t="n"/>
+      <c r="E25" s="311" t="n"/>
+      <c r="F25" s="312" t="n"/>
+      <c r="G25" s="312" t="n"/>
+      <c r="H25" s="312" t="n"/>
+      <c r="I25" s="312" t="n"/>
+      <c r="J25" s="312" t="n"/>
     </row>
     <row r="26" ht="12.75" customFormat="1" customHeight="1" s="29">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>Network deals</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="C26" s="297" t="n"/>
       <c r="D26" s="297" t="n"/>
       <c r="E26" s="298" t="n"/>
       <c r="F26" s="299" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="G26" s="300" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="H26" s="300" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I26" s="300" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="J26" s="301" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="29" t="n"/>
       <c r="B27" s="85" t="inlineStr">
         <is>
-          <t>One-time</t>
+          <t>Microtransit &amp; paratransit</t>
         </is>
       </c>
       <c r="C27" s="297" t="n"/>
       <c r="D27" s="297" t="n"/>
       <c r="E27" s="298" t="n"/>
       <c r="F27" s="299" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="G27" s="300" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="H27" s="300" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="I27" s="300" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="J27" s="301" t="n">
+        <v>0.293</v>
+      </c>
+    </row>
+    <row r="28" ht="12.75" customFormat="1" customHeight="1" s="29">
+      <c r="B28" s="85" t="inlineStr">
+        <is>
+          <t>Network deals</t>
+        </is>
+      </c>
+      <c r="C28" s="297" t="n"/>
+      <c r="D28" s="297" t="n"/>
+      <c r="E28" s="298" t="n"/>
+      <c r="F28" s="299" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G28" s="300" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H28" s="300" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I28" s="300" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J28" s="301" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" ht="12.75" customFormat="1" customHeight="1" s="29">
+      <c r="B29" s="85" t="inlineStr">
+        <is>
+          <t>One-time</t>
+        </is>
+      </c>
+      <c r="C29" s="297" t="n"/>
+      <c r="D29" s="297" t="n"/>
+      <c r="E29" s="298" t="n"/>
+      <c r="F29" s="299" t="n">
         <v>0.75</v>
       </c>
-      <c r="G27" s="300" t="n">
+      <c r="G29" s="300" t="n">
         <v>0.75</v>
       </c>
-      <c r="H27" s="300" t="n">
+      <c r="H29" s="300" t="n">
         <v>0.75</v>
       </c>
-      <c r="I27" s="300" t="n">
+      <c r="I29" s="300" t="n">
         <v>0.75</v>
       </c>
-      <c r="J27" s="301" t="n">
+      <c r="J29" s="301" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="B28" s="26" t="inlineStr">
+    <row r="30" ht="12.75" customHeight="1">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Gross profit ($mm)</t>
         </is>
       </c>
-      <c r="C28" s="278">
+      <c r="C30" s="278">
         <f>'Annual IS'!B10</f>
         <v/>
       </c>
-      <c r="D28" s="278">
+      <c r="D30" s="278">
         <f>'Annual IS'!C10</f>
         <v/>
       </c>
-      <c r="E28" s="279">
+      <c r="E30" s="279">
         <f>'Annual IS'!D10</f>
         <v/>
       </c>
-      <c r="F28" s="277">
-        <f>F4*F24+F6*F25+F7*F26+F8*F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="277">
-        <f>G4*G24+G6*G25+G7*G26+G8*G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="277">
-        <f>H4*H24+H6*H25+H7*H26+H8*H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="277">
-        <f>I4*I24+I6*I25+I7*I26+I8*I27</f>
-        <v/>
-      </c>
-      <c r="J28" s="277">
-        <f>J4*J24+J6*J25+J7*J26+J8*J27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="B29" s="280" t="inlineStr">
+      <c r="F30" s="277">
+        <f>F4*F26+F6*F27+F7*F28+F8*F29</f>
+        <v/>
+      </c>
+      <c r="G30" s="277">
+        <f>G4*G26+G6*G27+G7*G28+G8*G29</f>
+        <v/>
+      </c>
+      <c r="H30" s="277">
+        <f>H4*H26+H6*H27+H7*H28+H8*H29</f>
+        <v/>
+      </c>
+      <c r="I30" s="277">
+        <f>I4*I26+I6*I27+I7*I28+I8*I29</f>
+        <v/>
+      </c>
+      <c r="J30" s="277">
+        <f>J4*J26+J6*J27+J7*J28+J8*J29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="12.75" customHeight="1">
+      <c r="B31" s="280" t="inlineStr">
         <is>
           <t xml:space="preserve">   Gross margin</t>
         </is>
       </c>
-      <c r="C29" s="281">
-        <f>C28/C9</f>
-        <v/>
-      </c>
-      <c r="D29" s="282">
-        <f>D28/D9</f>
-        <v/>
-      </c>
-      <c r="E29" s="283">
-        <f>E28/E9</f>
-        <v/>
-      </c>
-      <c r="F29" s="282">
-        <f>F28/F9</f>
-        <v/>
-      </c>
-      <c r="G29" s="282">
-        <f>G28/G9</f>
-        <v/>
-      </c>
-      <c r="H29" s="282">
-        <f>H28/H9</f>
-        <v/>
-      </c>
-      <c r="I29" s="282">
-        <f>I28/I9</f>
-        <v/>
-      </c>
-      <c r="J29" s="282">
-        <f>J28/J9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="12.75" customHeight="1">
-      <c r="B30" s="288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Consensus gross margin (BBG; FY28 CapIQ)</t>
-        </is>
-      </c>
-      <c r="C30" s="289">
-        <f>C29</f>
-        <v/>
-      </c>
-      <c r="D30" s="289">
-        <f>D29</f>
-        <v/>
-      </c>
-      <c r="E30" s="290">
-        <f>E29</f>
-        <v/>
-      </c>
-      <c r="F30" s="313">
-        <f>'Consensus (BBG)'!P23</f>
-        <v/>
-      </c>
-      <c r="G30" s="313">
-        <f>'Consensus (BBG)'!Q23</f>
-        <v/>
-      </c>
-      <c r="H30" s="313">
-        <f>'Key Stats'!H20</f>
-        <v/>
-      </c>
-      <c r="I30" s="291" t="n"/>
-      <c r="J30" s="291" t="n"/>
-    </row>
-    <row r="31" ht="12.75" customHeight="1"/>
+      <c r="C31" s="281">
+        <f>C30/C9</f>
+        <v/>
+      </c>
+      <c r="D31" s="282">
+        <f>D30/D9</f>
+        <v/>
+      </c>
+      <c r="E31" s="283">
+        <f>E30/E9</f>
+        <v/>
+      </c>
+      <c r="F31" s="282">
+        <f>F30/F9</f>
+        <v/>
+      </c>
+      <c r="G31" s="282">
+        <f>G30/G9</f>
+        <v/>
+      </c>
+      <c r="H31" s="282">
+        <f>H30/H9</f>
+        <v/>
+      </c>
+      <c r="I31" s="282">
+        <f>I30/I9</f>
+        <v/>
+      </c>
+      <c r="J31" s="282">
+        <f>J30/J9</f>
+        <v/>
+      </c>
+    </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="29" t="n"/>
-      <c r="B32" s="314" t="inlineStr">
-        <is>
-          <t>Colour key: blue = hardcoded input, black = formula, green = link to another tab. Hover over cells with a red corner for sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="B33" s="314" t="inlineStr">
-        <is>
-          <t>Thesis 1: network deals are bus-operator contracts priced at ~95-107% of the city's transit budget, so they carry a 25% gross margin vs ~29% on microtransit and 75% on software.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B32" s="288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Consensus gross margin (BBG; FY28 CapIQ)</t>
+        </is>
+      </c>
+      <c r="C32" s="289">
+        <f>C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="289">
+        <f>D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="290">
+        <f>E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="313">
+        <f>'Consensus (BBG)'!P23</f>
+        <v/>
+      </c>
+      <c r="G32" s="313">
+        <f>'Consensus (BBG)'!Q23</f>
+        <v/>
+      </c>
+      <c r="H32" s="313">
+        <f>'Key Stats'!H20</f>
+        <v/>
+      </c>
+      <c r="I32" s="291" t="n"/>
+      <c r="J32" s="291" t="n"/>
+    </row>
+    <row r="33" ht="12.75" customFormat="1" customHeight="1" s="29"/>
     <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="314" t="inlineStr">
         <is>
-          <t>Thesis 3: microtransit/paratransit growth is net of budget-driven downsell and rebid price resets.</t>
+          <t>Colour key: blue = hardcoded input, black = formula, green = link to another tab. Hover over cells with a red corner for sources.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="314" t="inlineStr">
         <is>
+          <t>Thesis 1: network deals are bus-operator contracts priced at ~95-107% of the city's transit budget, so they carry a 25% gross margin vs ~29% on microtransit and 75% on software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="12.75" customHeight="1">
+      <c r="B36" s="314" t="inlineStr">
+        <is>
+          <t>Thesis 1: network deals become the growth engine (~a third of FY27 growth, ~25% of revenue by FY30), dragging gross margin toward operator levels. Thesis 3: microtransit/paratransit growth is net of budget-driven downsell and rebid price resets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="B37" s="314" t="inlineStr">
+        <is>
           <t>Consensus: Bloomberg FY26-27E (Consensus (BBG) tab, sum of quarters); FY28E from CapIQ (Key Stats tab) because Bloomberg stops at Q4 2027. FY29-30 have no consensus.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="12.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1"/>
     <row r="38" ht="12.75" customHeight="1"/>
     <row r="39" ht="12.75" customHeight="1"/>
     <row r="40" ht="12.75" customHeight="1"/>
@@ -6438,9 +6510,9 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="B33:J33"/>
     <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B36:J36"/>
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="F2:J2"/>
   </mergeCells>
